--- a/data_structure.xlsx
+++ b/data_structure.xlsx
@@ -413,137 +413,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>n_element</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_nodes</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>ncon1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ncon2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ncon3</t>
         </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>NDU</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>dzero</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>v</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[0.0, 0.0, 2.0, 2.0, 4.0]</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[-1.0, -5.0, -5.0, -1.0, -1.0]</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>10000000000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/data_structure.xlsx
+++ b/data_structure.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,19 +490,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -534,19 +534,19 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -562,19 +562,19 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007</v>
+        <v>0.02</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -590,19 +590,19 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0055</v>
+        <v>0.00859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0035</v>
+        <v>0.00547</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -618,19 +618,19 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002</v>
+        <v>0.008670000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -646,19 +646,19 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0035</v>
+        <v>0.00821</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005</v>
+        <v>0.00489</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -674,19 +674,19 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00625</v>
+        <v>0.008310000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00225</v>
+        <v>0.004900000000000001</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -702,19 +702,19 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0045</v>
+        <v>0.008280000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002</v>
+        <v>0.00493</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -730,19 +730,19 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00525</v>
+        <v>0.014335</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00075</v>
+        <v>0.00225</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -758,19 +758,19 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00475</v>
+        <v>0.004335</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00475</v>
+        <v>0.00225</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -786,7 +786,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
@@ -795,10 +795,10 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="G12" t="n">
-        <v>0.004500000000000001</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -814,19 +814,19 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00375</v>
+        <v>0.009105</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00325</v>
+        <v>0.007445</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -842,19 +842,19 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00275</v>
+        <v>0.005</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00175</v>
+        <v>0.005</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -870,19 +870,19 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001</v>
+        <v>0.004105</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0015</v>
+        <v>0.002445</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -898,19 +898,19 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00175</v>
+        <v>0.00844</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00025</v>
+        <v>0.004695</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -926,16 +926,20 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.009295000000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.007735000000000001</v>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
@@ -949,11 +953,21 @@
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>19</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.014295</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.002735</v>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
@@ -967,11 +981,21 @@
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>19</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.005</v>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
@@ -985,11 +1009,21 @@
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.008630000000000001</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.004985</v>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
@@ -1003,11 +1037,21 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.008400000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.005180000000000001</v>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
@@ -1021,11 +1065,21 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.00826</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.004895</v>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
@@ -1039,11 +1093,21 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.008490000000000001</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.004700000000000001</v>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
@@ -1057,11 +1121,21 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.008450000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005185</v>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
@@ -1075,11 +1149,21 @@
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16</v>
+      </c>
+      <c r="E25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.008435000000000002</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0052</v>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
@@ -1093,11 +1177,21 @@
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>21</v>
+      </c>
+      <c r="E26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.008245000000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.00491</v>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
@@ -1111,11 +1205,21 @@
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>21</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.008295</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.004915000000000001</v>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
@@ -1129,9 +1233,15 @@
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1147,9 +1257,15 @@
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>21</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" t="n">
+        <v>22</v>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1165,9 +1281,15 @@
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>23</v>
+      </c>
+      <c r="E30" t="n">
+        <v>19</v>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1183,9 +1305,15 @@
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>23</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>22</v>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1198,6 +1326,486 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>19</v>
+      </c>
+      <c r="D32" t="n">
+        <v>22</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>23</v>
+      </c>
+      <c r="D33" t="n">
+        <v>22</v>
+      </c>
+      <c r="E33" t="n">
+        <v>19</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>24</v>
+      </c>
+      <c r="E34" t="n">
+        <v>25</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>24</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>20</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>25</v>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="n">
+        <v>24</v>
+      </c>
+      <c r="D37" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" t="n">
+        <v>25</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" t="n">
+        <v>26</v>
+      </c>
+      <c r="E38" t="n">
+        <v>21</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>26</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>21</v>
+      </c>
+      <c r="D40" t="n">
+        <v>25</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>26</v>
+      </c>
+      <c r="D41" t="n">
+        <v>25</v>
+      </c>
+      <c r="E41" t="n">
+        <v>21</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>26</v>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>26</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>23</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D44" t="n">
+        <v>23</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>26</v>
+      </c>
+      <c r="D45" t="n">
+        <v>23</v>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_structure.xlsx
+++ b/data_structure.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,63 +490,65 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
         <v>0.01</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -554,7 +556,9 @@
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>12</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
     </row>
@@ -562,19 +566,19 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
         <v>0.02</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -582,7 +586,9 @@
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>13</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
     </row>
@@ -590,19 +596,19 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00859</v>
+        <v>0.02</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00547</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -610,7 +616,9 @@
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
     </row>
@@ -618,19 +626,19 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008670000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004500000000000001</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -638,7 +646,9 @@
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>27</v>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -646,19 +656,19 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00821</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00489</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -666,7 +676,9 @@
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>28</v>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
     </row>
@@ -674,19 +686,19 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008310000000000001</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004900000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -694,7 +706,9 @@
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>77</v>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
     </row>
@@ -702,19 +716,19 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008280000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00493</v>
+        <v>0.005</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -722,7 +736,9 @@
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>78</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
     </row>
@@ -730,27 +746,29 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>0.014335</v>
+        <v>0.025</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00225</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>83</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -758,19 +776,19 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>0.004335</v>
+        <v>0.025</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00225</v>
+        <v>0.005</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -778,7 +796,9 @@
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>84</v>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -786,19 +806,19 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
+        <v>64</v>
+      </c>
+      <c r="D12" t="n">
+        <v>63</v>
+      </c>
+      <c r="E12" t="n">
         <v>10</v>
       </c>
-      <c r="D12" t="n">
-        <v>14</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
       <c r="F12" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -806,7 +826,9 @@
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>249</v>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
     </row>
@@ -814,19 +836,19 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>0.009105</v>
+        <v>0.01</v>
       </c>
       <c r="G13" t="n">
-        <v>0.007445</v>
+        <v>0.005</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -834,7 +856,9 @@
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>250</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
     </row>
@@ -842,19 +866,19 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="F14" t="n">
         <v>0.005</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -862,7 +886,9 @@
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>255</v>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
     </row>
@@ -870,19 +896,19 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="F15" t="n">
-        <v>0.004105</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002445</v>
+        <v>0.005</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -890,7 +916,9 @@
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>256</v>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
     </row>
@@ -898,19 +926,19 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00844</v>
+        <v>0.005</v>
       </c>
       <c r="G16" t="n">
-        <v>0.004695</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -918,7 +946,9 @@
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>267</v>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
     </row>
@@ -926,19 +956,19 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="F17" t="n">
-        <v>0.009295000000000001</v>
+        <v>0.015</v>
       </c>
       <c r="G17" t="n">
-        <v>0.007735000000000001</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -946,7 +976,9 @@
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>268</v>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
     </row>
@@ -954,19 +986,19 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F18" t="n">
-        <v>0.014295</v>
+        <v>0.015</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002735</v>
+        <v>0.005</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -974,7 +1006,9 @@
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>273</v>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
     </row>
@@ -982,19 +1016,19 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
         <v>0.015</v>
       </c>
       <c r="G19" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1002,7 +1036,9 @@
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>274</v>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
     </row>
@@ -1010,19 +1046,19 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>0.008630000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004985</v>
+        <v>0.0075</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1038,19 +1074,19 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
-        <v>0.008400000000000001</v>
+        <v>0.0225</v>
       </c>
       <c r="G21" t="n">
-        <v>0.005180000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1066,19 +1102,19 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00826</v>
+        <v>0.0225</v>
       </c>
       <c r="G22" t="n">
-        <v>0.004895</v>
+        <v>0.0075</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1094,19 +1130,19 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="F23" t="n">
-        <v>0.008490000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004700000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1122,19 +1158,19 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>0.008450000000000001</v>
+        <v>0.0225</v>
       </c>
       <c r="G24" t="n">
-        <v>0.005185</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1150,19 +1186,19 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="F25" t="n">
-        <v>0.008435000000000002</v>
+        <v>0.0225</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0052</v>
+        <v>0.0025</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1178,19 +1214,19 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="F26" t="n">
-        <v>0.008245000000000001</v>
+        <v>0.025</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00491</v>
+        <v>0.0025</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1206,19 +1242,19 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>0.008295</v>
+        <v>0.0275</v>
       </c>
       <c r="G27" t="n">
-        <v>0.004915000000000001</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1234,16 +1270,20 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="D28" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
@@ -1258,16 +1298,20 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0075</v>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
@@ -1282,16 +1326,20 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D30" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="E30" t="n">
-        <v>19</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0075</v>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
@@ -1306,16 +1354,20 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
+        <v>70</v>
+      </c>
+      <c r="D31" t="n">
         <v>23</v>
       </c>
-      <c r="D31" t="n">
-        <v>7</v>
-      </c>
       <c r="E31" t="n">
-        <v>22</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.01</v>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
@@ -1330,16 +1382,20 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="D32" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
@@ -1354,16 +1410,20 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D33" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="E33" t="n">
-        <v>19</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
@@ -1378,16 +1438,20 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.005</v>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
@@ -1402,16 +1466,20 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E35" t="n">
-        <v>20</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0075</v>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
@@ -1426,16 +1494,20 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0075</v>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
@@ -1450,16 +1522,20 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="D37" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.01</v>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
@@ -1474,16 +1550,20 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D38" t="n">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="E38" t="n">
-        <v>21</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
@@ -1498,16 +1578,20 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>25</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
@@ -1522,16 +1606,20 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="D40" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0075</v>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
@@ -1546,16 +1634,20 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="D41" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>21</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.005</v>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
@@ -1570,16 +1662,20 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D42" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="E42" t="n">
-        <v>24</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
@@ -1594,16 +1690,20 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
+        <v>80</v>
+      </c>
+      <c r="D43" t="n">
         <v>26</v>
       </c>
-      <c r="D43" t="n">
-        <v>7</v>
-      </c>
       <c r="E43" t="n">
-        <v>23</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
@@ -1618,16 +1718,20 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="D44" t="n">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
@@ -1642,16 +1746,20 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="D45" t="n">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E45" t="n">
-        <v>24</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
@@ -1665,11 +1773,21 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>25</v>
+      </c>
+      <c r="D46" t="n">
+        <v>79</v>
+      </c>
+      <c r="E46" t="n">
+        <v>75</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
@@ -1683,11 +1801,21 @@
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>79</v>
+      </c>
+      <c r="D47" t="n">
+        <v>26</v>
+      </c>
+      <c r="E47" t="n">
+        <v>80</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
@@ -1701,11 +1829,21 @@
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>75</v>
+      </c>
+      <c r="D48" t="n">
+        <v>80</v>
+      </c>
+      <c r="E48" t="n">
+        <v>27</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
@@ -1719,11 +1857,21 @@
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>79</v>
+      </c>
+      <c r="D49" t="n">
+        <v>80</v>
+      </c>
+      <c r="E49" t="n">
+        <v>75</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
@@ -1737,11 +1885,21 @@
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" t="n">
+        <v>67</v>
+      </c>
+      <c r="E50" t="n">
+        <v>60</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.005</v>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
@@ -1755,11 +1913,21 @@
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>67</v>
+      </c>
+      <c r="D51" t="n">
+        <v>24</v>
+      </c>
+      <c r="E51" t="n">
+        <v>83</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.0075</v>
+      </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
@@ -1773,11 +1941,21 @@
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>60</v>
+      </c>
+      <c r="D52" t="n">
+        <v>83</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.005</v>
+      </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
@@ -1791,11 +1969,21 @@
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="C53" t="n">
+        <v>67</v>
+      </c>
+      <c r="D53" t="n">
+        <v>83</v>
+      </c>
+      <c r="E53" t="n">
+        <v>60</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.01</v>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
@@ -1806,6 +1994,8030 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>24</v>
+      </c>
+      <c r="D54" t="n">
+        <v>73</v>
+      </c>
+      <c r="E54" t="n">
+        <v>84</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>73</v>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>77</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="n">
+        <v>84</v>
+      </c>
+      <c r="D56" t="n">
+        <v>77</v>
+      </c>
+      <c r="E56" t="n">
+        <v>25</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>73</v>
+      </c>
+      <c r="D57" t="n">
+        <v>77</v>
+      </c>
+      <c r="E57" t="n">
+        <v>84</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>20</v>
+      </c>
+      <c r="D58" t="n">
+        <v>85</v>
+      </c>
+      <c r="E58" t="n">
+        <v>63</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="n">
+        <v>85</v>
+      </c>
+      <c r="D59" t="n">
+        <v>25</v>
+      </c>
+      <c r="E59" t="n">
+        <v>74</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="n">
+        <v>63</v>
+      </c>
+      <c r="D60" t="n">
+        <v>74</v>
+      </c>
+      <c r="E60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>85</v>
+      </c>
+      <c r="D61" t="n">
+        <v>74</v>
+      </c>
+      <c r="E61" t="n">
+        <v>63</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="n">
+        <v>24</v>
+      </c>
+      <c r="D62" t="n">
+        <v>84</v>
+      </c>
+      <c r="E62" t="n">
+        <v>83</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="n">
+        <v>84</v>
+      </c>
+      <c r="D63" t="n">
+        <v>25</v>
+      </c>
+      <c r="E63" t="n">
+        <v>85</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="n">
+        <v>83</v>
+      </c>
+      <c r="D64" t="n">
+        <v>85</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="n">
+        <v>84</v>
+      </c>
+      <c r="D65" t="n">
+        <v>85</v>
+      </c>
+      <c r="E65" t="n">
+        <v>83</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="n">
+        <v>7</v>
+      </c>
+      <c r="D66" t="n">
+        <v>86</v>
+      </c>
+      <c r="E66" t="n">
+        <v>88</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="n">
+        <v>86</v>
+      </c>
+      <c r="D67" t="n">
+        <v>28</v>
+      </c>
+      <c r="E67" t="n">
+        <v>87</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="n">
+        <v>88</v>
+      </c>
+      <c r="D68" t="n">
+        <v>87</v>
+      </c>
+      <c r="E68" t="n">
+        <v>30</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="n">
+        <v>86</v>
+      </c>
+      <c r="D69" t="n">
+        <v>87</v>
+      </c>
+      <c r="E69" t="n">
+        <v>88</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="n">
+        <v>28</v>
+      </c>
+      <c r="D70" t="n">
+        <v>89</v>
+      </c>
+      <c r="E70" t="n">
+        <v>91</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="n">
+        <v>89</v>
+      </c>
+      <c r="D71" t="n">
+        <v>11</v>
+      </c>
+      <c r="E71" t="n">
+        <v>90</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="n">
+        <v>91</v>
+      </c>
+      <c r="D72" t="n">
+        <v>90</v>
+      </c>
+      <c r="E72" t="n">
+        <v>29</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="n">
+        <v>89</v>
+      </c>
+      <c r="D73" t="n">
+        <v>90</v>
+      </c>
+      <c r="E73" t="n">
+        <v>91</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="n">
+        <v>30</v>
+      </c>
+      <c r="D74" t="n">
+        <v>92</v>
+      </c>
+      <c r="E74" t="n">
+        <v>94</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="n">
+        <v>92</v>
+      </c>
+      <c r="D75" t="n">
+        <v>29</v>
+      </c>
+      <c r="E75" t="n">
+        <v>93</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="n">
+        <v>94</v>
+      </c>
+      <c r="D76" t="n">
+        <v>93</v>
+      </c>
+      <c r="E76" t="n">
+        <v>13</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.02625</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="n">
+        <v>92</v>
+      </c>
+      <c r="D77" t="n">
+        <v>93</v>
+      </c>
+      <c r="E77" t="n">
+        <v>94</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.02625</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="n">
+        <v>28</v>
+      </c>
+      <c r="D78" t="n">
+        <v>91</v>
+      </c>
+      <c r="E78" t="n">
+        <v>87</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="n">
+        <v>91</v>
+      </c>
+      <c r="D79" t="n">
+        <v>29</v>
+      </c>
+      <c r="E79" t="n">
+        <v>92</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.02625</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="n">
+        <v>87</v>
+      </c>
+      <c r="D80" t="n">
+        <v>92</v>
+      </c>
+      <c r="E80" t="n">
+        <v>30</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.02625</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="n">
+        <v>91</v>
+      </c>
+      <c r="D81" t="n">
+        <v>92</v>
+      </c>
+      <c r="E81" t="n">
+        <v>87</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="n">
+        <v>11</v>
+      </c>
+      <c r="D82" t="n">
+        <v>95</v>
+      </c>
+      <c r="E82" t="n">
+        <v>97</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.02875</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="n">
+        <v>95</v>
+      </c>
+      <c r="D83" t="n">
+        <v>31</v>
+      </c>
+      <c r="E83" t="n">
+        <v>96</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.02875</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="n">
+        <v>97</v>
+      </c>
+      <c r="D84" t="n">
+        <v>96</v>
+      </c>
+      <c r="E84" t="n">
+        <v>33</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="n">
+        <v>95</v>
+      </c>
+      <c r="D85" t="n">
+        <v>96</v>
+      </c>
+      <c r="E85" t="n">
+        <v>97</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="n">
+        <v>31</v>
+      </c>
+      <c r="D86" t="n">
+        <v>98</v>
+      </c>
+      <c r="E86" t="n">
+        <v>100</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>98</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="n">
+        <v>99</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="n">
+        <v>100</v>
+      </c>
+      <c r="D88" t="n">
+        <v>99</v>
+      </c>
+      <c r="E88" t="n">
+        <v>32</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="n">
+        <v>98</v>
+      </c>
+      <c r="D89" t="n">
+        <v>99</v>
+      </c>
+      <c r="E89" t="n">
+        <v>100</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>33</v>
+      </c>
+      <c r="D90" t="n">
+        <v>101</v>
+      </c>
+      <c r="E90" t="n">
+        <v>103</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="n">
+        <v>101</v>
+      </c>
+      <c r="D91" t="n">
+        <v>32</v>
+      </c>
+      <c r="E91" t="n">
+        <v>102</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>103</v>
+      </c>
+      <c r="D92" t="n">
+        <v>102</v>
+      </c>
+      <c r="E92" t="n">
+        <v>12</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="n">
+        <v>101</v>
+      </c>
+      <c r="D93" t="n">
+        <v>102</v>
+      </c>
+      <c r="E93" t="n">
+        <v>103</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="n">
+        <v>31</v>
+      </c>
+      <c r="D94" t="n">
+        <v>100</v>
+      </c>
+      <c r="E94" t="n">
+        <v>96</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="n">
+        <v>100</v>
+      </c>
+      <c r="D95" t="n">
+        <v>32</v>
+      </c>
+      <c r="E95" t="n">
+        <v>101</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="n">
+        <v>96</v>
+      </c>
+      <c r="D96" t="n">
+        <v>101</v>
+      </c>
+      <c r="E96" t="n">
+        <v>33</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="n">
+        <v>100</v>
+      </c>
+      <c r="D97" t="n">
+        <v>101</v>
+      </c>
+      <c r="E97" t="n">
+        <v>96</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="n">
+        <v>13</v>
+      </c>
+      <c r="D98" t="n">
+        <v>104</v>
+      </c>
+      <c r="E98" t="n">
+        <v>106</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="n">
+        <v>104</v>
+      </c>
+      <c r="D99" t="n">
+        <v>34</v>
+      </c>
+      <c r="E99" t="n">
+        <v>105</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>106</v>
+      </c>
+      <c r="D100" t="n">
+        <v>105</v>
+      </c>
+      <c r="E100" t="n">
+        <v>36</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>104</v>
+      </c>
+      <c r="D101" t="n">
+        <v>105</v>
+      </c>
+      <c r="E101" t="n">
+        <v>106</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="n">
+        <v>34</v>
+      </c>
+      <c r="D102" t="n">
+        <v>107</v>
+      </c>
+      <c r="E102" t="n">
+        <v>109</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>107</v>
+      </c>
+      <c r="D103" t="n">
+        <v>12</v>
+      </c>
+      <c r="E103" t="n">
+        <v>108</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="n">
+        <v>109</v>
+      </c>
+      <c r="D104" t="n">
+        <v>108</v>
+      </c>
+      <c r="E104" t="n">
+        <v>35</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="n">
+        <v>107</v>
+      </c>
+      <c r="D105" t="n">
+        <v>108</v>
+      </c>
+      <c r="E105" t="n">
+        <v>109</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="n">
+        <v>36</v>
+      </c>
+      <c r="D106" t="n">
+        <v>110</v>
+      </c>
+      <c r="E106" t="n">
+        <v>112</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="n">
+        <v>110</v>
+      </c>
+      <c r="D107" t="n">
+        <v>35</v>
+      </c>
+      <c r="E107" t="n">
+        <v>111</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="n">
+        <v>112</v>
+      </c>
+      <c r="D108" t="n">
+        <v>111</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="n">
+        <v>110</v>
+      </c>
+      <c r="D109" t="n">
+        <v>111</v>
+      </c>
+      <c r="E109" t="n">
+        <v>112</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="n">
+        <v>34</v>
+      </c>
+      <c r="D110" t="n">
+        <v>109</v>
+      </c>
+      <c r="E110" t="n">
+        <v>105</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="n">
+        <v>109</v>
+      </c>
+      <c r="D111" t="n">
+        <v>35</v>
+      </c>
+      <c r="E111" t="n">
+        <v>110</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="n">
+        <v>105</v>
+      </c>
+      <c r="D112" t="n">
+        <v>110</v>
+      </c>
+      <c r="E112" t="n">
+        <v>36</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="n">
+        <v>109</v>
+      </c>
+      <c r="D113" t="n">
+        <v>110</v>
+      </c>
+      <c r="E113" t="n">
+        <v>105</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="n">
+        <v>11</v>
+      </c>
+      <c r="D114" t="n">
+        <v>97</v>
+      </c>
+      <c r="E114" t="n">
+        <v>90</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="n">
+        <v>97</v>
+      </c>
+      <c r="D115" t="n">
+        <v>33</v>
+      </c>
+      <c r="E115" t="n">
+        <v>113</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="n">
+        <v>90</v>
+      </c>
+      <c r="D116" t="n">
+        <v>113</v>
+      </c>
+      <c r="E116" t="n">
+        <v>29</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="n">
+        <v>97</v>
+      </c>
+      <c r="D117" t="n">
+        <v>113</v>
+      </c>
+      <c r="E117" t="n">
+        <v>90</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="n">
+        <v>33</v>
+      </c>
+      <c r="D118" t="n">
+        <v>103</v>
+      </c>
+      <c r="E118" t="n">
+        <v>114</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="n">
+        <v>103</v>
+      </c>
+      <c r="D119" t="n">
+        <v>12</v>
+      </c>
+      <c r="E119" t="n">
+        <v>107</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="n">
+        <v>114</v>
+      </c>
+      <c r="D120" t="n">
+        <v>107</v>
+      </c>
+      <c r="E120" t="n">
+        <v>34</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="n">
+        <v>103</v>
+      </c>
+      <c r="D121" t="n">
+        <v>107</v>
+      </c>
+      <c r="E121" t="n">
+        <v>114</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="n">
+        <v>29</v>
+      </c>
+      <c r="D122" t="n">
+        <v>115</v>
+      </c>
+      <c r="E122" t="n">
+        <v>93</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="n">
+        <v>115</v>
+      </c>
+      <c r="D123" t="n">
+        <v>34</v>
+      </c>
+      <c r="E123" t="n">
+        <v>104</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="n">
+        <v>93</v>
+      </c>
+      <c r="D124" t="n">
+        <v>104</v>
+      </c>
+      <c r="E124" t="n">
+        <v>13</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="n">
+        <v>115</v>
+      </c>
+      <c r="D125" t="n">
+        <v>104</v>
+      </c>
+      <c r="E125" t="n">
+        <v>93</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="n">
+        <v>33</v>
+      </c>
+      <c r="D126" t="n">
+        <v>114</v>
+      </c>
+      <c r="E126" t="n">
+        <v>113</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="n">
+        <v>114</v>
+      </c>
+      <c r="D127" t="n">
+        <v>34</v>
+      </c>
+      <c r="E127" t="n">
+        <v>115</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="n">
+        <v>113</v>
+      </c>
+      <c r="D128" t="n">
+        <v>115</v>
+      </c>
+      <c r="E128" t="n">
+        <v>29</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="n">
+        <v>114</v>
+      </c>
+      <c r="D129" t="n">
+        <v>115</v>
+      </c>
+      <c r="E129" t="n">
+        <v>113</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="n">
+        <v>2</v>
+      </c>
+      <c r="D130" t="n">
+        <v>98</v>
+      </c>
+      <c r="E130" t="n">
+        <v>117</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="n">
+        <v>98</v>
+      </c>
+      <c r="D131" t="n">
+        <v>31</v>
+      </c>
+      <c r="E131" t="n">
+        <v>116</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="n">
+        <v>117</v>
+      </c>
+      <c r="D132" t="n">
+        <v>116</v>
+      </c>
+      <c r="E132" t="n">
+        <v>38</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="n">
+        <v>98</v>
+      </c>
+      <c r="D133" t="n">
+        <v>116</v>
+      </c>
+      <c r="E133" t="n">
+        <v>117</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="n">
+        <v>31</v>
+      </c>
+      <c r="D134" t="n">
+        <v>95</v>
+      </c>
+      <c r="E134" t="n">
+        <v>119</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="n">
+        <v>95</v>
+      </c>
+      <c r="D135" t="n">
+        <v>11</v>
+      </c>
+      <c r="E135" t="n">
+        <v>118</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="n">
+        <v>119</v>
+      </c>
+      <c r="D136" t="n">
+        <v>118</v>
+      </c>
+      <c r="E136" t="n">
+        <v>37</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="n">
+        <v>95</v>
+      </c>
+      <c r="D137" t="n">
+        <v>118</v>
+      </c>
+      <c r="E137" t="n">
+        <v>119</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="n">
+        <v>38</v>
+      </c>
+      <c r="D138" t="n">
+        <v>120</v>
+      </c>
+      <c r="E138" t="n">
+        <v>122</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="n">
+        <v>120</v>
+      </c>
+      <c r="D139" t="n">
+        <v>37</v>
+      </c>
+      <c r="E139" t="n">
+        <v>121</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="n">
+        <v>122</v>
+      </c>
+      <c r="D140" t="n">
+        <v>121</v>
+      </c>
+      <c r="E140" t="n">
+        <v>15</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="n">
+        <v>120</v>
+      </c>
+      <c r="D141" t="n">
+        <v>121</v>
+      </c>
+      <c r="E141" t="n">
+        <v>122</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="n">
+        <v>31</v>
+      </c>
+      <c r="D142" t="n">
+        <v>119</v>
+      </c>
+      <c r="E142" t="n">
+        <v>116</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="n">
+        <v>119</v>
+      </c>
+      <c r="D143" t="n">
+        <v>37</v>
+      </c>
+      <c r="E143" t="n">
+        <v>120</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="n">
+        <v>116</v>
+      </c>
+      <c r="D144" t="n">
+        <v>120</v>
+      </c>
+      <c r="E144" t="n">
+        <v>38</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="n">
+        <v>119</v>
+      </c>
+      <c r="D145" t="n">
+        <v>120</v>
+      </c>
+      <c r="E145" t="n">
+        <v>116</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="n">
+        <v>11</v>
+      </c>
+      <c r="D146" t="n">
+        <v>89</v>
+      </c>
+      <c r="E146" t="n">
+        <v>124</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="n">
+        <v>89</v>
+      </c>
+      <c r="D147" t="n">
+        <v>28</v>
+      </c>
+      <c r="E147" t="n">
+        <v>123</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="n">
+        <v>124</v>
+      </c>
+      <c r="D148" t="n">
+        <v>123</v>
+      </c>
+      <c r="E148" t="n">
+        <v>40</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="n">
+        <v>89</v>
+      </c>
+      <c r="D149" t="n">
+        <v>123</v>
+      </c>
+      <c r="E149" t="n">
+        <v>124</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="n">
+        <v>28</v>
+      </c>
+      <c r="D150" t="n">
+        <v>86</v>
+      </c>
+      <c r="E150" t="n">
+        <v>126</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="n">
+        <v>86</v>
+      </c>
+      <c r="D151" t="n">
+        <v>7</v>
+      </c>
+      <c r="E151" t="n">
+        <v>125</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="n">
+        <v>126</v>
+      </c>
+      <c r="D152" t="n">
+        <v>125</v>
+      </c>
+      <c r="E152" t="n">
+        <v>39</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="n">
+        <v>86</v>
+      </c>
+      <c r="D153" t="n">
+        <v>125</v>
+      </c>
+      <c r="E153" t="n">
+        <v>126</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="n">
+        <v>40</v>
+      </c>
+      <c r="D154" t="n">
+        <v>127</v>
+      </c>
+      <c r="E154" t="n">
+        <v>129</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="n">
+        <v>127</v>
+      </c>
+      <c r="D155" t="n">
+        <v>39</v>
+      </c>
+      <c r="E155" t="n">
+        <v>128</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="n">
+        <v>129</v>
+      </c>
+      <c r="D156" t="n">
+        <v>128</v>
+      </c>
+      <c r="E156" t="n">
+        <v>14</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="n">
+        <v>127</v>
+      </c>
+      <c r="D157" t="n">
+        <v>128</v>
+      </c>
+      <c r="E157" t="n">
+        <v>129</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="n">
+        <v>28</v>
+      </c>
+      <c r="D158" t="n">
+        <v>126</v>
+      </c>
+      <c r="E158" t="n">
+        <v>123</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="n">
+        <v>126</v>
+      </c>
+      <c r="D159" t="n">
+        <v>39</v>
+      </c>
+      <c r="E159" t="n">
+        <v>127</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="n">
+        <v>123</v>
+      </c>
+      <c r="D160" t="n">
+        <v>127</v>
+      </c>
+      <c r="E160" t="n">
+        <v>40</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="n">
+        <v>126</v>
+      </c>
+      <c r="D161" t="n">
+        <v>127</v>
+      </c>
+      <c r="E161" t="n">
+        <v>123</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="n">
+        <v>15</v>
+      </c>
+      <c r="D162" t="n">
+        <v>130</v>
+      </c>
+      <c r="E162" t="n">
+        <v>132</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="n">
+        <v>130</v>
+      </c>
+      <c r="D163" t="n">
+        <v>41</v>
+      </c>
+      <c r="E163" t="n">
+        <v>131</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="n">
+        <v>132</v>
+      </c>
+      <c r="D164" t="n">
+        <v>131</v>
+      </c>
+      <c r="E164" t="n">
+        <v>43</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="n">
+        <v>130</v>
+      </c>
+      <c r="D165" t="n">
+        <v>131</v>
+      </c>
+      <c r="E165" t="n">
+        <v>132</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="n">
+        <v>41</v>
+      </c>
+      <c r="D166" t="n">
+        <v>133</v>
+      </c>
+      <c r="E166" t="n">
+        <v>135</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="n">
+        <v>133</v>
+      </c>
+      <c r="D167" t="n">
+        <v>14</v>
+      </c>
+      <c r="E167" t="n">
+        <v>134</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="n">
+        <v>135</v>
+      </c>
+      <c r="D168" t="n">
+        <v>134</v>
+      </c>
+      <c r="E168" t="n">
+        <v>42</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="n">
+        <v>133</v>
+      </c>
+      <c r="D169" t="n">
+        <v>134</v>
+      </c>
+      <c r="E169" t="n">
+        <v>135</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="n">
+        <v>43</v>
+      </c>
+      <c r="D170" t="n">
+        <v>136</v>
+      </c>
+      <c r="E170" t="n">
+        <v>138</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="n">
+        <v>136</v>
+      </c>
+      <c r="D171" t="n">
+        <v>42</v>
+      </c>
+      <c r="E171" t="n">
+        <v>137</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="n">
+        <v>138</v>
+      </c>
+      <c r="D172" t="n">
+        <v>137</v>
+      </c>
+      <c r="E172" t="n">
+        <v>6</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="n">
+        <v>136</v>
+      </c>
+      <c r="D173" t="n">
+        <v>137</v>
+      </c>
+      <c r="E173" t="n">
+        <v>138</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="n">
+        <v>41</v>
+      </c>
+      <c r="D174" t="n">
+        <v>135</v>
+      </c>
+      <c r="E174" t="n">
+        <v>131</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="n">
+        <v>135</v>
+      </c>
+      <c r="D175" t="n">
+        <v>42</v>
+      </c>
+      <c r="E175" t="n">
+        <v>136</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="n">
+        <v>131</v>
+      </c>
+      <c r="D176" t="n">
+        <v>136</v>
+      </c>
+      <c r="E176" t="n">
+        <v>43</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="n">
+        <v>135</v>
+      </c>
+      <c r="D177" t="n">
+        <v>136</v>
+      </c>
+      <c r="E177" t="n">
+        <v>131</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="n">
+        <v>11</v>
+      </c>
+      <c r="D178" t="n">
+        <v>124</v>
+      </c>
+      <c r="E178" t="n">
+        <v>118</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="n">
+        <v>124</v>
+      </c>
+      <c r="D179" t="n">
+        <v>40</v>
+      </c>
+      <c r="E179" t="n">
+        <v>139</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="n">
+        <v>118</v>
+      </c>
+      <c r="D180" t="n">
+        <v>139</v>
+      </c>
+      <c r="E180" t="n">
+        <v>37</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="n">
+        <v>124</v>
+      </c>
+      <c r="D181" t="n">
+        <v>139</v>
+      </c>
+      <c r="E181" t="n">
+        <v>118</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="n">
+        <v>40</v>
+      </c>
+      <c r="D182" t="n">
+        <v>129</v>
+      </c>
+      <c r="E182" t="n">
+        <v>140</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="n">
+        <v>129</v>
+      </c>
+      <c r="D183" t="n">
+        <v>14</v>
+      </c>
+      <c r="E183" t="n">
+        <v>133</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="n">
+        <v>140</v>
+      </c>
+      <c r="D184" t="n">
+        <v>133</v>
+      </c>
+      <c r="E184" t="n">
+        <v>41</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="n">
+        <v>129</v>
+      </c>
+      <c r="D185" t="n">
+        <v>133</v>
+      </c>
+      <c r="E185" t="n">
+        <v>140</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="n">
+        <v>37</v>
+      </c>
+      <c r="D186" t="n">
+        <v>141</v>
+      </c>
+      <c r="E186" t="n">
+        <v>121</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="n">
+        <v>141</v>
+      </c>
+      <c r="D187" t="n">
+        <v>41</v>
+      </c>
+      <c r="E187" t="n">
+        <v>130</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="n">
+        <v>121</v>
+      </c>
+      <c r="D188" t="n">
+        <v>130</v>
+      </c>
+      <c r="E188" t="n">
+        <v>15</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="n">
+        <v>141</v>
+      </c>
+      <c r="D189" t="n">
+        <v>130</v>
+      </c>
+      <c r="E189" t="n">
+        <v>121</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="n">
+        <v>40</v>
+      </c>
+      <c r="D190" t="n">
+        <v>140</v>
+      </c>
+      <c r="E190" t="n">
+        <v>139</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="n">
+        <v>140</v>
+      </c>
+      <c r="D191" t="n">
+        <v>41</v>
+      </c>
+      <c r="E191" t="n">
+        <v>141</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="n">
+        <v>139</v>
+      </c>
+      <c r="D192" t="n">
+        <v>141</v>
+      </c>
+      <c r="E192" t="n">
+        <v>37</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="n">
+        <v>140</v>
+      </c>
+      <c r="D193" t="n">
+        <v>141</v>
+      </c>
+      <c r="E193" t="n">
+        <v>139</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" t="n">
+        <v>142</v>
+      </c>
+      <c r="E194" t="n">
+        <v>99</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="n">
+        <v>142</v>
+      </c>
+      <c r="D195" t="n">
+        <v>44</v>
+      </c>
+      <c r="E195" t="n">
+        <v>143</v>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="n">
+        <v>99</v>
+      </c>
+      <c r="D196" t="n">
+        <v>143</v>
+      </c>
+      <c r="E196" t="n">
+        <v>32</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="n">
+        <v>142</v>
+      </c>
+      <c r="D197" t="n">
+        <v>143</v>
+      </c>
+      <c r="E197" t="n">
+        <v>99</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="n">
+        <v>44</v>
+      </c>
+      <c r="D198" t="n">
+        <v>144</v>
+      </c>
+      <c r="E198" t="n">
+        <v>146</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="n">
+        <v>144</v>
+      </c>
+      <c r="D199" t="n">
+        <v>16</v>
+      </c>
+      <c r="E199" t="n">
+        <v>145</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="n">
+        <v>146</v>
+      </c>
+      <c r="D200" t="n">
+        <v>145</v>
+      </c>
+      <c r="E200" t="n">
+        <v>45</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="n">
+        <v>144</v>
+      </c>
+      <c r="D201" t="n">
+        <v>145</v>
+      </c>
+      <c r="E201" t="n">
+        <v>146</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="n">
+        <v>32</v>
+      </c>
+      <c r="D202" t="n">
+        <v>147</v>
+      </c>
+      <c r="E202" t="n">
+        <v>102</v>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="n">
+        <v>147</v>
+      </c>
+      <c r="D203" t="n">
+        <v>45</v>
+      </c>
+      <c r="E203" t="n">
+        <v>148</v>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="n">
+        <v>102</v>
+      </c>
+      <c r="D204" t="n">
+        <v>148</v>
+      </c>
+      <c r="E204" t="n">
+        <v>12</v>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="n">
+        <v>147</v>
+      </c>
+      <c r="D205" t="n">
+        <v>148</v>
+      </c>
+      <c r="E205" t="n">
+        <v>102</v>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="n">
+        <v>44</v>
+      </c>
+      <c r="D206" t="n">
+        <v>146</v>
+      </c>
+      <c r="E206" t="n">
+        <v>143</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="n">
+        <v>146</v>
+      </c>
+      <c r="D207" t="n">
+        <v>45</v>
+      </c>
+      <c r="E207" t="n">
+        <v>147</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="n">
+        <v>143</v>
+      </c>
+      <c r="D208" t="n">
+        <v>147</v>
+      </c>
+      <c r="E208" t="n">
+        <v>32</v>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="n">
+        <v>146</v>
+      </c>
+      <c r="D209" t="n">
+        <v>147</v>
+      </c>
+      <c r="E209" t="n">
+        <v>143</v>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="n">
+        <v>16</v>
+      </c>
+      <c r="D210" t="n">
+        <v>149</v>
+      </c>
+      <c r="E210" t="n">
+        <v>151</v>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="n">
+        <v>149</v>
+      </c>
+      <c r="D211" t="n">
+        <v>46</v>
+      </c>
+      <c r="E211" t="n">
+        <v>150</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="n">
+        <v>151</v>
+      </c>
+      <c r="D212" t="n">
+        <v>150</v>
+      </c>
+      <c r="E212" t="n">
+        <v>48</v>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="n">
+        <v>149</v>
+      </c>
+      <c r="D213" t="n">
+        <v>150</v>
+      </c>
+      <c r="E213" t="n">
+        <v>151</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="n">
+        <v>46</v>
+      </c>
+      <c r="D214" t="n">
+        <v>152</v>
+      </c>
+      <c r="E214" t="n">
+        <v>154</v>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="n">
+        <v>152</v>
+      </c>
+      <c r="D215" t="n">
+        <v>4</v>
+      </c>
+      <c r="E215" t="n">
+        <v>153</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="n">
+        <v>154</v>
+      </c>
+      <c r="D216" t="n">
+        <v>153</v>
+      </c>
+      <c r="E216" t="n">
+        <v>47</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="n">
+        <v>152</v>
+      </c>
+      <c r="D217" t="n">
+        <v>153</v>
+      </c>
+      <c r="E217" t="n">
+        <v>154</v>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="n">
+        <v>48</v>
+      </c>
+      <c r="D218" t="n">
+        <v>155</v>
+      </c>
+      <c r="E218" t="n">
+        <v>157</v>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="n">
+        <v>155</v>
+      </c>
+      <c r="D219" t="n">
+        <v>47</v>
+      </c>
+      <c r="E219" t="n">
+        <v>156</v>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="n">
+        <v>157</v>
+      </c>
+      <c r="D220" t="n">
+        <v>156</v>
+      </c>
+      <c r="E220" t="n">
+        <v>17</v>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="n">
+        <v>155</v>
+      </c>
+      <c r="D221" t="n">
+        <v>156</v>
+      </c>
+      <c r="E221" t="n">
+        <v>157</v>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="n">
+        <v>46</v>
+      </c>
+      <c r="D222" t="n">
+        <v>154</v>
+      </c>
+      <c r="E222" t="n">
+        <v>150</v>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="n">
+        <v>154</v>
+      </c>
+      <c r="D223" t="n">
+        <v>47</v>
+      </c>
+      <c r="E223" t="n">
+        <v>155</v>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="n">
+        <v>150</v>
+      </c>
+      <c r="D224" t="n">
+        <v>155</v>
+      </c>
+      <c r="E224" t="n">
+        <v>48</v>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="n">
+        <v>154</v>
+      </c>
+      <c r="D225" t="n">
+        <v>155</v>
+      </c>
+      <c r="E225" t="n">
+        <v>150</v>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="n">
+        <v>12</v>
+      </c>
+      <c r="D226" t="n">
+        <v>158</v>
+      </c>
+      <c r="E226" t="n">
+        <v>108</v>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="n">
+        <v>158</v>
+      </c>
+      <c r="D227" t="n">
+        <v>49</v>
+      </c>
+      <c r="E227" t="n">
+        <v>159</v>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="n">
+        <v>108</v>
+      </c>
+      <c r="D228" t="n">
+        <v>159</v>
+      </c>
+      <c r="E228" t="n">
+        <v>35</v>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="n">
+        <v>158</v>
+      </c>
+      <c r="D229" t="n">
+        <v>159</v>
+      </c>
+      <c r="E229" t="n">
+        <v>108</v>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="n">
+        <v>49</v>
+      </c>
+      <c r="D230" t="n">
+        <v>160</v>
+      </c>
+      <c r="E230" t="n">
+        <v>162</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="n">
+        <v>160</v>
+      </c>
+      <c r="D231" t="n">
+        <v>17</v>
+      </c>
+      <c r="E231" t="n">
+        <v>161</v>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="n">
+        <v>162</v>
+      </c>
+      <c r="D232" t="n">
+        <v>161</v>
+      </c>
+      <c r="E232" t="n">
+        <v>50</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="n">
+        <v>160</v>
+      </c>
+      <c r="D233" t="n">
+        <v>161</v>
+      </c>
+      <c r="E233" t="n">
+        <v>162</v>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="n">
+        <v>35</v>
+      </c>
+      <c r="D234" t="n">
+        <v>163</v>
+      </c>
+      <c r="E234" t="n">
+        <v>111</v>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="n">
+        <v>163</v>
+      </c>
+      <c r="D235" t="n">
+        <v>50</v>
+      </c>
+      <c r="E235" t="n">
+        <v>164</v>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="n">
+        <v>111</v>
+      </c>
+      <c r="D236" t="n">
+        <v>164</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1</v>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="n">
+        <v>163</v>
+      </c>
+      <c r="D237" t="n">
+        <v>164</v>
+      </c>
+      <c r="E237" t="n">
+        <v>111</v>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="n">
+        <v>49</v>
+      </c>
+      <c r="D238" t="n">
+        <v>162</v>
+      </c>
+      <c r="E238" t="n">
+        <v>159</v>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="n">
+        <v>162</v>
+      </c>
+      <c r="D239" t="n">
+        <v>50</v>
+      </c>
+      <c r="E239" t="n">
+        <v>163</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="n">
+        <v>159</v>
+      </c>
+      <c r="D240" t="n">
+        <v>163</v>
+      </c>
+      <c r="E240" t="n">
+        <v>35</v>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="n">
+        <v>162</v>
+      </c>
+      <c r="D241" t="n">
+        <v>163</v>
+      </c>
+      <c r="E241" t="n">
+        <v>159</v>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="n">
+        <v>16</v>
+      </c>
+      <c r="D242" t="n">
+        <v>151</v>
+      </c>
+      <c r="E242" t="n">
+        <v>145</v>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="n">
+        <v>151</v>
+      </c>
+      <c r="D243" t="n">
+        <v>48</v>
+      </c>
+      <c r="E243" t="n">
+        <v>165</v>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="n">
+        <v>145</v>
+      </c>
+      <c r="D244" t="n">
+        <v>165</v>
+      </c>
+      <c r="E244" t="n">
+        <v>45</v>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="n">
+        <v>151</v>
+      </c>
+      <c r="D245" t="n">
+        <v>165</v>
+      </c>
+      <c r="E245" t="n">
+        <v>145</v>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="n">
+        <v>48</v>
+      </c>
+      <c r="D246" t="n">
+        <v>157</v>
+      </c>
+      <c r="E246" t="n">
+        <v>166</v>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="n">
+        <v>157</v>
+      </c>
+      <c r="D247" t="n">
+        <v>17</v>
+      </c>
+      <c r="E247" t="n">
+        <v>160</v>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="n">
+        <v>166</v>
+      </c>
+      <c r="D248" t="n">
+        <v>160</v>
+      </c>
+      <c r="E248" t="n">
+        <v>49</v>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="n">
+        <v>157</v>
+      </c>
+      <c r="D249" t="n">
+        <v>160</v>
+      </c>
+      <c r="E249" t="n">
+        <v>166</v>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="n">
+        <v>45</v>
+      </c>
+      <c r="D250" t="n">
+        <v>167</v>
+      </c>
+      <c r="E250" t="n">
+        <v>148</v>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="n">
+        <v>167</v>
+      </c>
+      <c r="D251" t="n">
+        <v>49</v>
+      </c>
+      <c r="E251" t="n">
+        <v>158</v>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="n">
+        <v>148</v>
+      </c>
+      <c r="D252" t="n">
+        <v>158</v>
+      </c>
+      <c r="E252" t="n">
+        <v>12</v>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="n">
+        <v>167</v>
+      </c>
+      <c r="D253" t="n">
+        <v>158</v>
+      </c>
+      <c r="E253" t="n">
+        <v>148</v>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="n">
+        <v>48</v>
+      </c>
+      <c r="D254" t="n">
+        <v>166</v>
+      </c>
+      <c r="E254" t="n">
+        <v>165</v>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="n">
+        <v>166</v>
+      </c>
+      <c r="D255" t="n">
+        <v>49</v>
+      </c>
+      <c r="E255" t="n">
+        <v>167</v>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="n">
+        <v>165</v>
+      </c>
+      <c r="D256" t="n">
+        <v>167</v>
+      </c>
+      <c r="E256" t="n">
+        <v>45</v>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="n">
+        <v>166</v>
+      </c>
+      <c r="D257" t="n">
+        <v>167</v>
+      </c>
+      <c r="E257" t="n">
+        <v>165</v>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="n">
+        <v>4</v>
+      </c>
+      <c r="D258" t="n">
+        <v>68</v>
+      </c>
+      <c r="E258" t="n">
+        <v>153</v>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="n">
+        <v>68</v>
+      </c>
+      <c r="D259" t="n">
+        <v>22</v>
+      </c>
+      <c r="E259" t="n">
+        <v>168</v>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="n">
+        <v>153</v>
+      </c>
+      <c r="D260" t="n">
+        <v>168</v>
+      </c>
+      <c r="E260" t="n">
+        <v>47</v>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="n">
+        <v>68</v>
+      </c>
+      <c r="D261" t="n">
+        <v>168</v>
+      </c>
+      <c r="E261" t="n">
+        <v>153</v>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="n">
+        <v>22</v>
+      </c>
+      <c r="D262" t="n">
+        <v>65</v>
+      </c>
+      <c r="E262" t="n">
+        <v>170</v>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="n">
+        <v>65</v>
+      </c>
+      <c r="D263" t="n">
+        <v>8</v>
+      </c>
+      <c r="E263" t="n">
+        <v>169</v>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="n">
+        <v>170</v>
+      </c>
+      <c r="D264" t="n">
+        <v>169</v>
+      </c>
+      <c r="E264" t="n">
+        <v>51</v>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="n">
+        <v>65</v>
+      </c>
+      <c r="D265" t="n">
+        <v>169</v>
+      </c>
+      <c r="E265" t="n">
+        <v>170</v>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="n">
+        <v>47</v>
+      </c>
+      <c r="D266" t="n">
+        <v>171</v>
+      </c>
+      <c r="E266" t="n">
+        <v>156</v>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="n">
+        <v>171</v>
+      </c>
+      <c r="D267" t="n">
+        <v>51</v>
+      </c>
+      <c r="E267" t="n">
+        <v>172</v>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr"/>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="n">
+        <v>156</v>
+      </c>
+      <c r="D268" t="n">
+        <v>172</v>
+      </c>
+      <c r="E268" t="n">
+        <v>17</v>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr"/>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="n">
+        <v>171</v>
+      </c>
+      <c r="D269" t="n">
+        <v>172</v>
+      </c>
+      <c r="E269" t="n">
+        <v>156</v>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr"/>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="n">
+        <v>22</v>
+      </c>
+      <c r="D270" t="n">
+        <v>170</v>
+      </c>
+      <c r="E270" t="n">
+        <v>168</v>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="n">
+        <v>170</v>
+      </c>
+      <c r="D271" t="n">
+        <v>51</v>
+      </c>
+      <c r="E271" t="n">
+        <v>171</v>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="n">
+        <v>168</v>
+      </c>
+      <c r="D272" t="n">
+        <v>171</v>
+      </c>
+      <c r="E272" t="n">
+        <v>47</v>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="n">
+        <v>170</v>
+      </c>
+      <c r="D273" t="n">
+        <v>171</v>
+      </c>
+      <c r="E273" t="n">
+        <v>168</v>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" t="n">
+        <v>8</v>
+      </c>
+      <c r="D274" t="n">
+        <v>59</v>
+      </c>
+      <c r="E274" t="n">
+        <v>174</v>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="n">
+        <v>59</v>
+      </c>
+      <c r="D275" t="n">
+        <v>19</v>
+      </c>
+      <c r="E275" t="n">
+        <v>173</v>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" t="n">
+        <v>174</v>
+      </c>
+      <c r="D276" t="n">
+        <v>173</v>
+      </c>
+      <c r="E276" t="n">
+        <v>53</v>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="n">
+        <v>59</v>
+      </c>
+      <c r="D277" t="n">
+        <v>173</v>
+      </c>
+      <c r="E277" t="n">
+        <v>174</v>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr"/>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="n">
+        <v>19</v>
+      </c>
+      <c r="D278" t="n">
+        <v>56</v>
+      </c>
+      <c r="E278" t="n">
+        <v>176</v>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr"/>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="n">
+        <v>56</v>
+      </c>
+      <c r="D279" t="n">
+        <v>3</v>
+      </c>
+      <c r="E279" t="n">
+        <v>175</v>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr"/>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="n">
+        <v>176</v>
+      </c>
+      <c r="D280" t="n">
+        <v>175</v>
+      </c>
+      <c r="E280" t="n">
+        <v>52</v>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr"/>
+      <c r="B281" t="inlineStr"/>
+      <c r="C281" t="n">
+        <v>56</v>
+      </c>
+      <c r="D281" t="n">
+        <v>175</v>
+      </c>
+      <c r="E281" t="n">
+        <v>176</v>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr"/>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="n">
+        <v>53</v>
+      </c>
+      <c r="D282" t="n">
+        <v>177</v>
+      </c>
+      <c r="E282" t="n">
+        <v>179</v>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr"/>
+      <c r="B283" t="inlineStr"/>
+      <c r="C283" t="n">
+        <v>177</v>
+      </c>
+      <c r="D283" t="n">
+        <v>52</v>
+      </c>
+      <c r="E283" t="n">
+        <v>178</v>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr"/>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="n">
+        <v>179</v>
+      </c>
+      <c r="D284" t="n">
+        <v>178</v>
+      </c>
+      <c r="E284" t="n">
+        <v>18</v>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr"/>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="n">
+        <v>177</v>
+      </c>
+      <c r="D285" t="n">
+        <v>178</v>
+      </c>
+      <c r="E285" t="n">
+        <v>179</v>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="n">
+        <v>19</v>
+      </c>
+      <c r="D286" t="n">
+        <v>176</v>
+      </c>
+      <c r="E286" t="n">
+        <v>173</v>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr"/>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" t="n">
+        <v>176</v>
+      </c>
+      <c r="D287" t="n">
+        <v>52</v>
+      </c>
+      <c r="E287" t="n">
+        <v>177</v>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr"/>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="n">
+        <v>173</v>
+      </c>
+      <c r="D288" t="n">
+        <v>177</v>
+      </c>
+      <c r="E288" t="n">
+        <v>53</v>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="n">
+        <v>176</v>
+      </c>
+      <c r="D289" t="n">
+        <v>177</v>
+      </c>
+      <c r="E289" t="n">
+        <v>173</v>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" t="inlineStr"/>
+      <c r="C290" t="n">
+        <v>17</v>
+      </c>
+      <c r="D290" t="n">
+        <v>180</v>
+      </c>
+      <c r="E290" t="n">
+        <v>161</v>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" t="n">
+        <v>180</v>
+      </c>
+      <c r="D291" t="n">
+        <v>54</v>
+      </c>
+      <c r="E291" t="n">
+        <v>181</v>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" t="inlineStr"/>
+      <c r="C292" t="n">
+        <v>161</v>
+      </c>
+      <c r="D292" t="n">
+        <v>181</v>
+      </c>
+      <c r="E292" t="n">
+        <v>50</v>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="n">
+        <v>180</v>
+      </c>
+      <c r="D293" t="n">
+        <v>181</v>
+      </c>
+      <c r="E293" t="n">
+        <v>161</v>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="n">
+        <v>54</v>
+      </c>
+      <c r="D294" t="n">
+        <v>182</v>
+      </c>
+      <c r="E294" t="n">
+        <v>184</v>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr"/>
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" t="n">
+        <v>182</v>
+      </c>
+      <c r="D295" t="n">
+        <v>18</v>
+      </c>
+      <c r="E295" t="n">
+        <v>183</v>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="n">
+        <v>184</v>
+      </c>
+      <c r="D296" t="n">
+        <v>183</v>
+      </c>
+      <c r="E296" t="n">
+        <v>55</v>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" t="inlineStr"/>
+      <c r="C297" t="n">
+        <v>182</v>
+      </c>
+      <c r="D297" t="n">
+        <v>183</v>
+      </c>
+      <c r="E297" t="n">
+        <v>184</v>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr"/>
+      <c r="B298" t="inlineStr"/>
+      <c r="C298" t="n">
+        <v>50</v>
+      </c>
+      <c r="D298" t="n">
+        <v>185</v>
+      </c>
+      <c r="E298" t="n">
+        <v>164</v>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr"/>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" t="n">
+        <v>185</v>
+      </c>
+      <c r="D299" t="n">
+        <v>55</v>
+      </c>
+      <c r="E299" t="n">
+        <v>186</v>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr"/>
+      <c r="B300" t="inlineStr"/>
+      <c r="C300" t="n">
+        <v>164</v>
+      </c>
+      <c r="D300" t="n">
+        <v>186</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1</v>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr"/>
+      <c r="B301" t="inlineStr"/>
+      <c r="C301" t="n">
+        <v>185</v>
+      </c>
+      <c r="D301" t="n">
+        <v>186</v>
+      </c>
+      <c r="E301" t="n">
+        <v>164</v>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr"/>
+      <c r="B302" t="inlineStr"/>
+      <c r="C302" t="n">
+        <v>54</v>
+      </c>
+      <c r="D302" t="n">
+        <v>184</v>
+      </c>
+      <c r="E302" t="n">
+        <v>181</v>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr"/>
+      <c r="B303" t="inlineStr"/>
+      <c r="C303" t="n">
+        <v>184</v>
+      </c>
+      <c r="D303" t="n">
+        <v>55</v>
+      </c>
+      <c r="E303" t="n">
+        <v>185</v>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr"/>
+      <c r="B304" t="inlineStr"/>
+      <c r="C304" t="n">
+        <v>181</v>
+      </c>
+      <c r="D304" t="n">
+        <v>185</v>
+      </c>
+      <c r="E304" t="n">
+        <v>50</v>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" t="inlineStr"/>
+      <c r="C305" t="n">
+        <v>184</v>
+      </c>
+      <c r="D305" t="n">
+        <v>185</v>
+      </c>
+      <c r="E305" t="n">
+        <v>181</v>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr"/>
+      <c r="B306" t="inlineStr"/>
+      <c r="C306" t="n">
+        <v>8</v>
+      </c>
+      <c r="D306" t="n">
+        <v>174</v>
+      </c>
+      <c r="E306" t="n">
+        <v>169</v>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" t="inlineStr"/>
+      <c r="C307" t="n">
+        <v>174</v>
+      </c>
+      <c r="D307" t="n">
+        <v>53</v>
+      </c>
+      <c r="E307" t="n">
+        <v>187</v>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+      <c r="B308" t="inlineStr"/>
+      <c r="C308" t="n">
+        <v>169</v>
+      </c>
+      <c r="D308" t="n">
+        <v>187</v>
+      </c>
+      <c r="E308" t="n">
+        <v>51</v>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr"/>
+      <c r="B309" t="inlineStr"/>
+      <c r="C309" t="n">
+        <v>174</v>
+      </c>
+      <c r="D309" t="n">
+        <v>187</v>
+      </c>
+      <c r="E309" t="n">
+        <v>169</v>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr"/>
+      <c r="B310" t="inlineStr"/>
+      <c r="C310" t="n">
+        <v>53</v>
+      </c>
+      <c r="D310" t="n">
+        <v>179</v>
+      </c>
+      <c r="E310" t="n">
+        <v>188</v>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr"/>
+      <c r="B311" t="inlineStr"/>
+      <c r="C311" t="n">
+        <v>179</v>
+      </c>
+      <c r="D311" t="n">
+        <v>18</v>
+      </c>
+      <c r="E311" t="n">
+        <v>182</v>
+      </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr"/>
+      <c r="B312" t="inlineStr"/>
+      <c r="C312" t="n">
+        <v>188</v>
+      </c>
+      <c r="D312" t="n">
+        <v>182</v>
+      </c>
+      <c r="E312" t="n">
+        <v>54</v>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
+      <c r="J312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr"/>
+      <c r="B313" t="inlineStr"/>
+      <c r="C313" t="n">
+        <v>179</v>
+      </c>
+      <c r="D313" t="n">
+        <v>182</v>
+      </c>
+      <c r="E313" t="n">
+        <v>188</v>
+      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr"/>
+      <c r="B314" t="inlineStr"/>
+      <c r="C314" t="n">
+        <v>51</v>
+      </c>
+      <c r="D314" t="n">
+        <v>189</v>
+      </c>
+      <c r="E314" t="n">
+        <v>172</v>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+      <c r="J314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr"/>
+      <c r="B315" t="inlineStr"/>
+      <c r="C315" t="n">
+        <v>189</v>
+      </c>
+      <c r="D315" t="n">
+        <v>54</v>
+      </c>
+      <c r="E315" t="n">
+        <v>180</v>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+      <c r="J315" t="n">
+        <v>0</v>
+      </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr"/>
+      <c r="B316" t="inlineStr"/>
+      <c r="C316" t="n">
+        <v>172</v>
+      </c>
+      <c r="D316" t="n">
+        <v>180</v>
+      </c>
+      <c r="E316" t="n">
+        <v>17</v>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="n">
+        <v>189</v>
+      </c>
+      <c r="D317" t="n">
+        <v>180</v>
+      </c>
+      <c r="E317" t="n">
+        <v>172</v>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr"/>
+      <c r="B318" t="inlineStr"/>
+      <c r="C318" t="n">
+        <v>53</v>
+      </c>
+      <c r="D318" t="n">
+        <v>188</v>
+      </c>
+      <c r="E318" t="n">
+        <v>187</v>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr"/>
+      <c r="B319" t="inlineStr"/>
+      <c r="C319" t="n">
+        <v>188</v>
+      </c>
+      <c r="D319" t="n">
+        <v>54</v>
+      </c>
+      <c r="E319" t="n">
+        <v>189</v>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" t="inlineStr"/>
+      <c r="C320" t="n">
+        <v>187</v>
+      </c>
+      <c r="D320" t="n">
+        <v>189</v>
+      </c>
+      <c r="E320" t="n">
+        <v>51</v>
+      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="inlineStr"/>
+      <c r="C321" t="n">
+        <v>188</v>
+      </c>
+      <c r="D321" t="n">
+        <v>189</v>
+      </c>
+      <c r="E321" t="n">
+        <v>187</v>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+      <c r="J321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" t="inlineStr"/>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+      <c r="J322" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" t="inlineStr"/>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" t="inlineStr"/>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr"/>
+      <c r="B325" t="inlineStr"/>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
+      <c r="J325" t="n">
+        <v>0</v>
+      </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr"/>
+      <c r="B326" t="inlineStr"/>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" t="inlineStr"/>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
+      <c r="J327" t="n">
+        <v>0</v>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr"/>
+      <c r="B328" t="inlineStr"/>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
+      <c r="J328" t="n">
+        <v>0</v>
+      </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr"/>
+      <c r="B329" t="inlineStr"/>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
+      <c r="J329" t="n">
+        <v>0</v>
+      </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" t="inlineStr"/>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
+      <c r="J330" t="n">
+        <v>0</v>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" t="inlineStr"/>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
+      <c r="J331" t="n">
+        <v>0</v>
+      </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr"/>
+      <c r="B332" t="inlineStr"/>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
+      <c r="J332" t="n">
+        <v>0</v>
+      </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" t="inlineStr"/>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
+      <c r="J333" t="n">
+        <v>0</v>
+      </c>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" t="inlineStr"/>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
+      <c r="J334" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr"/>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
+      <c r="J335" t="n">
+        <v>0</v>
+      </c>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="inlineStr"/>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
+      <c r="J336" t="n">
+        <v>0</v>
+      </c>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
+      <c r="J337" t="n">
+        <v>0</v>
+      </c>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr"/>
+      <c r="B338" t="inlineStr"/>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
+      <c r="J338" t="n">
+        <v>0</v>
+      </c>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" t="inlineStr"/>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
+      <c r="J339" t="n">
+        <v>0</v>
+      </c>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr"/>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
+      <c r="J340" t="n">
+        <v>0</v>
+      </c>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr"/>
+      <c r="B341" t="inlineStr"/>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
+      <c r="J341" t="n">
+        <v>0</v>
+      </c>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr"/>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
+      <c r="J342" t="n">
+        <v>0</v>
+      </c>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+      <c r="B343" t="inlineStr"/>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
+      <c r="J343" t="n">
+        <v>0</v>
+      </c>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr"/>
+      <c r="B344" t="inlineStr"/>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="n">
+        <v>0</v>
+      </c>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr"/>
+      <c r="B345" t="inlineStr"/>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr"/>
+      <c r="J345" t="n">
+        <v>0</v>
+      </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+      <c r="B346" t="inlineStr"/>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
+      <c r="J346" t="n">
+        <v>0</v>
+      </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" t="inlineStr"/>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
+      <c r="J347" t="n">
+        <v>0</v>
+      </c>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" t="inlineStr"/>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
+      <c r="J348" t="n">
+        <v>0</v>
+      </c>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="n">
+        <v>0</v>
+      </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="n">
+        <v>0</v>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr"/>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="n">
+        <v>0</v>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr"/>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="n">
+        <v>0</v>
+      </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="n">
+        <v>0</v>
+      </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="n">
+        <v>0</v>
+      </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="n">
+        <v>0</v>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="n">
+        <v>0</v>
+      </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="n">
+        <v>0</v>
+      </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="n">
+        <v>0</v>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="n">
+        <v>0</v>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr"/>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="n">
+        <v>0</v>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="n">
+        <v>0</v>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="n">
+        <v>0</v>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="n">
+        <v>0</v>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="n">
+        <v>0</v>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr"/>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="n">
+        <v>0</v>
+      </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr"/>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="n">
+        <v>0</v>
+      </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr"/>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="n">
+        <v>0</v>
+      </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr"/>
+      <c r="B370" t="inlineStr"/>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="n">
+        <v>0</v>
+      </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr"/>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
+      <c r="J371" t="n">
+        <v>0</v>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr"/>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="n">
+        <v>0</v>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr"/>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
+      <c r="J373" t="n">
+        <v>0</v>
+      </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" t="inlineStr"/>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="n">
+        <v>0</v>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr"/>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
+      <c r="J375" t="n">
+        <v>0</v>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr"/>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr"/>
+      <c r="J376" t="n">
+        <v>0</v>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr"/>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
+      <c r="J377" t="n">
+        <v>0</v>
+      </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr"/>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr"/>
+      <c r="J378" t="n">
+        <v>0</v>
+      </c>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr"/>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="n">
+        <v>0</v>
+      </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_structure.xlsx
+++ b/data_structure.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N379"/>
+  <dimension ref="A1:N315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,25 +490,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="B2" t="n">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>1000000000</v>
@@ -520,35 +520,33 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L2" t="n">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.01</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -556,9 +554,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>12</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
     </row>
@@ -566,16 +562,16 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="G4" t="n">
         <v>0.01</v>
@@ -586,9 +582,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>13</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
     </row>
@@ -596,16 +590,16 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -616,9 +610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>14</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
     </row>
@@ -626,19 +618,19 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -646,9 +638,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>27</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -656,19 +646,19 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -676,9 +666,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>28</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
     </row>
@@ -686,19 +674,19 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -706,9 +694,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>77</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
     </row>
@@ -716,19 +702,19 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -736,9 +722,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>78</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
     </row>
@@ -746,29 +730,27 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>0.025</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>83</v>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -776,19 +758,19 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>0.025</v>
+        <v>0.002130466767345598</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005</v>
+        <v>0.004682019885470806</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -796,9 +778,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>84</v>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -806,19 +786,19 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.005</v>
+        <v>0.004631606966252106</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005</v>
+        <v>-0.0006671154771972934</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -826,9 +806,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>249</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
     </row>
@@ -836,29 +814,27 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01</v>
+        <v>0.01234919867331015</v>
       </c>
       <c r="G13" t="n">
-        <v>0.005</v>
+        <v>0.003618548104620701</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>250</v>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
     </row>
@@ -866,19 +842,19 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005</v>
+        <v>0.006153120665824914</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01</v>
+        <v>0.007947335050264554</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -886,9 +862,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>255</v>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
     </row>
@@ -896,19 +870,19 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.001065233383672799</v>
       </c>
       <c r="G15" t="n">
-        <v>0.005</v>
+        <v>0.007341009942735403</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -916,9 +890,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>256</v>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
     </row>
@@ -926,19 +898,19 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.005</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -946,9 +918,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>267</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
     </row>
@@ -956,19 +926,19 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E17" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
-        <v>0.015</v>
+        <v>0.001065233383672799</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.002341009942735403</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -976,9 +946,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>268</v>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
     </row>
@@ -986,19 +954,19 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
-        <v>0.015</v>
+        <v>0.008315803483126053</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005</v>
+        <v>-0.0003335577385986467</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1006,9 +974,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>273</v>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
     </row>
@@ -1016,19 +982,19 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
-        <v>0.015</v>
+        <v>0.005815803483126053</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01</v>
+        <v>-0.002833557738598647</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1036,9 +1002,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>274</v>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
     </row>
@@ -1046,19 +1010,19 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02</v>
+        <v>0.0095</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0075</v>
+        <v>-0.0025</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1074,19 +1038,19 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0225</v>
+        <v>0.002315803483126053</v>
       </c>
       <c r="G21" t="n">
-        <v>0.005</v>
+        <v>-0.0003335577385986467</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1102,19 +1066,19 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0225</v>
+        <v>0.0035</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0075</v>
+        <v>-0.0025</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1130,19 +1094,19 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02</v>
+        <v>0.008576560332912457</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0025</v>
+        <v>0.008973667525132277</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1158,19 +1122,19 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D24" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0225</v>
+        <v>0.0055</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1186,19 +1150,19 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D25" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E25" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0225</v>
+        <v>0.003076560332912457</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0025</v>
+        <v>0.008973667525132277</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1214,19 +1178,19 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D26" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F26" t="n">
-        <v>0.025</v>
+        <v>0.007576560332912458</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0025</v>
+        <v>0.006473667525132277</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1242,19 +1206,19 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0275</v>
+        <v>0.01</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1270,19 +1234,19 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D28" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0275</v>
+        <v>0.004141793716585256</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0025</v>
+        <v>0.00631467746786768</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1298,19 +1262,19 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D29" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0025</v>
+        <v>0.01217459933665507</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0075</v>
+        <v>0.00180927405231035</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1326,19 +1290,19 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E30" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F30" t="n">
-        <v>0.005</v>
+        <v>0.0145</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0075</v>
+        <v>0.0035</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1354,19 +1318,19 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D31" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0025</v>
+        <v>0.01467459933665507</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01</v>
+        <v>0.005309274052310351</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1382,19 +1346,19 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0075</v>
+        <v>0.01067459933665507</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0025</v>
+        <v>0.004309274052310351</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1410,16 +1374,16 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D33" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01</v>
+        <v>0.0105</v>
       </c>
       <c r="G33" t="n">
         <v>0.0025</v>
@@ -1438,19 +1402,19 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0075</v>
+        <v>0.01167459933665507</v>
       </c>
       <c r="G34" t="n">
-        <v>0.005</v>
+        <v>0.00680927405231035</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1466,19 +1430,19 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E35" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0075</v>
+        <v>0.014</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0075</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1494,19 +1458,19 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D36" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E36" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0075</v>
+        <v>0.001</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1522,19 +1486,19 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D37" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E37" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0075</v>
+        <v>0.007000000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01</v>
+        <v>0.0035</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1550,19 +1514,19 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D38" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E38" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F38" t="n">
-        <v>0.005</v>
+        <v>0.004815803483126053</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0025</v>
+        <v>0.0006664422614013533</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1578,19 +1542,19 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0075</v>
+        <v>0.003565233383672799</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.003341009942735403</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1606,19 +1570,19 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D40" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E40" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0075</v>
+        <v>0.001</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1634,19 +1598,19 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D41" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E41" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0025</v>
+        <v>0.006076560332912457</v>
       </c>
       <c r="G41" t="n">
-        <v>0.005</v>
+        <v>0.006973667525132277</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1662,19 +1626,19 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D42" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E42" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0025</v>
+        <v>0.004065233383672799</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0025</v>
+        <v>0.005341009942735403</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1690,19 +1654,19 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D43" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E43" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0025</v>
+        <v>0.004</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1718,19 +1682,19 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D44" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0025</v>
+        <v>0.007500000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1746,19 +1710,19 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D45" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E45" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0125</v>
+        <v>0.001597850075509198</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.006011514914103105</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1774,19 +1738,19 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D46" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E46" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0125</v>
+        <v>0.001065233383672799</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0025</v>
+        <v>0.004841009942735403</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1802,19 +1766,19 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D47" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E47" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0175</v>
+        <v>0.001597850075509198</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.003511514914103104</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1830,19 +1794,19 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D48" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E48" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0175</v>
+        <v>0.0005326166918363994</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0025</v>
+        <v>0.008670504971367701</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1858,19 +1822,19 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D49" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E49" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F49" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0025</v>
+        <v>0.0075</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1886,19 +1850,19 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D50" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E50" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0125</v>
+        <v>0.0005326166918363994</v>
       </c>
       <c r="G50" t="n">
-        <v>0.005</v>
+        <v>0.006170504971367702</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -1914,19 +1878,19 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E51" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0125</v>
+        <v>0.0005326166918363994</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0075</v>
+        <v>0.003670504971367701</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -1942,19 +1906,19 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D52" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E52" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0175</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.005</v>
+        <v>0.0025</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1970,19 +1934,19 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D53" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E53" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0175</v>
+        <v>0.0005326166918363994</v>
       </c>
       <c r="G53" t="n">
-        <v>0.01</v>
+        <v>0.001170504971367701</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -1998,19 +1962,19 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D54" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E54" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0175</v>
+        <v>0.01015790174156303</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0075</v>
+        <v>-0.0001667788692993234</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -2026,19 +1990,19 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
+        <v>72</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
         <v>73</v>
       </c>
-      <c r="D55" t="n">
-        <v>9</v>
-      </c>
-      <c r="E55" t="n">
-        <v>77</v>
-      </c>
       <c r="F55" t="n">
-        <v>0.015</v>
+        <v>0.008907901741563026</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0075</v>
+        <v>-0.001416778869299323</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -2054,19 +2018,19 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D56" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0125</v>
+        <v>0.01075</v>
       </c>
       <c r="G56" t="n">
-        <v>0.01</v>
+        <v>-0.00125</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -2082,19 +2046,19 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
+        <v>72</v>
+      </c>
+      <c r="D57" t="n">
         <v>73</v>
       </c>
-      <c r="D57" t="n">
-        <v>77</v>
-      </c>
       <c r="E57" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F57" t="n">
-        <v>0.02</v>
+        <v>0.00647370522468908</v>
       </c>
       <c r="G57" t="n">
-        <v>0.008750000000000001</v>
+        <v>-0.0005003366078979701</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -2110,19 +2074,19 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D58" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E58" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F58" t="n">
-        <v>0.02125</v>
+        <v>0.005223705224689079</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0075</v>
+        <v>-0.00175033660789797</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -2138,19 +2102,19 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D59" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E59" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F59" t="n">
-        <v>0.02125</v>
+        <v>0.007065803483126053</v>
       </c>
       <c r="G59" t="n">
-        <v>0.008750000000000001</v>
+        <v>-0.001583557738598647</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -2166,19 +2130,19 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D60" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>0.02</v>
+        <v>0.007657901741563026</v>
       </c>
       <c r="G60" t="n">
-        <v>0.00625</v>
+        <v>-0.002666778869299323</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2194,19 +2158,19 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D61" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E61" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F61" t="n">
-        <v>0.02125</v>
+        <v>0.006407901741563027</v>
       </c>
       <c r="G61" t="n">
-        <v>0.005</v>
+        <v>-0.003916778869299324</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2222,19 +2186,19 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D62" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E62" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F62" t="n">
-        <v>0.02125</v>
+        <v>0.00825</v>
       </c>
       <c r="G62" t="n">
-        <v>0.00625</v>
+        <v>-0.00375</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2250,19 +2214,19 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D63" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E63" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0225</v>
+        <v>0.004657901741563026</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00625</v>
+        <v>-0.002666778869299323</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -2278,19 +2242,19 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D64" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E64" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
-        <v>0.02375</v>
+        <v>0.00525</v>
       </c>
       <c r="G64" t="n">
-        <v>0.005</v>
+        <v>-0.00375</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -2306,19 +2270,19 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D65" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E65" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F65" t="n">
-        <v>0.02375</v>
+        <v>0.00347370522468908</v>
       </c>
       <c r="G65" t="n">
-        <v>0.00625</v>
+        <v>-0.0005003366078979701</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -2334,19 +2298,19 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E66" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F66" t="n">
-        <v>0.02</v>
+        <v>0.004065803483126053</v>
       </c>
       <c r="G66" t="n">
-        <v>0.00375</v>
+        <v>-0.001583557738598647</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -2362,19 +2326,19 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D67" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E67" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F67" t="n">
-        <v>0.02125</v>
+        <v>0.002907901741563026</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0025</v>
+        <v>-0.001416778869299323</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -2390,19 +2354,19 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D68" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E68" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F68" t="n">
-        <v>0.02125</v>
+        <v>0.001157901741563027</v>
       </c>
       <c r="G68" t="n">
-        <v>0.00375</v>
+        <v>-0.0001667788692993234</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -2418,19 +2382,19 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D69" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E69" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F69" t="n">
-        <v>0.02</v>
+        <v>0.00175</v>
       </c>
       <c r="G69" t="n">
-        <v>0.00125</v>
+        <v>-0.00125</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -2446,19 +2410,19 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D70" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E70" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F70" t="n">
-        <v>0.02125</v>
+        <v>0.007364840499368685</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>0.008460501287698416</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -2474,19 +2438,19 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="D71" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E71" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02125</v>
+        <v>0.005826560332912457</v>
       </c>
       <c r="G71" t="n">
-        <v>0.00125</v>
+        <v>0.008973667525132277</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -2502,19 +2466,19 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D72" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0225</v>
+        <v>0.004614840499368686</v>
       </c>
       <c r="G72" t="n">
-        <v>0.00125</v>
+        <v>0.008460501287698416</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -2530,19 +2494,19 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="D73" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F73" t="n">
-        <v>0.02375</v>
+        <v>0.009788280166456227</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>0.009486833762566139</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -2558,19 +2522,19 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D74" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E74" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F74" t="n">
-        <v>0.02375</v>
+        <v>0.00825</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00125</v>
+        <v>0.01</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -2586,19 +2550,19 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D75" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E75" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F75" t="n">
-        <v>0.025</v>
+        <v>0.007038280166456228</v>
       </c>
       <c r="G75" t="n">
-        <v>0.00375</v>
+        <v>0.009486833762566139</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -2614,19 +2578,19 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D76" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E76" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
-        <v>0.02625</v>
+        <v>0.004288280166456228</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0025</v>
+        <v>0.009486833762566139</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -2642,19 +2606,19 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D77" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E77" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F77" t="n">
-        <v>0.02625</v>
+        <v>0.00275</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00375</v>
+        <v>0.01</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -2670,19 +2634,19 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D78" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E78" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F78" t="n">
-        <v>0.025</v>
+        <v>0.001538280166456229</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00125</v>
+        <v>0.009486833762566139</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -2698,19 +2662,19 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D79" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E79" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F79" t="n">
-        <v>0.02625</v>
+        <v>0.009288280166456228</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>0.008236833762566138</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -2726,19 +2690,19 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D80" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E80" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F80" t="n">
-        <v>0.02625</v>
+        <v>0.0105</v>
       </c>
       <c r="G80" t="n">
-        <v>0.00125</v>
+        <v>0.008750000000000001</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -2754,19 +2718,19 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D81" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E81" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0275</v>
+        <v>0.006864840499368686</v>
       </c>
       <c r="G81" t="n">
-        <v>0.00125</v>
+        <v>0.007210501287698416</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -2782,19 +2746,19 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D82" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E82" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="F82" t="n">
-        <v>0.02875</v>
+        <v>0.008076560332912458</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>0.007723667525132277</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -2810,19 +2774,19 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D83" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E83" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F83" t="n">
-        <v>0.02875</v>
+        <v>0.00878828016645623</v>
       </c>
       <c r="G83" t="n">
-        <v>0.00125</v>
+        <v>0.006986833762566138</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -2838,19 +2802,19 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="D84" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E84" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0225</v>
+        <v>0.008288280166456229</v>
       </c>
       <c r="G84" t="n">
-        <v>0.00375</v>
+        <v>0.005736833762566139</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -2866,19 +2830,19 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D85" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E85" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="F85" t="n">
-        <v>0.02375</v>
+        <v>0.009500000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0025</v>
+        <v>0.00625</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -2894,19 +2858,19 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D86" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E86" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F86" t="n">
-        <v>0.02375</v>
+        <v>0.003136130241965427</v>
       </c>
       <c r="G86" t="n">
-        <v>0.00375</v>
+        <v>0.005498348676669243</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
@@ -2922,19 +2886,19 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E87" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="F87" t="n">
-        <v>0.00125</v>
+        <v>0.002603513550129027</v>
       </c>
       <c r="G87" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.006827843705301541</v>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -2950,19 +2914,19 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D88" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="E88" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0025</v>
+        <v>0.005147457191205085</v>
       </c>
       <c r="G88" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.007131006259066117</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -2978,19 +2942,19 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D89" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="E89" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F89" t="n">
-        <v>0.00125</v>
+        <v>0.003609177024748856</v>
       </c>
       <c r="G89" t="n">
-        <v>0.01</v>
+        <v>0.007644172496499979</v>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -3006,19 +2970,19 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D90" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E90" t="n">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="F90" t="n">
-        <v>0.00375</v>
+        <v>0.002070896858292628</v>
       </c>
       <c r="G90" t="n">
-        <v>0.00625</v>
+        <v>0.008157338733933841</v>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -3034,19 +2998,19 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D91" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E91" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="F91" t="n">
-        <v>0.005</v>
+        <v>0.01226189900498261</v>
       </c>
       <c r="G91" t="n">
-        <v>0.00625</v>
+        <v>0.002713911078465526</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -3062,19 +3026,19 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="D92" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>0.00375</v>
+        <v>0.01342459933665507</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0075</v>
+        <v>0.00355927405231035</v>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -3090,19 +3054,19 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D93" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="F93" t="n">
-        <v>0.00375</v>
+        <v>0.01351189900498261</v>
       </c>
       <c r="G93" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.004463911078465526</v>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
@@ -3118,19 +3082,19 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D94" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E94" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F94" t="n">
-        <v>0.005</v>
+        <v>0.01208729966832754</v>
       </c>
       <c r="G94" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.0009046370261551752</v>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -3146,19 +3110,19 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D95" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E95" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F95" t="n">
-        <v>0.00375</v>
+        <v>0.01325</v>
       </c>
       <c r="G95" t="n">
-        <v>0.01</v>
+        <v>0.00175</v>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -3174,19 +3138,19 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D96" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E96" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F96" t="n">
-        <v>0.00625</v>
+        <v>0.01333729966832754</v>
       </c>
       <c r="G96" t="n">
-        <v>0.00375</v>
+        <v>0.002654637026155175</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
@@ -3202,19 +3166,19 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D97" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E97" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0075</v>
+        <v>0.01458729966832754</v>
       </c>
       <c r="G97" t="n">
-        <v>0.00375</v>
+        <v>0.004404637026155176</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
@@ -3230,19 +3194,19 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D98" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E98" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F98" t="n">
-        <v>0.00625</v>
+        <v>0.01575</v>
       </c>
       <c r="G98" t="n">
-        <v>0.005</v>
+        <v>0.00525</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
@@ -3258,19 +3222,19 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D99" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E99" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F99" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.01583729966832754</v>
       </c>
       <c r="G99" t="n">
-        <v>0.00125</v>
+        <v>0.006154637026155175</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
@@ -3286,19 +3250,19 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D100" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E100" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F100" t="n">
-        <v>0.01</v>
+        <v>0.01133729966832754</v>
       </c>
       <c r="G100" t="n">
-        <v>0.00125</v>
+        <v>0.002154637026155175</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
@@ -3314,19 +3278,19 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D101" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E101" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F101" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.01125</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0025</v>
+        <v>0.00125</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
@@ -3342,19 +3306,19 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D102" t="n">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E102" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F102" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.01151189900498261</v>
       </c>
       <c r="G102" t="n">
-        <v>0.00375</v>
+        <v>0.003963911078465525</v>
       </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
@@ -3370,19 +3334,19 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D103" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E103" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="F103" t="n">
-        <v>0.01</v>
+        <v>0.01142459933665507</v>
       </c>
       <c r="G103" t="n">
-        <v>0.00375</v>
+        <v>0.00305927405231035</v>
       </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
@@ -3398,19 +3362,19 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D104" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E104" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F104" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.01058729966832754</v>
       </c>
       <c r="G104" t="n">
-        <v>0.005</v>
+        <v>0.003404637026155176</v>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
@@ -3426,19 +3390,19 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D105" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E105" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F105" t="n">
-        <v>0.00625</v>
+        <v>0.009837299668327536</v>
       </c>
       <c r="G105" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.004654637026155175</v>
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
@@ -3454,19 +3418,19 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D106" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E106" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0075</v>
+        <v>0.009750000000000002</v>
       </c>
       <c r="G106" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
@@ -3482,19 +3446,19 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D107" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E107" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="F107" t="n">
-        <v>0.00625</v>
+        <v>0.01133729966832754</v>
       </c>
       <c r="G107" t="n">
-        <v>0.01</v>
+        <v>0.008404637026155175</v>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
@@ -3510,19 +3474,19 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D108" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F108" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.01283729966832754</v>
       </c>
       <c r="G108" t="n">
-        <v>0.00625</v>
+        <v>0.007654637026155176</v>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
@@ -3538,19 +3502,19 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D109" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E109" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F109" t="n">
-        <v>0.01</v>
+        <v>0.0125</v>
       </c>
       <c r="G109" t="n">
-        <v>0.00625</v>
+        <v>0.009250000000000001</v>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
@@ -3566,19 +3530,19 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D110" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E110" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F110" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.01201189900498261</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0075</v>
+        <v>0.005213911078465526</v>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
@@ -3594,19 +3558,19 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D111" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E111" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F111" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.01317459933665507</v>
       </c>
       <c r="G111" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.00605927405231035</v>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
@@ -3622,19 +3586,19 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D112" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E112" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F112" t="n">
-        <v>0.01</v>
+        <v>0.01433729966832754</v>
       </c>
       <c r="G112" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.006904637026155175</v>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
@@ -3650,19 +3614,19 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D113" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E113" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F113" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.0155</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01</v>
+        <v>0.00775</v>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
@@ -3678,19 +3642,19 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D114" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E114" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F114" t="n">
-        <v>0.00625</v>
+        <v>0.01117459933665507</v>
       </c>
       <c r="G114" t="n">
-        <v>0.00625</v>
+        <v>0.00555927405231035</v>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
@@ -3706,19 +3670,19 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D115" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E115" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0075</v>
+        <v>0.01083729966832754</v>
       </c>
       <c r="G115" t="n">
-        <v>0.00625</v>
+        <v>0.007154637026155175</v>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
@@ -3734,19 +3698,19 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D116" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E116" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F116" t="n">
-        <v>0.00625</v>
+        <v>0.01033729966832754</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0075</v>
+        <v>0.005904637026155175</v>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
@@ -3762,19 +3726,19 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D117" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E117" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0075</v>
+        <v>0.006750000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>0.00125</v>
+        <v>0.0015</v>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
@@ -3790,19 +3754,19 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D118" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E118" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F118" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.007750000000000001</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>0.00225</v>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
@@ -3818,19 +3782,19 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D119" t="n">
         <v>12</v>
       </c>
       <c r="E119" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F119" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="G119" t="n">
-        <v>0.00375</v>
+        <v>0.00275</v>
       </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
@@ -3846,19 +3810,19 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D120" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E120" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F120" t="n">
-        <v>0.00625</v>
+        <v>0.01025</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0025</v>
+        <v>0.0005</v>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
@@ -3874,19 +3838,19 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D121" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E121" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F121" t="n">
-        <v>0.00625</v>
+        <v>0.009500000000000001</v>
       </c>
       <c r="G121" t="n">
-        <v>0.00125</v>
+        <v>0.00175</v>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
@@ -3902,19 +3866,19 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D122" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E122" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="F122" t="n">
-        <v>0.005</v>
+        <v>0.008750000000000001</v>
       </c>
       <c r="G122" t="n">
-        <v>0.00125</v>
+        <v>0.003</v>
       </c>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
@@ -3930,19 +3894,19 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D123" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E123" t="n">
         <v>104</v>
       </c>
       <c r="F123" t="n">
-        <v>0.00625</v>
+        <v>0.008</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>0.00425</v>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
@@ -3958,19 +3922,19 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D124" t="n">
         <v>104</v>
       </c>
       <c r="E124" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0025</v>
+        <v>0.004907901741563027</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00625</v>
+        <v>0.001333221130700677</v>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
@@ -3986,19 +3950,19 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D125" t="n">
         <v>104</v>
       </c>
       <c r="E125" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="F125" t="n">
-        <v>0.00375</v>
+        <v>0.006657901741563027</v>
       </c>
       <c r="G125" t="n">
-        <v>0.005</v>
+        <v>0.0008332211307006767</v>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
@@ -4014,19 +3978,19 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D126" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E126" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>0.00472370522468908</v>
       </c>
       <c r="G126" t="n">
-        <v>0.008750000000000001</v>
+        <v>-3.366078979700582e-07</v>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
@@ -4042,19 +4006,19 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D127" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E127" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F127" t="n">
-        <v>0.00125</v>
+        <v>0.006565803483126053</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0075</v>
+        <v>0.0001664422614013533</v>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
@@ -4070,19 +4034,19 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D128" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E128" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F128" t="n">
-        <v>0.00125</v>
+        <v>0.008407901741563027</v>
       </c>
       <c r="G128" t="n">
-        <v>0.00625</v>
+        <v>0.0003332211307006767</v>
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
@@ -4098,19 +4062,19 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D129" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E129" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>0.004282616691836399</v>
       </c>
       <c r="G129" t="n">
-        <v>0.00625</v>
+        <v>0.002670504971367701</v>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
@@ -4126,19 +4090,19 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E130" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="F130" t="n">
-        <v>0.00125</v>
+        <v>0.003032616691836399</v>
       </c>
       <c r="G130" t="n">
-        <v>0.005</v>
+        <v>0.002170504971367702</v>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
@@ -4154,19 +4118,19 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D131" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E131" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F131" t="n">
         <v>0.00375</v>
       </c>
       <c r="G131" t="n">
-        <v>0.00125</v>
+        <v>0.0015</v>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
@@ -4182,19 +4146,19 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D132" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E132" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0025</v>
+        <v>0.002847850075509199</v>
       </c>
       <c r="G132" t="n">
-        <v>0.00125</v>
+        <v>0.004011514914103105</v>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
@@ -4210,19 +4174,19 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D133" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E133" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="F133" t="n">
-        <v>0.00375</v>
+        <v>0.002315233383672799</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>0.002841009942735403</v>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
@@ -4238,19 +4202,19 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D134" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E134" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="F134" t="n">
-        <v>0.00125</v>
+        <v>0.001782616691836399</v>
       </c>
       <c r="G134" t="n">
-        <v>0.00375</v>
+        <v>0.001670504971367702</v>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
@@ -4266,19 +4230,19 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D135" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E135" t="n">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>0.00125</v>
       </c>
       <c r="G135" t="n">
-        <v>0.00375</v>
+        <v>0.0005</v>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
@@ -4294,19 +4258,19 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D136" t="n">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="E136" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F136" t="n">
-        <v>0.00125</v>
+        <v>0.003565803483126053</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0025</v>
+        <v>0.0001664422614013533</v>
       </c>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
@@ -4322,19 +4286,19 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D137" t="n">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="E137" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="F137" t="n">
-        <v>0.00125</v>
+        <v>0.003657901741563027</v>
       </c>
       <c r="G137" t="n">
-        <v>0.00125</v>
+        <v>0.0008332211307006767</v>
       </c>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
@@ -4350,19 +4314,19 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D138" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E138" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>0.002407901741563027</v>
       </c>
       <c r="G138" t="n">
-        <v>0.00125</v>
+        <v>0.0003332211307006767</v>
       </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
@@ -4378,19 +4342,19 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D139" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E139" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="F139" t="n">
-        <v>0.00125</v>
+        <v>0.006038280166456229</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>0.006486833762566139</v>
       </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
@@ -4406,19 +4370,19 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D140" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E140" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F140" t="n">
-        <v>0.00375</v>
+        <v>0.005070896858292628</v>
       </c>
       <c r="G140" t="n">
-        <v>0.00375</v>
+        <v>0.00615733873393384</v>
       </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
@@ -4434,19 +4398,19 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D141" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E141" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0025</v>
+        <v>0.005032616691836399</v>
       </c>
       <c r="G141" t="n">
-        <v>0.00375</v>
+        <v>0.005670504971367701</v>
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
@@ -4462,19 +4426,19 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D142" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E142" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F142" t="n">
-        <v>0.00375</v>
+        <v>0.006114840499368685</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0025</v>
+        <v>0.007460501287698416</v>
       </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
@@ -4490,19 +4454,19 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D143" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E143" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F143" t="n">
-        <v>0.01125</v>
+        <v>0.005109177024748857</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>0.006644172496499979</v>
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
@@ -4518,19 +4482,19 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D144" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E144" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F144" t="n">
-        <v>0.01125</v>
+        <v>0.004103513550129027</v>
       </c>
       <c r="G144" t="n">
-        <v>0.00125</v>
+        <v>0.005827843705301541</v>
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
@@ -4546,19 +4510,19 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D145" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E145" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F145" t="n">
-        <v>0.01375</v>
+        <v>0.003097850075509198</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>0.005011514914103104</v>
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
@@ -4574,19 +4538,19 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D146" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="E146" t="n">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="F146" t="n">
-        <v>0.01375</v>
+        <v>0.005249999999999999</v>
       </c>
       <c r="G146" t="n">
-        <v>0.00125</v>
+        <v>0.003</v>
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
@@ -4602,19 +4566,19 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D147" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E147" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0125</v>
+        <v>0.0045326166918364</v>
       </c>
       <c r="G147" t="n">
-        <v>0.00125</v>
+        <v>0.003670504971367701</v>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
@@ -4630,19 +4594,19 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D148" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E148" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F148" t="n">
-        <v>0.01125</v>
+        <v>0.00575</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0025</v>
+        <v>0.005</v>
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
@@ -4658,19 +4622,19 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D149" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E149" t="n">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="F149" t="n">
-        <v>0.01125</v>
+        <v>0.004782616691836399</v>
       </c>
       <c r="G149" t="n">
-        <v>0.00375</v>
+        <v>0.004670504971367701</v>
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
@@ -4686,19 +4650,19 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D150" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E150" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F150" t="n">
-        <v>0.01625</v>
+        <v>0.003815233383672799</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>0.004341009942735403</v>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
@@ -4714,19 +4678,19 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D151" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E151" t="n">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="F151" t="n">
-        <v>0.01625</v>
+        <v>0.006826560332912457</v>
       </c>
       <c r="G151" t="n">
-        <v>0.00125</v>
+        <v>0.006723667525132277</v>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
@@ -4742,19 +4706,19 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D152" t="n">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="E152" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F152" t="n">
-        <v>0.015</v>
+        <v>0.006750000000000001</v>
       </c>
       <c r="G152" t="n">
-        <v>0.00125</v>
+        <v>0.00575</v>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -4770,19 +4734,19 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D153" t="n">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="E153" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F153" t="n">
-        <v>0.01875</v>
+        <v>0.006788280166456229</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>0.006236833762566138</v>
       </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
@@ -4798,19 +4762,19 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D154" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E154" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="F154" t="n">
-        <v>0.01875</v>
+        <v>0.007538280166456229</v>
       </c>
       <c r="G154" t="n">
-        <v>0.00125</v>
+        <v>0.005986833762566138</v>
       </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
@@ -4826,19 +4790,19 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D155" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E155" t="n">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0175</v>
+        <v>0.00825</v>
       </c>
       <c r="G155" t="n">
-        <v>0.00125</v>
+        <v>0.005249999999999999</v>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
@@ -4854,19 +4818,19 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="D156" t="n">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="E156" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F156" t="n">
-        <v>0.01625</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0025</v>
+        <v>0.00475</v>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
@@ -4882,16 +4846,16 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D157" t="n">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="E157" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="F157" t="n">
-        <v>0.01625</v>
+        <v>0.00625</v>
       </c>
       <c r="G157" t="n">
         <v>0.00375</v>
@@ -4910,19 +4874,19 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D158" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E158" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="F158" t="n">
-        <v>0.015</v>
+        <v>0.007250000000000001</v>
       </c>
       <c r="G158" t="n">
-        <v>0.00375</v>
+        <v>0.0045</v>
       </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
@@ -4938,20 +4902,16 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D159" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E159" t="n">
-        <v>127</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0.01125</v>
-      </c>
-      <c r="G159" t="n">
-        <v>0.005</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="n">
@@ -4966,20 +4926,16 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D160" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E160" t="n">
-        <v>40</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0.01125</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0.00625</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="n">
@@ -4994,20 +4950,16 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D161" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E161" t="n">
-        <v>123</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="G161" t="n">
-        <v>0.005</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="n">
@@ -5022,20 +4974,16 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D162" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E162" t="n">
-        <v>132</v>
-      </c>
-      <c r="F162" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="G162" t="n">
-        <v>0.00625</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="n">
@@ -5050,20 +4998,16 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="D163" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E163" t="n">
-        <v>131</v>
-      </c>
-      <c r="F163" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="G163" t="n">
-        <v>0.00625</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="n">
@@ -5078,20 +5022,16 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D164" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="E164" t="n">
-        <v>43</v>
-      </c>
-      <c r="F164" t="n">
-        <v>0.01125</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0.0075</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="n">
@@ -5106,20 +5046,16 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="D165" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="E165" t="n">
-        <v>132</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0.01125</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0.008750000000000001</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="n">
@@ -5134,20 +5070,16 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D166" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E166" t="n">
-        <v>135</v>
-      </c>
-      <c r="F166" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="G166" t="n">
-        <v>0.0025</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="n">
@@ -5162,20 +5094,16 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D167" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E167" t="n">
-        <v>134</v>
-      </c>
-      <c r="F167" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="G167" t="n">
-        <v>0.00375</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="n">
@@ -5190,20 +5118,16 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D168" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="E168" t="n">
-        <v>42</v>
-      </c>
-      <c r="F168" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="G168" t="n">
-        <v>0.00375</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="n">
@@ -5218,20 +5142,16 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D169" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="E169" t="n">
-        <v>135</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0.01875</v>
-      </c>
-      <c r="G169" t="n">
-        <v>0.0025</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="n">
@@ -5246,20 +5166,16 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D170" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E170" t="n">
-        <v>138</v>
-      </c>
-      <c r="F170" t="n">
-        <v>0.01875</v>
-      </c>
-      <c r="G170" t="n">
-        <v>0.005</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="n">
@@ -5274,20 +5190,16 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D171" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E171" t="n">
-        <v>137</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0.01875</v>
-      </c>
-      <c r="G171" t="n">
-        <v>0.00375</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="n">
@@ -5302,20 +5214,16 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D172" t="n">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="E172" t="n">
-        <v>6</v>
-      </c>
-      <c r="F172" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0.00375</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
@@ -5330,20 +5238,16 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D173" t="n">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="E173" t="n">
-        <v>138</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.01625</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0.005</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
@@ -5358,20 +5262,16 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D174" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E174" t="n">
-        <v>131</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0.01875</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0.0075</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="n">
@@ -5386,20 +5286,16 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D175" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E175" t="n">
-        <v>136</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0.01875</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0.00625</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
@@ -5414,20 +5310,16 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D176" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E176" t="n">
-        <v>43</v>
-      </c>
-      <c r="F176" t="n">
-        <v>0.01875</v>
-      </c>
-      <c r="G176" t="n">
-        <v>0.01</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="n">
@@ -5442,20 +5334,16 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D177" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E177" t="n">
-        <v>131</v>
-      </c>
-      <c r="F177" t="n">
-        <v>0.01875</v>
-      </c>
-      <c r="G177" t="n">
-        <v>0.008750000000000001</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="n">
@@ -5470,20 +5358,16 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D178" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E178" t="n">
-        <v>118</v>
-      </c>
-      <c r="F178" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="G178" t="n">
-        <v>0.008750000000000001</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="n">
@@ -5498,20 +5382,16 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
+        <v>123</v>
+      </c>
+      <c r="D179" t="n">
+        <v>37</v>
+      </c>
+      <c r="E179" t="n">
         <v>124</v>
       </c>
-      <c r="D179" t="n">
-        <v>40</v>
-      </c>
-      <c r="E179" t="n">
-        <v>139</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0.01625</v>
-      </c>
-      <c r="G179" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="n">
@@ -5526,20 +5406,16 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D180" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E180" t="n">
-        <v>37</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0.01625</v>
-      </c>
-      <c r="G180" t="n">
-        <v>0.008750000000000001</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="n">
@@ -5554,20 +5430,16 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
+        <v>123</v>
+      </c>
+      <c r="D181" t="n">
         <v>124</v>
       </c>
-      <c r="D181" t="n">
-        <v>139</v>
-      </c>
       <c r="E181" t="n">
-        <v>118</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G181" t="n">
-        <v>0.00625</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="n">
@@ -5582,20 +5454,16 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D182" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E182" t="n">
-        <v>140</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="G182" t="n">
-        <v>0.0075</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="n">
@@ -5610,20 +5478,16 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D183" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E183" t="n">
-        <v>133</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G183" t="n">
-        <v>0.008750000000000001</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="n">
@@ -5638,20 +5502,16 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D184" t="n">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E184" t="n">
-        <v>41</v>
-      </c>
-      <c r="F184" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="G184" t="n">
-        <v>0.01</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="n">
@@ -5666,20 +5526,16 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D185" t="n">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E185" t="n">
-        <v>140</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="G185" t="n">
-        <v>0.008750000000000001</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="n">
@@ -5694,20 +5550,16 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D186" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E186" t="n">
-        <v>121</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="G186" t="n">
-        <v>0.008750000000000001</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="n">
@@ -5722,20 +5574,16 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D187" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="E187" t="n">
-        <v>130</v>
-      </c>
-      <c r="F187" t="n">
-        <v>0.01125</v>
-      </c>
-      <c r="G187" t="n">
-        <v>0.01</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="n">
@@ -5750,20 +5598,16 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D188" t="n">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="E188" t="n">
-        <v>15</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="G188" t="n">
-        <v>0.00625</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="n">
@@ -5778,20 +5622,16 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D189" t="n">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="E189" t="n">
-        <v>121</v>
-      </c>
-      <c r="F189" t="n">
-        <v>0.01625</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0.0075</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="n">
@@ -5806,20 +5646,16 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D190" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="E190" t="n">
-        <v>139</v>
-      </c>
-      <c r="F190" t="n">
-        <v>0.01625</v>
-      </c>
-      <c r="G190" t="n">
-        <v>0.00625</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="n">
@@ -5834,13 +5670,13 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D191" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="E191" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
@@ -5858,13 +5694,13 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D192" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E192" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
@@ -5882,13 +5718,13 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D193" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E193" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
@@ -5906,13 +5742,13 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D194" t="n">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="E194" t="n">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
@@ -5930,13 +5766,13 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D195" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E195" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
@@ -5954,13 +5790,13 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="D196" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E196" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
@@ -5978,13 +5814,13 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D197" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E197" t="n">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
@@ -6002,13 +5838,13 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D198" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E198" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
@@ -6026,13 +5862,13 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D199" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E199" t="n">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
@@ -6050,13 +5886,13 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D200" t="n">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="E200" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
@@ -6074,13 +5910,13 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D201" t="n">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="E201" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
@@ -6098,13 +5934,13 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D202" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E202" t="n">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
@@ -6122,13 +5958,13 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D203" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E203" t="n">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
@@ -6146,13 +5982,13 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="D204" t="n">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="E204" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
@@ -6170,13 +6006,13 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D205" t="n">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="E205" t="n">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
@@ -6194,13 +6030,13 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D206" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="E206" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
@@ -6218,13 +6054,13 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D207" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E207" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
@@ -6242,13 +6078,13 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D208" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E208" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
@@ -6266,13 +6102,13 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D209" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E209" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
@@ -6290,13 +6126,13 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D210" t="n">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="E210" t="n">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
@@ -6314,13 +6150,13 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="D211" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E211" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
@@ -6338,13 +6174,13 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="D212" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E212" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
@@ -6362,13 +6198,13 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="D213" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E213" t="n">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
@@ -6386,13 +6222,13 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D214" t="n">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="E214" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
@@ -6410,13 +6246,13 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="n">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="D215" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E215" t="n">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr"/>
@@ -6434,13 +6270,13 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D216" t="n">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="E216" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
@@ -6458,13 +6294,13 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="D217" t="n">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="E217" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
@@ -6482,13 +6318,13 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D218" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="E218" t="n">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
@@ -6506,13 +6342,13 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D219" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E219" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr"/>
@@ -6530,13 +6366,13 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="D220" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="E220" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
@@ -6554,13 +6390,13 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D221" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="E221" t="n">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr"/>
@@ -6578,13 +6414,13 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D222" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="E222" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
@@ -6602,13 +6438,13 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D223" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E223" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr"/>
@@ -6626,13 +6462,13 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D224" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="E224" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
@@ -6650,13 +6486,13 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D225" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="E225" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr"/>
@@ -6674,13 +6510,13 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D226" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="E226" t="n">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr"/>
@@ -6698,13 +6534,13 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="D227" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E227" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr"/>
@@ -6722,13 +6558,13 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="D228" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E228" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
@@ -6746,13 +6582,13 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="D229" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E229" t="n">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
@@ -6770,13 +6606,13 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D230" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E230" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
@@ -6794,13 +6630,13 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="D231" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E231" t="n">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr"/>
@@ -6818,13 +6654,13 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D232" t="n">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="E232" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr"/>
@@ -6842,13 +6678,13 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="D233" t="n">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="E233" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
@@ -6866,13 +6702,13 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D234" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="E234" t="n">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
@@ -6890,13 +6726,13 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="D235" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E235" t="n">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
@@ -6914,13 +6750,13 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="n">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="D236" t="n">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="E236" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
@@ -6938,13 +6774,13 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="D237" t="n">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="E237" t="n">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr"/>
@@ -6962,13 +6798,13 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D238" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="E238" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr"/>
@@ -6986,13 +6822,13 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D239" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E239" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr"/>
@@ -7010,13 +6846,13 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="D240" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="E240" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
@@ -7034,13 +6870,13 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D241" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="E241" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
@@ -7058,13 +6894,13 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D242" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E242" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
@@ -7082,13 +6918,13 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr"/>
       <c r="C243" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D243" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E243" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
@@ -7106,13 +6942,13 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D244" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E244" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
@@ -7130,13 +6966,13 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D245" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E245" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr"/>
@@ -7154,13 +6990,13 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D246" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E246" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr"/>
@@ -7178,13 +7014,13 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D247" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E247" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr"/>
@@ -7202,13 +7038,13 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="D248" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E248" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr"/>
@@ -7226,13 +7062,13 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D249" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E249" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
@@ -7250,13 +7086,13 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D250" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="E250" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
@@ -7274,13 +7110,13 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D251" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E251" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
@@ -7298,13 +7134,13 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="D252" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="E252" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
@@ -7322,13 +7158,13 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D253" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="E253" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
@@ -7346,13 +7182,13 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D254" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="E254" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
@@ -7370,13 +7206,13 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="D255" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E255" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
@@ -7394,13 +7230,13 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="D256" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="E256" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
@@ -7418,13 +7254,13 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="D257" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="E257" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
@@ -7442,13 +7278,13 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D258" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="E258" t="n">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
@@ -7466,13 +7302,13 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="D259" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E259" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr"/>
@@ -7490,13 +7326,13 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="n">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="D260" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="E260" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr"/>
@@ -7514,13 +7350,13 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="D261" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="E261" t="n">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr"/>
@@ -7538,13 +7374,13 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D262" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E262" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
@@ -7562,13 +7398,13 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D263" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E263" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
@@ -7586,13 +7422,13 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D264" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="E264" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr"/>
@@ -7610,13 +7446,13 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D265" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="E265" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr"/>
@@ -7634,13 +7470,13 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr"/>
       <c r="C266" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D266" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E266" t="n">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr"/>
@@ -7658,13 +7494,13 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D267" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E267" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr"/>
@@ -7682,13 +7518,13 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="n">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="D268" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="E268" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr"/>
@@ -7706,13 +7542,13 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D269" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="E269" t="n">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr"/>
@@ -7730,13 +7566,13 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D270" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="E270" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr"/>
@@ -7754,13 +7590,13 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr"/>
       <c r="C271" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D271" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E271" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr"/>
@@ -7778,13 +7614,13 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="D272" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E272" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr"/>
@@ -7802,13 +7638,13 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D273" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E273" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
@@ -7826,13 +7662,13 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D274" t="n">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="E274" t="n">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
@@ -7850,13 +7686,13 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="D275" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E275" t="n">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr"/>
@@ -7874,13 +7710,13 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="n">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="D276" t="n">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="E276" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr"/>
@@ -7898,13 +7734,13 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="n">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="D277" t="n">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="E277" t="n">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr"/>
@@ -7922,13 +7758,13 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D278" t="n">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="E278" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr"/>
@@ -7946,13 +7782,13 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="D279" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E279" t="n">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr"/>
@@ -7970,13 +7806,13 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D280" t="n">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="E280" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr"/>
@@ -7994,13 +7830,13 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="D281" t="n">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="E281" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr"/>
@@ -8018,13 +7854,13 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D282" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E282" t="n">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
@@ -8042,13 +7878,13 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="D283" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E283" t="n">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr"/>
@@ -8066,13 +7902,13 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="n">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="D284" t="n">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="E284" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr"/>
@@ -8090,13 +7926,13 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="D285" t="n">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="E285" t="n">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr"/>
@@ -8114,13 +7950,13 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D286" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E286" t="n">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr"/>
@@ -8138,13 +7974,13 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D287" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E287" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr"/>
@@ -8162,13 +7998,13 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D288" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E288" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr"/>
@@ -8186,13 +8022,13 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D289" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E289" t="n">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr"/>
@@ -8209,15 +8045,9 @@
     <row r="290">
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr"/>
-      <c r="C290" t="n">
-        <v>17</v>
-      </c>
-      <c r="D290" t="n">
-        <v>180</v>
-      </c>
-      <c r="E290" t="n">
-        <v>161</v>
-      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr"/>
@@ -8233,15 +8063,9 @@
     <row r="291">
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr"/>
-      <c r="C291" t="n">
-        <v>180</v>
-      </c>
-      <c r="D291" t="n">
-        <v>54</v>
-      </c>
-      <c r="E291" t="n">
-        <v>181</v>
-      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
@@ -8257,15 +8081,9 @@
     <row r="292">
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr"/>
-      <c r="C292" t="n">
-        <v>161</v>
-      </c>
-      <c r="D292" t="n">
-        <v>181</v>
-      </c>
-      <c r="E292" t="n">
-        <v>50</v>
-      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr"/>
@@ -8281,15 +8099,9 @@
     <row r="293">
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr"/>
-      <c r="C293" t="n">
-        <v>180</v>
-      </c>
-      <c r="D293" t="n">
-        <v>181</v>
-      </c>
-      <c r="E293" t="n">
-        <v>161</v>
-      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr"/>
@@ -8305,15 +8117,9 @@
     <row r="294">
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr"/>
-      <c r="C294" t="n">
-        <v>54</v>
-      </c>
-      <c r="D294" t="n">
-        <v>182</v>
-      </c>
-      <c r="E294" t="n">
-        <v>184</v>
-      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr"/>
@@ -8329,15 +8135,9 @@
     <row r="295">
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr"/>
-      <c r="C295" t="n">
-        <v>182</v>
-      </c>
-      <c r="D295" t="n">
-        <v>18</v>
-      </c>
-      <c r="E295" t="n">
-        <v>183</v>
-      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr"/>
@@ -8353,15 +8153,9 @@
     <row r="296">
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr"/>
-      <c r="C296" t="n">
-        <v>184</v>
-      </c>
-      <c r="D296" t="n">
-        <v>183</v>
-      </c>
-      <c r="E296" t="n">
-        <v>55</v>
-      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
@@ -8377,15 +8171,9 @@
     <row r="297">
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr"/>
-      <c r="C297" t="n">
-        <v>182</v>
-      </c>
-      <c r="D297" t="n">
-        <v>183</v>
-      </c>
-      <c r="E297" t="n">
-        <v>184</v>
-      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr"/>
@@ -8401,15 +8189,9 @@
     <row r="298">
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr"/>
-      <c r="C298" t="n">
-        <v>50</v>
-      </c>
-      <c r="D298" t="n">
-        <v>185</v>
-      </c>
-      <c r="E298" t="n">
-        <v>164</v>
-      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
@@ -8425,15 +8207,9 @@
     <row r="299">
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr"/>
-      <c r="C299" t="n">
-        <v>185</v>
-      </c>
-      <c r="D299" t="n">
-        <v>55</v>
-      </c>
-      <c r="E299" t="n">
-        <v>186</v>
-      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr"/>
@@ -8449,15 +8225,9 @@
     <row r="300">
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr"/>
-      <c r="C300" t="n">
-        <v>164</v>
-      </c>
-      <c r="D300" t="n">
-        <v>186</v>
-      </c>
-      <c r="E300" t="n">
-        <v>1</v>
-      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr"/>
@@ -8473,15 +8243,9 @@
     <row r="301">
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr"/>
-      <c r="C301" t="n">
-        <v>185</v>
-      </c>
-      <c r="D301" t="n">
-        <v>186</v>
-      </c>
-      <c r="E301" t="n">
-        <v>164</v>
-      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
@@ -8497,15 +8261,9 @@
     <row r="302">
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr"/>
-      <c r="C302" t="n">
-        <v>54</v>
-      </c>
-      <c r="D302" t="n">
-        <v>184</v>
-      </c>
-      <c r="E302" t="n">
-        <v>181</v>
-      </c>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr"/>
@@ -8521,15 +8279,9 @@
     <row r="303">
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr"/>
-      <c r="C303" t="n">
-        <v>184</v>
-      </c>
-      <c r="D303" t="n">
-        <v>55</v>
-      </c>
-      <c r="E303" t="n">
-        <v>185</v>
-      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
@@ -8545,15 +8297,9 @@
     <row r="304">
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr"/>
-      <c r="C304" t="n">
-        <v>181</v>
-      </c>
-      <c r="D304" t="n">
-        <v>185</v>
-      </c>
-      <c r="E304" t="n">
-        <v>50</v>
-      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
@@ -8569,15 +8315,9 @@
     <row r="305">
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr"/>
-      <c r="C305" t="n">
-        <v>184</v>
-      </c>
-      <c r="D305" t="n">
-        <v>185</v>
-      </c>
-      <c r="E305" t="n">
-        <v>181</v>
-      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
@@ -8593,15 +8333,9 @@
     <row r="306">
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr"/>
-      <c r="C306" t="n">
-        <v>8</v>
-      </c>
-      <c r="D306" t="n">
-        <v>174</v>
-      </c>
-      <c r="E306" t="n">
-        <v>169</v>
-      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
@@ -8617,15 +8351,9 @@
     <row r="307">
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr"/>
-      <c r="C307" t="n">
-        <v>174</v>
-      </c>
-      <c r="D307" t="n">
-        <v>53</v>
-      </c>
-      <c r="E307" t="n">
-        <v>187</v>
-      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr"/>
@@ -8641,15 +8369,9 @@
     <row r="308">
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr"/>
-      <c r="C308" t="n">
-        <v>169</v>
-      </c>
-      <c r="D308" t="n">
-        <v>187</v>
-      </c>
-      <c r="E308" t="n">
-        <v>51</v>
-      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr"/>
@@ -8665,15 +8387,9 @@
     <row r="309">
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr"/>
-      <c r="C309" t="n">
-        <v>174</v>
-      </c>
-      <c r="D309" t="n">
-        <v>187</v>
-      </c>
-      <c r="E309" t="n">
-        <v>169</v>
-      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
@@ -8689,15 +8405,9 @@
     <row r="310">
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr"/>
-      <c r="C310" t="n">
-        <v>53</v>
-      </c>
-      <c r="D310" t="n">
-        <v>179</v>
-      </c>
-      <c r="E310" t="n">
-        <v>188</v>
-      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr"/>
@@ -8713,15 +8423,9 @@
     <row r="311">
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr"/>
-      <c r="C311" t="n">
-        <v>179</v>
-      </c>
-      <c r="D311" t="n">
-        <v>18</v>
-      </c>
-      <c r="E311" t="n">
-        <v>182</v>
-      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr"/>
@@ -8737,15 +8441,9 @@
     <row r="312">
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr"/>
-      <c r="C312" t="n">
-        <v>188</v>
-      </c>
-      <c r="D312" t="n">
-        <v>182</v>
-      </c>
-      <c r="E312" t="n">
-        <v>54</v>
-      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
@@ -8761,15 +8459,9 @@
     <row r="313">
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr"/>
-      <c r="C313" t="n">
-        <v>179</v>
-      </c>
-      <c r="D313" t="n">
-        <v>182</v>
-      </c>
-      <c r="E313" t="n">
-        <v>188</v>
-      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr"/>
@@ -8785,15 +8477,9 @@
     <row r="314">
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr"/>
-      <c r="C314" t="n">
-        <v>51</v>
-      </c>
-      <c r="D314" t="n">
-        <v>189</v>
-      </c>
-      <c r="E314" t="n">
-        <v>172</v>
-      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr"/>
@@ -8809,15 +8495,9 @@
     <row r="315">
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr"/>
-      <c r="C315" t="n">
-        <v>189</v>
-      </c>
-      <c r="D315" t="n">
-        <v>54</v>
-      </c>
-      <c r="E315" t="n">
-        <v>180</v>
-      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr"/>
@@ -8830,1194 +8510,6 @@
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr"/>
     </row>
-    <row r="316">
-      <c r="A316" t="inlineStr"/>
-      <c r="B316" t="inlineStr"/>
-      <c r="C316" t="n">
-        <v>172</v>
-      </c>
-      <c r="D316" t="n">
-        <v>180</v>
-      </c>
-      <c r="E316" t="n">
-        <v>17</v>
-      </c>
-      <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
-      <c r="J316" t="n">
-        <v>0</v>
-      </c>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr"/>
-      <c r="B317" t="inlineStr"/>
-      <c r="C317" t="n">
-        <v>189</v>
-      </c>
-      <c r="D317" t="n">
-        <v>180</v>
-      </c>
-      <c r="E317" t="n">
-        <v>172</v>
-      </c>
-      <c r="F317" t="inlineStr"/>
-      <c r="G317" t="inlineStr"/>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
-      <c r="J317" t="n">
-        <v>0</v>
-      </c>
-      <c r="K317" t="inlineStr"/>
-      <c r="L317" t="inlineStr"/>
-      <c r="M317" t="inlineStr"/>
-      <c r="N317" t="inlineStr"/>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr"/>
-      <c r="B318" t="inlineStr"/>
-      <c r="C318" t="n">
-        <v>53</v>
-      </c>
-      <c r="D318" t="n">
-        <v>188</v>
-      </c>
-      <c r="E318" t="n">
-        <v>187</v>
-      </c>
-      <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr"/>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
-      <c r="J318" t="n">
-        <v>0</v>
-      </c>
-      <c r="K318" t="inlineStr"/>
-      <c r="L318" t="inlineStr"/>
-      <c r="M318" t="inlineStr"/>
-      <c r="N318" t="inlineStr"/>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr"/>
-      <c r="B319" t="inlineStr"/>
-      <c r="C319" t="n">
-        <v>188</v>
-      </c>
-      <c r="D319" t="n">
-        <v>54</v>
-      </c>
-      <c r="E319" t="n">
-        <v>189</v>
-      </c>
-      <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr"/>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
-      <c r="J319" t="n">
-        <v>0</v>
-      </c>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
-      <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr"/>
-      <c r="B320" t="inlineStr"/>
-      <c r="C320" t="n">
-        <v>187</v>
-      </c>
-      <c r="D320" t="n">
-        <v>189</v>
-      </c>
-      <c r="E320" t="n">
-        <v>51</v>
-      </c>
-      <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
-      <c r="J320" t="n">
-        <v>0</v>
-      </c>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr"/>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr"/>
-      <c r="B321" t="inlineStr"/>
-      <c r="C321" t="n">
-        <v>188</v>
-      </c>
-      <c r="D321" t="n">
-        <v>189</v>
-      </c>
-      <c r="E321" t="n">
-        <v>187</v>
-      </c>
-      <c r="F321" t="inlineStr"/>
-      <c r="G321" t="inlineStr"/>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
-      <c r="J321" t="n">
-        <v>0</v>
-      </c>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-      <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr"/>
-      <c r="B322" t="inlineStr"/>
-      <c r="C322" t="inlineStr"/>
-      <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr"/>
-      <c r="J322" t="n">
-        <v>0</v>
-      </c>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
-      <c r="M322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr"/>
-      <c r="B323" t="inlineStr"/>
-      <c r="C323" t="inlineStr"/>
-      <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
-      <c r="G323" t="inlineStr"/>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
-      <c r="J323" t="n">
-        <v>0</v>
-      </c>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
-      <c r="M323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr"/>
-      <c r="B324" t="inlineStr"/>
-      <c r="C324" t="inlineStr"/>
-      <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
-      <c r="J324" t="n">
-        <v>0</v>
-      </c>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr"/>
-      <c r="B325" t="inlineStr"/>
-      <c r="C325" t="inlineStr"/>
-      <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
-      <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
-      <c r="J325" t="n">
-        <v>0</v>
-      </c>
-      <c r="K325" t="inlineStr"/>
-      <c r="L325" t="inlineStr"/>
-      <c r="M325" t="inlineStr"/>
-      <c r="N325" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr"/>
-      <c r="B326" t="inlineStr"/>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
-      <c r="G326" t="inlineStr"/>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
-      <c r="J326" t="n">
-        <v>0</v>
-      </c>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
-      <c r="M326" t="inlineStr"/>
-      <c r="N326" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr"/>
-      <c r="B327" t="inlineStr"/>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
-      <c r="J327" t="n">
-        <v>0</v>
-      </c>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
-      <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr"/>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr"/>
-      <c r="B328" t="inlineStr"/>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
-      <c r="J328" t="n">
-        <v>0</v>
-      </c>
-      <c r="K328" t="inlineStr"/>
-      <c r="L328" t="inlineStr"/>
-      <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr"/>
-      <c r="B329" t="inlineStr"/>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
-      <c r="G329" t="inlineStr"/>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr"/>
-      <c r="J329" t="n">
-        <v>0</v>
-      </c>
-      <c r="K329" t="inlineStr"/>
-      <c r="L329" t="inlineStr"/>
-      <c r="M329" t="inlineStr"/>
-      <c r="N329" t="inlineStr"/>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr"/>
-      <c r="B330" t="inlineStr"/>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
-      <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
-      <c r="J330" t="n">
-        <v>0</v>
-      </c>
-      <c r="K330" t="inlineStr"/>
-      <c r="L330" t="inlineStr"/>
-      <c r="M330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr"/>
-      <c r="B331" t="inlineStr"/>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
-      <c r="G331" t="inlineStr"/>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr"/>
-      <c r="J331" t="n">
-        <v>0</v>
-      </c>
-      <c r="K331" t="inlineStr"/>
-      <c r="L331" t="inlineStr"/>
-      <c r="M331" t="inlineStr"/>
-      <c r="N331" t="inlineStr"/>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr"/>
-      <c r="B332" t="inlineStr"/>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
-      <c r="H332" t="inlineStr"/>
-      <c r="I332" t="inlineStr"/>
-      <c r="J332" t="n">
-        <v>0</v>
-      </c>
-      <c r="K332" t="inlineStr"/>
-      <c r="L332" t="inlineStr"/>
-      <c r="M332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr"/>
-      <c r="B333" t="inlineStr"/>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
-      <c r="G333" t="inlineStr"/>
-      <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr"/>
-      <c r="J333" t="n">
-        <v>0</v>
-      </c>
-      <c r="K333" t="inlineStr"/>
-      <c r="L333" t="inlineStr"/>
-      <c r="M333" t="inlineStr"/>
-      <c r="N333" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr"/>
-      <c r="B334" t="inlineStr"/>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr"/>
-      <c r="J334" t="n">
-        <v>0</v>
-      </c>
-      <c r="K334" t="inlineStr"/>
-      <c r="L334" t="inlineStr"/>
-      <c r="M334" t="inlineStr"/>
-      <c r="N334" t="inlineStr"/>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr"/>
-      <c r="B335" t="inlineStr"/>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
-      <c r="J335" t="n">
-        <v>0</v>
-      </c>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
-      <c r="M335" t="inlineStr"/>
-      <c r="N335" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr"/>
-      <c r="B336" t="inlineStr"/>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr"/>
-      <c r="I336" t="inlineStr"/>
-      <c r="J336" t="n">
-        <v>0</v>
-      </c>
-      <c r="K336" t="inlineStr"/>
-      <c r="L336" t="inlineStr"/>
-      <c r="M336" t="inlineStr"/>
-      <c r="N336" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr"/>
-      <c r="B337" t="inlineStr"/>
-      <c r="C337" t="inlineStr"/>
-      <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr"/>
-      <c r="J337" t="n">
-        <v>0</v>
-      </c>
-      <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
-      <c r="M337" t="inlineStr"/>
-      <c r="N337" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr"/>
-      <c r="B338" t="inlineStr"/>
-      <c r="C338" t="inlineStr"/>
-      <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
-      <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr"/>
-      <c r="I338" t="inlineStr"/>
-      <c r="J338" t="n">
-        <v>0</v>
-      </c>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
-      <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr"/>
-      <c r="B339" t="inlineStr"/>
-      <c r="C339" t="inlineStr"/>
-      <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
-      <c r="G339" t="inlineStr"/>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr"/>
-      <c r="J339" t="n">
-        <v>0</v>
-      </c>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
-      <c r="M339" t="inlineStr"/>
-      <c r="N339" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr"/>
-      <c r="B340" t="inlineStr"/>
-      <c r="C340" t="inlineStr"/>
-      <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr"/>
-      <c r="J340" t="n">
-        <v>0</v>
-      </c>
-      <c r="K340" t="inlineStr"/>
-      <c r="L340" t="inlineStr"/>
-      <c r="M340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr"/>
-      <c r="B341" t="inlineStr"/>
-      <c r="C341" t="inlineStr"/>
-      <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
-      <c r="G341" t="inlineStr"/>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr"/>
-      <c r="J341" t="n">
-        <v>0</v>
-      </c>
-      <c r="K341" t="inlineStr"/>
-      <c r="L341" t="inlineStr"/>
-      <c r="M341" t="inlineStr"/>
-      <c r="N341" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr"/>
-      <c r="B342" t="inlineStr"/>
-      <c r="C342" t="inlineStr"/>
-      <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr"/>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr"/>
-      <c r="J342" t="n">
-        <v>0</v>
-      </c>
-      <c r="K342" t="inlineStr"/>
-      <c r="L342" t="inlineStr"/>
-      <c r="M342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr"/>
-      <c r="B343" t="inlineStr"/>
-      <c r="C343" t="inlineStr"/>
-      <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
-      <c r="G343" t="inlineStr"/>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr"/>
-      <c r="J343" t="n">
-        <v>0</v>
-      </c>
-      <c r="K343" t="inlineStr"/>
-      <c r="L343" t="inlineStr"/>
-      <c r="M343" t="inlineStr"/>
-      <c r="N343" t="inlineStr"/>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr"/>
-      <c r="B344" t="inlineStr"/>
-      <c r="C344" t="inlineStr"/>
-      <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr"/>
-      <c r="J344" t="n">
-        <v>0</v>
-      </c>
-      <c r="K344" t="inlineStr"/>
-      <c r="L344" t="inlineStr"/>
-      <c r="M344" t="inlineStr"/>
-      <c r="N344" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr"/>
-      <c r="B345" t="inlineStr"/>
-      <c r="C345" t="inlineStr"/>
-      <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr"/>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr"/>
-      <c r="J345" t="n">
-        <v>0</v>
-      </c>
-      <c r="K345" t="inlineStr"/>
-      <c r="L345" t="inlineStr"/>
-      <c r="M345" t="inlineStr"/>
-      <c r="N345" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr"/>
-      <c r="B346" t="inlineStr"/>
-      <c r="C346" t="inlineStr"/>
-      <c r="D346" t="inlineStr"/>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
-      <c r="G346" t="inlineStr"/>
-      <c r="H346" t="inlineStr"/>
-      <c r="I346" t="inlineStr"/>
-      <c r="J346" t="n">
-        <v>0</v>
-      </c>
-      <c r="K346" t="inlineStr"/>
-      <c r="L346" t="inlineStr"/>
-      <c r="M346" t="inlineStr"/>
-      <c r="N346" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr"/>
-      <c r="B347" t="inlineStr"/>
-      <c r="C347" t="inlineStr"/>
-      <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
-      <c r="G347" t="inlineStr"/>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr"/>
-      <c r="J347" t="n">
-        <v>0</v>
-      </c>
-      <c r="K347" t="inlineStr"/>
-      <c r="L347" t="inlineStr"/>
-      <c r="M347" t="inlineStr"/>
-      <c r="N347" t="inlineStr"/>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr"/>
-      <c r="B348" t="inlineStr"/>
-      <c r="C348" t="inlineStr"/>
-      <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
-      <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr"/>
-      <c r="J348" t="n">
-        <v>0</v>
-      </c>
-      <c r="K348" t="inlineStr"/>
-      <c r="L348" t="inlineStr"/>
-      <c r="M348" t="inlineStr"/>
-      <c r="N348" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr"/>
-      <c r="B349" t="inlineStr"/>
-      <c r="C349" t="inlineStr"/>
-      <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr"/>
-      <c r="H349" t="inlineStr"/>
-      <c r="I349" t="inlineStr"/>
-      <c r="J349" t="n">
-        <v>0</v>
-      </c>
-      <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr"/>
-      <c r="M349" t="inlineStr"/>
-      <c r="N349" t="inlineStr"/>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr"/>
-      <c r="B350" t="inlineStr"/>
-      <c r="C350" t="inlineStr"/>
-      <c r="D350" t="inlineStr"/>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
-      <c r="G350" t="inlineStr"/>
-      <c r="H350" t="inlineStr"/>
-      <c r="I350" t="inlineStr"/>
-      <c r="J350" t="n">
-        <v>0</v>
-      </c>
-      <c r="K350" t="inlineStr"/>
-      <c r="L350" t="inlineStr"/>
-      <c r="M350" t="inlineStr"/>
-      <c r="N350" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr"/>
-      <c r="B351" t="inlineStr"/>
-      <c r="C351" t="inlineStr"/>
-      <c r="D351" t="inlineStr"/>
-      <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
-      <c r="G351" t="inlineStr"/>
-      <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr"/>
-      <c r="J351" t="n">
-        <v>0</v>
-      </c>
-      <c r="K351" t="inlineStr"/>
-      <c r="L351" t="inlineStr"/>
-      <c r="M351" t="inlineStr"/>
-      <c r="N351" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr"/>
-      <c r="B352" t="inlineStr"/>
-      <c r="C352" t="inlineStr"/>
-      <c r="D352" t="inlineStr"/>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
-      <c r="J352" t="n">
-        <v>0</v>
-      </c>
-      <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
-      <c r="M352" t="inlineStr"/>
-      <c r="N352" t="inlineStr"/>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr"/>
-      <c r="B353" t="inlineStr"/>
-      <c r="C353" t="inlineStr"/>
-      <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
-      <c r="H353" t="inlineStr"/>
-      <c r="I353" t="inlineStr"/>
-      <c r="J353" t="n">
-        <v>0</v>
-      </c>
-      <c r="K353" t="inlineStr"/>
-      <c r="L353" t="inlineStr"/>
-      <c r="M353" t="inlineStr"/>
-      <c r="N353" t="inlineStr"/>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr"/>
-      <c r="B354" t="inlineStr"/>
-      <c r="C354" t="inlineStr"/>
-      <c r="D354" t="inlineStr"/>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
-      <c r="G354" t="inlineStr"/>
-      <c r="H354" t="inlineStr"/>
-      <c r="I354" t="inlineStr"/>
-      <c r="J354" t="n">
-        <v>0</v>
-      </c>
-      <c r="K354" t="inlineStr"/>
-      <c r="L354" t="inlineStr"/>
-      <c r="M354" t="inlineStr"/>
-      <c r="N354" t="inlineStr"/>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr"/>
-      <c r="B355" t="inlineStr"/>
-      <c r="C355" t="inlineStr"/>
-      <c r="D355" t="inlineStr"/>
-      <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
-      <c r="G355" t="inlineStr"/>
-      <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
-      <c r="J355" t="n">
-        <v>0</v>
-      </c>
-      <c r="K355" t="inlineStr"/>
-      <c r="L355" t="inlineStr"/>
-      <c r="M355" t="inlineStr"/>
-      <c r="N355" t="inlineStr"/>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr"/>
-      <c r="B356" t="inlineStr"/>
-      <c r="C356" t="inlineStr"/>
-      <c r="D356" t="inlineStr"/>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
-      <c r="J356" t="n">
-        <v>0</v>
-      </c>
-      <c r="K356" t="inlineStr"/>
-      <c r="L356" t="inlineStr"/>
-      <c r="M356" t="inlineStr"/>
-      <c r="N356" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr"/>
-      <c r="B357" t="inlineStr"/>
-      <c r="C357" t="inlineStr"/>
-      <c r="D357" t="inlineStr"/>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr"/>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
-      <c r="J357" t="n">
-        <v>0</v>
-      </c>
-      <c r="K357" t="inlineStr"/>
-      <c r="L357" t="inlineStr"/>
-      <c r="M357" t="inlineStr"/>
-      <c r="N357" t="inlineStr"/>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr"/>
-      <c r="B358" t="inlineStr"/>
-      <c r="C358" t="inlineStr"/>
-      <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr"/>
-      <c r="H358" t="inlineStr"/>
-      <c r="I358" t="inlineStr"/>
-      <c r="J358" t="n">
-        <v>0</v>
-      </c>
-      <c r="K358" t="inlineStr"/>
-      <c r="L358" t="inlineStr"/>
-      <c r="M358" t="inlineStr"/>
-      <c r="N358" t="inlineStr"/>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr"/>
-      <c r="B359" t="inlineStr"/>
-      <c r="C359" t="inlineStr"/>
-      <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
-      <c r="G359" t="inlineStr"/>
-      <c r="H359" t="inlineStr"/>
-      <c r="I359" t="inlineStr"/>
-      <c r="J359" t="n">
-        <v>0</v>
-      </c>
-      <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
-      <c r="M359" t="inlineStr"/>
-      <c r="N359" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr"/>
-      <c r="B360" t="inlineStr"/>
-      <c r="C360" t="inlineStr"/>
-      <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
-      <c r="G360" t="inlineStr"/>
-      <c r="H360" t="inlineStr"/>
-      <c r="I360" t="inlineStr"/>
-      <c r="J360" t="n">
-        <v>0</v>
-      </c>
-      <c r="K360" t="inlineStr"/>
-      <c r="L360" t="inlineStr"/>
-      <c r="M360" t="inlineStr"/>
-      <c r="N360" t="inlineStr"/>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr"/>
-      <c r="B361" t="inlineStr"/>
-      <c r="C361" t="inlineStr"/>
-      <c r="D361" t="inlineStr"/>
-      <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
-      <c r="G361" t="inlineStr"/>
-      <c r="H361" t="inlineStr"/>
-      <c r="I361" t="inlineStr"/>
-      <c r="J361" t="n">
-        <v>0</v>
-      </c>
-      <c r="K361" t="inlineStr"/>
-      <c r="L361" t="inlineStr"/>
-      <c r="M361" t="inlineStr"/>
-      <c r="N361" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr"/>
-      <c r="B362" t="inlineStr"/>
-      <c r="C362" t="inlineStr"/>
-      <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
-      <c r="H362" t="inlineStr"/>
-      <c r="I362" t="inlineStr"/>
-      <c r="J362" t="n">
-        <v>0</v>
-      </c>
-      <c r="K362" t="inlineStr"/>
-      <c r="L362" t="inlineStr"/>
-      <c r="M362" t="inlineStr"/>
-      <c r="N362" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr"/>
-      <c r="B363" t="inlineStr"/>
-      <c r="C363" t="inlineStr"/>
-      <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
-      <c r="J363" t="n">
-        <v>0</v>
-      </c>
-      <c r="K363" t="inlineStr"/>
-      <c r="L363" t="inlineStr"/>
-      <c r="M363" t="inlineStr"/>
-      <c r="N363" t="inlineStr"/>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr"/>
-      <c r="B364" t="inlineStr"/>
-      <c r="C364" t="inlineStr"/>
-      <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
-      <c r="G364" t="inlineStr"/>
-      <c r="H364" t="inlineStr"/>
-      <c r="I364" t="inlineStr"/>
-      <c r="J364" t="n">
-        <v>0</v>
-      </c>
-      <c r="K364" t="inlineStr"/>
-      <c r="L364" t="inlineStr"/>
-      <c r="M364" t="inlineStr"/>
-      <c r="N364" t="inlineStr"/>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr"/>
-      <c r="B365" t="inlineStr"/>
-      <c r="C365" t="inlineStr"/>
-      <c r="D365" t="inlineStr"/>
-      <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
-      <c r="J365" t="n">
-        <v>0</v>
-      </c>
-      <c r="K365" t="inlineStr"/>
-      <c r="L365" t="inlineStr"/>
-      <c r="M365" t="inlineStr"/>
-      <c r="N365" t="inlineStr"/>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr"/>
-      <c r="B366" t="inlineStr"/>
-      <c r="C366" t="inlineStr"/>
-      <c r="D366" t="inlineStr"/>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
-      <c r="H366" t="inlineStr"/>
-      <c r="I366" t="inlineStr"/>
-      <c r="J366" t="n">
-        <v>0</v>
-      </c>
-      <c r="K366" t="inlineStr"/>
-      <c r="L366" t="inlineStr"/>
-      <c r="M366" t="inlineStr"/>
-      <c r="N366" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr"/>
-      <c r="B367" t="inlineStr"/>
-      <c r="C367" t="inlineStr"/>
-      <c r="D367" t="inlineStr"/>
-      <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
-      <c r="G367" t="inlineStr"/>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr"/>
-      <c r="J367" t="n">
-        <v>0</v>
-      </c>
-      <c r="K367" t="inlineStr"/>
-      <c r="L367" t="inlineStr"/>
-      <c r="M367" t="inlineStr"/>
-      <c r="N367" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr"/>
-      <c r="B368" t="inlineStr"/>
-      <c r="C368" t="inlineStr"/>
-      <c r="D368" t="inlineStr"/>
-      <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr"/>
-      <c r="J368" t="n">
-        <v>0</v>
-      </c>
-      <c r="K368" t="inlineStr"/>
-      <c r="L368" t="inlineStr"/>
-      <c r="M368" t="inlineStr"/>
-      <c r="N368" t="inlineStr"/>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr"/>
-      <c r="B369" t="inlineStr"/>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" t="inlineStr"/>
-      <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
-      <c r="G369" t="inlineStr"/>
-      <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr"/>
-      <c r="J369" t="n">
-        <v>0</v>
-      </c>
-      <c r="K369" t="inlineStr"/>
-      <c r="L369" t="inlineStr"/>
-      <c r="M369" t="inlineStr"/>
-      <c r="N369" t="inlineStr"/>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr"/>
-      <c r="B370" t="inlineStr"/>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
-      <c r="G370" t="inlineStr"/>
-      <c r="H370" t="inlineStr"/>
-      <c r="I370" t="inlineStr"/>
-      <c r="J370" t="n">
-        <v>0</v>
-      </c>
-      <c r="K370" t="inlineStr"/>
-      <c r="L370" t="inlineStr"/>
-      <c r="M370" t="inlineStr"/>
-      <c r="N370" t="inlineStr"/>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr"/>
-      <c r="B371" t="inlineStr"/>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
-      <c r="G371" t="inlineStr"/>
-      <c r="H371" t="inlineStr"/>
-      <c r="I371" t="inlineStr"/>
-      <c r="J371" t="n">
-        <v>0</v>
-      </c>
-      <c r="K371" t="inlineStr"/>
-      <c r="L371" t="inlineStr"/>
-      <c r="M371" t="inlineStr"/>
-      <c r="N371" t="inlineStr"/>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr"/>
-      <c r="B372" t="inlineStr"/>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
-      <c r="J372" t="n">
-        <v>0</v>
-      </c>
-      <c r="K372" t="inlineStr"/>
-      <c r="L372" t="inlineStr"/>
-      <c r="M372" t="inlineStr"/>
-      <c r="N372" t="inlineStr"/>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr"/>
-      <c r="B373" t="inlineStr"/>
-      <c r="C373" t="inlineStr"/>
-      <c r="D373" t="inlineStr"/>
-      <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
-      <c r="H373" t="inlineStr"/>
-      <c r="I373" t="inlineStr"/>
-      <c r="J373" t="n">
-        <v>0</v>
-      </c>
-      <c r="K373" t="inlineStr"/>
-      <c r="L373" t="inlineStr"/>
-      <c r="M373" t="inlineStr"/>
-      <c r="N373" t="inlineStr"/>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr"/>
-      <c r="B374" t="inlineStr"/>
-      <c r="C374" t="inlineStr"/>
-      <c r="D374" t="inlineStr"/>
-      <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
-      <c r="G374" t="inlineStr"/>
-      <c r="H374" t="inlineStr"/>
-      <c r="I374" t="inlineStr"/>
-      <c r="J374" t="n">
-        <v>0</v>
-      </c>
-      <c r="K374" t="inlineStr"/>
-      <c r="L374" t="inlineStr"/>
-      <c r="M374" t="inlineStr"/>
-      <c r="N374" t="inlineStr"/>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr"/>
-      <c r="B375" t="inlineStr"/>
-      <c r="C375" t="inlineStr"/>
-      <c r="D375" t="inlineStr"/>
-      <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
-      <c r="H375" t="inlineStr"/>
-      <c r="I375" t="inlineStr"/>
-      <c r="J375" t="n">
-        <v>0</v>
-      </c>
-      <c r="K375" t="inlineStr"/>
-      <c r="L375" t="inlineStr"/>
-      <c r="M375" t="inlineStr"/>
-      <c r="N375" t="inlineStr"/>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr"/>
-      <c r="B376" t="inlineStr"/>
-      <c r="C376" t="inlineStr"/>
-      <c r="D376" t="inlineStr"/>
-      <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
-      <c r="J376" t="n">
-        <v>0</v>
-      </c>
-      <c r="K376" t="inlineStr"/>
-      <c r="L376" t="inlineStr"/>
-      <c r="M376" t="inlineStr"/>
-      <c r="N376" t="inlineStr"/>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr"/>
-      <c r="B377" t="inlineStr"/>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr"/>
-      <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
-      <c r="H377" t="inlineStr"/>
-      <c r="I377" t="inlineStr"/>
-      <c r="J377" t="n">
-        <v>0</v>
-      </c>
-      <c r="K377" t="inlineStr"/>
-      <c r="L377" t="inlineStr"/>
-      <c r="M377" t="inlineStr"/>
-      <c r="N377" t="inlineStr"/>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr"/>
-      <c r="B378" t="inlineStr"/>
-      <c r="C378" t="inlineStr"/>
-      <c r="D378" t="inlineStr"/>
-      <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr"/>
-      <c r="H378" t="inlineStr"/>
-      <c r="I378" t="inlineStr"/>
-      <c r="J378" t="n">
-        <v>0</v>
-      </c>
-      <c r="K378" t="inlineStr"/>
-      <c r="L378" t="inlineStr"/>
-      <c r="M378" t="inlineStr"/>
-      <c r="N378" t="inlineStr"/>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr"/>
-      <c r="B379" t="inlineStr"/>
-      <c r="C379" t="inlineStr"/>
-      <c r="D379" t="inlineStr"/>
-      <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
-      <c r="H379" t="inlineStr"/>
-      <c r="I379" t="inlineStr"/>
-      <c r="J379" t="n">
-        <v>0</v>
-      </c>
-      <c r="K379" t="inlineStr"/>
-      <c r="L379" t="inlineStr"/>
-      <c r="M379" t="inlineStr"/>
-      <c r="N379" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_structure.xlsx
+++ b/data_structure.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N315"/>
+  <dimension ref="A1:N379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,28 +490,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="B2" t="n">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.0007800000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="H2" t="n">
-        <v>1000000000</v>
+        <v>615000000000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -520,33 +520,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>0.225</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -554,7 +556,9 @@
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
     </row>
@@ -562,27 +566,29 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>0.011</v>
+        <v>0.0005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>9</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
     </row>
@@ -590,13 +596,13 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
         <v>0.012</v>
@@ -610,7 +616,9 @@
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>10</v>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
     </row>
@@ -618,19 +626,19 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>0.017</v>
+        <v>0.0112</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -638,7 +646,9 @@
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>27</v>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -646,27 +656,29 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>28</v>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
     </row>
@@ -674,19 +686,19 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
         <v>0.006</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -694,7 +706,9 @@
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>77</v>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
     </row>
@@ -702,19 +716,19 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005</v>
+        <v>0.0006400000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -722,7 +736,9 @@
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>78</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
     </row>
@@ -730,27 +746,29 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.00025</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>83</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -758,19 +776,19 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002130466767345598</v>
+        <v>0.00039</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004682019885470806</v>
+        <v>-0.002</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -778,7 +796,9 @@
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>84</v>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -786,19 +806,19 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004631606966252106</v>
+        <v>0.00325</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0006671154771972934</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -806,7 +826,9 @@
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>249</v>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
     </row>
@@ -814,27 +836,29 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01234919867331015</v>
+        <v>0.00339</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003618548104620701</v>
+        <v>-0.002</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>250</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
     </row>
@@ -842,19 +866,19 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006153120665824914</v>
+        <v>0.0086</v>
       </c>
       <c r="G14" t="n">
-        <v>0.007947335050264554</v>
+        <v>-0.002</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -862,7 +886,9 @@
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>255</v>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
     </row>
@@ -870,19 +896,19 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001065233383672799</v>
+        <v>0.0116</v>
       </c>
       <c r="G15" t="n">
-        <v>0.007341009942735403</v>
+        <v>-0.002</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -890,7 +916,9 @@
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>256</v>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
     </row>
@@ -898,19 +926,19 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -918,7 +946,9 @@
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>267</v>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
     </row>
@@ -926,19 +956,19 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001065233383672799</v>
+        <v>0.006</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002341009942735403</v>
+        <v>-0.002</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -946,7 +976,9 @@
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>268</v>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
     </row>
@@ -954,19 +986,19 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008315803483126053</v>
+        <v>0.00339</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0003335577385986467</v>
+        <v>-0.004</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -974,7 +1006,9 @@
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>273</v>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
     </row>
@@ -982,19 +1016,19 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>0.005815803483126053</v>
+        <v>0.0086</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.002833557738598647</v>
+        <v>-0.004</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1002,7 +1036,9 @@
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>274</v>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
     </row>
@@ -1010,19 +1046,19 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0095</v>
+        <v>0.0007100000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0025</v>
+        <v>-0.003</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1038,19 +1074,19 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E21" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
-        <v>0.002315803483126053</v>
+        <v>0.000515</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003335577385986467</v>
+        <v>-0.002</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1066,19 +1102,19 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E22" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0035</v>
+        <v>0.000585</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0025</v>
+        <v>-0.003</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1094,19 +1130,19 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F23" t="n">
-        <v>0.008576560332912457</v>
+        <v>0.00057</v>
       </c>
       <c r="G23" t="n">
-        <v>0.008973667525132277</v>
+        <v>-0.001</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1122,19 +1158,19 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D24" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0055</v>
+        <v>0.000375</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1150,19 +1186,19 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E25" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F25" t="n">
-        <v>0.003076560332912457</v>
+        <v>0.000445</v>
       </c>
       <c r="G25" t="n">
-        <v>0.008973667525132277</v>
+        <v>-0.001</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1178,19 +1214,19 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F26" t="n">
-        <v>0.007576560332912458</v>
+        <v>0.00032</v>
       </c>
       <c r="G26" t="n">
-        <v>0.006473667525132277</v>
+        <v>-0.001</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1206,19 +1242,19 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01</v>
+        <v>0.000125</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0075</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1234,19 +1270,19 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
-        <v>0.004141793716585256</v>
+        <v>0.000195</v>
       </c>
       <c r="G28" t="n">
-        <v>0.00631467746786768</v>
+        <v>-0.001</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1262,19 +1298,19 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E29" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01217459933665507</v>
+        <v>0.004625000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00180927405231035</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1290,19 +1326,19 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E30" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0145</v>
+        <v>0.00332</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0035</v>
+        <v>-0.001</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1318,19 +1354,19 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E31" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01467459933665507</v>
+        <v>0.004695</v>
       </c>
       <c r="G31" t="n">
-        <v>0.005309274052310351</v>
+        <v>-0.001</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1346,19 +1382,19 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E32" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01067459933665507</v>
+        <v>0.001875</v>
       </c>
       <c r="G32" t="n">
-        <v>0.004309274052310351</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1374,19 +1410,19 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E33" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0105</v>
+        <v>0.001945</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0025</v>
+        <v>-0.001</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1402,19 +1438,19 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01167459933665507</v>
+        <v>0.002015</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00680927405231035</v>
+        <v>-0.002</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1430,19 +1466,19 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D35" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E35" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F35" t="n">
-        <v>0.014</v>
+        <v>0.002085</v>
       </c>
       <c r="G35" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.003</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1458,19 +1494,19 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D36" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E36" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F36" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0073</v>
       </c>
       <c r="G36" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1486,19 +1522,19 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D37" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E37" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F37" t="n">
-        <v>0.007000000000000001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0035</v>
+        <v>-0.001</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1514,19 +1550,19 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D38" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F38" t="n">
-        <v>0.004815803483126053</v>
+        <v>0.007500000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0006664422614013533</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1542,19 +1578,19 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F39" t="n">
-        <v>0.003565233383672799</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>0.003341009942735403</v>
+        <v>-0.003</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1570,19 +1606,19 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D40" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E40" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0025</v>
+        <v>0.0114</v>
       </c>
       <c r="G40" t="n">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1598,19 +1634,19 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D41" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F41" t="n">
-        <v>0.006076560332912457</v>
+        <v>0.0101</v>
       </c>
       <c r="G41" t="n">
-        <v>0.006973667525132277</v>
+        <v>-0.002</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1626,19 +1662,19 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D42" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E42" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F42" t="n">
-        <v>0.004065233383672799</v>
+        <v>0.0103</v>
       </c>
       <c r="G42" t="n">
-        <v>0.005341009942735403</v>
+        <v>-0.001</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1654,19 +1690,19 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E43" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0055</v>
+        <v>0.0118</v>
       </c>
       <c r="G43" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1682,19 +1718,19 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D44" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.007500000000000001</v>
+        <v>0.0105</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1710,19 +1746,19 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D45" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E45" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F45" t="n">
-        <v>0.001597850075509198</v>
+        <v>0.006</v>
       </c>
       <c r="G45" t="n">
-        <v>0.006011514914103105</v>
+        <v>-0.003</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1738,19 +1774,19 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D46" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F46" t="n">
-        <v>0.001065233383672799</v>
+        <v>0.004695</v>
       </c>
       <c r="G46" t="n">
-        <v>0.004841009942735403</v>
+        <v>-0.003</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1766,19 +1802,19 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E47" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F47" t="n">
-        <v>0.001597850075509198</v>
+        <v>0.004695</v>
       </c>
       <c r="G47" t="n">
-        <v>0.003511514914103104</v>
+        <v>-0.004</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1794,19 +1830,19 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D48" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E48" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0005326166918363994</v>
+        <v>0.006</v>
       </c>
       <c r="G48" t="n">
-        <v>0.008670504971367701</v>
+        <v>-0.001</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1822,19 +1858,19 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D49" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E49" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.004695</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0075</v>
+        <v>-0.002</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1850,19 +1886,19 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E50" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0005326166918363994</v>
+        <v>0.00339</v>
       </c>
       <c r="G50" t="n">
-        <v>0.006170504971367702</v>
+        <v>-0.003</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -1878,19 +1914,19 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D51" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E51" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0005326166918363994</v>
+        <v>0.002085</v>
       </c>
       <c r="G51" t="n">
-        <v>0.003670504971367701</v>
+        <v>-0.004</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -1906,19 +1942,19 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E52" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>0.0073</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0025</v>
+        <v>-0.004</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1934,19 +1970,19 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D53" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E53" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0005326166918363994</v>
+        <v>0.0073</v>
       </c>
       <c r="G53" t="n">
-        <v>0.001170504971367701</v>
+        <v>-0.003</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -1962,19 +1998,19 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D54" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E54" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01015790174156303</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.0001667788692993234</v>
+        <v>-0.004</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -1990,19 +2026,19 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F55" t="n">
-        <v>0.008907901741563026</v>
+        <v>0.0086</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001416778869299323</v>
+        <v>-0.003</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -2018,19 +2054,19 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D56" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
-        <v>0.01075</v>
+        <v>0.0073</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.00125</v>
+        <v>-0.002</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -2046,19 +2082,19 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D57" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E57" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F57" t="n">
-        <v>0.00647370522468908</v>
+        <v>0.0007450000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.0005003366078979701</v>
+        <v>-0.0035</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -2074,19 +2110,19 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D58" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E58" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F58" t="n">
-        <v>0.005223705224689079</v>
+        <v>0.0006475000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.00175033660789797</v>
+        <v>-0.003</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -2102,19 +2138,19 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D59" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E59" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F59" t="n">
-        <v>0.007065803483126053</v>
+        <v>0.0006825000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.001583557738598647</v>
+        <v>-0.0035</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -2130,19 +2166,19 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D60" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>0.007657901741563026</v>
+        <v>0.000675</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.002666778869299323</v>
+        <v>-0.0025</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2158,19 +2194,19 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D61" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E61" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F61" t="n">
-        <v>0.006407901741563027</v>
+        <v>0.0005775000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.003916778869299324</v>
+        <v>-0.002</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2186,19 +2222,19 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D62" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E62" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F62" t="n">
-        <v>0.00825</v>
+        <v>0.0006125000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.00375</v>
+        <v>-0.0025</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2214,19 +2250,19 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D63" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E63" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F63" t="n">
-        <v>0.004657901741563026</v>
+        <v>0.00055</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.002666778869299323</v>
+        <v>-0.0025</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -2242,19 +2278,19 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D64" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00525</v>
+        <v>0.0004525</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.00375</v>
+        <v>-0.002</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -2270,19 +2306,19 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D65" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E65" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F65" t="n">
-        <v>0.00347370522468908</v>
+        <v>0.0004875</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.0005003366078979701</v>
+        <v>-0.0025</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -2298,19 +2334,19 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E66" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F66" t="n">
-        <v>0.004065803483126053</v>
+        <v>0.0006050000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.001583557738598647</v>
+        <v>-0.0015</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -2326,19 +2362,19 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D67" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E67" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F67" t="n">
-        <v>0.002907901741563026</v>
+        <v>0.0005075</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.001416778869299323</v>
+        <v>-0.001</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -2354,19 +2390,19 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D68" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E68" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F68" t="n">
-        <v>0.001157901741563027</v>
+        <v>0.0005425</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.0001667788692993234</v>
+        <v>-0.0015</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -2382,19 +2418,19 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D69" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E69" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F69" t="n">
-        <v>0.00175</v>
+        <v>0.000535</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.00125</v>
+        <v>-0.0005</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -2410,19 +2446,19 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D70" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E70" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F70" t="n">
-        <v>0.007364840499368685</v>
+        <v>0.0004375</v>
       </c>
       <c r="G70" t="n">
-        <v>0.008460501287698416</v>
+        <v>0</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -2438,19 +2474,19 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D71" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E71" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F71" t="n">
-        <v>0.005826560332912457</v>
+        <v>0.0004725</v>
       </c>
       <c r="G71" t="n">
-        <v>0.008973667525132277</v>
+        <v>-0.0005</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -2466,19 +2502,19 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D72" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E72" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F72" t="n">
-        <v>0.004614840499368686</v>
+        <v>0.00041</v>
       </c>
       <c r="G72" t="n">
-        <v>0.008460501287698416</v>
+        <v>-0.0005</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -2494,19 +2530,19 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D73" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E73" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F73" t="n">
-        <v>0.009788280166456227</v>
+        <v>0.0003125</v>
       </c>
       <c r="G73" t="n">
-        <v>0.009486833762566139</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -2522,19 +2558,19 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D74" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E74" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F74" t="n">
-        <v>0.00825</v>
+        <v>0.0003475</v>
       </c>
       <c r="G74" t="n">
-        <v>0.01</v>
+        <v>-0.0005</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -2550,19 +2586,19 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D75" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E75" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F75" t="n">
-        <v>0.007038280166456228</v>
+        <v>0.0003550000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>0.009486833762566139</v>
+        <v>-0.0015</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -2578,19 +2614,19 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D76" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E76" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F76" t="n">
-        <v>0.004288280166456228</v>
+        <v>0.0002575</v>
       </c>
       <c r="G76" t="n">
-        <v>0.009486833762566139</v>
+        <v>-0.001</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -2606,19 +2642,19 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D77" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E77" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F77" t="n">
-        <v>0.00275</v>
+        <v>0.0002925</v>
       </c>
       <c r="G77" t="n">
-        <v>0.01</v>
+        <v>-0.0015</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -2634,19 +2670,19 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D78" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E78" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F78" t="n">
-        <v>0.001538280166456229</v>
+        <v>0.000285</v>
       </c>
       <c r="G78" t="n">
-        <v>0.009486833762566139</v>
+        <v>-0.0005</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -2662,19 +2698,19 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D79" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E79" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F79" t="n">
-        <v>0.009288280166456228</v>
+        <v>0.0001875</v>
       </c>
       <c r="G79" t="n">
-        <v>0.008236833762566138</v>
+        <v>0</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -2690,19 +2726,19 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D80" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E80" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0105</v>
+        <v>0.0002225</v>
       </c>
       <c r="G80" t="n">
-        <v>0.008750000000000001</v>
+        <v>-0.0005</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -2718,19 +2754,19 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D81" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E81" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F81" t="n">
-        <v>0.006864840499368686</v>
+        <v>0.00016</v>
       </c>
       <c r="G81" t="n">
-        <v>0.007210501287698416</v>
+        <v>-0.0005</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -2746,19 +2782,19 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D82" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E82" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="F82" t="n">
-        <v>0.008076560332912458</v>
+        <v>6.25e-05</v>
       </c>
       <c r="G82" t="n">
-        <v>0.007723667525132277</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -2774,19 +2810,19 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D83" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E83" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F83" t="n">
-        <v>0.00878828016645623</v>
+        <v>9.750000000000001e-05</v>
       </c>
       <c r="G83" t="n">
-        <v>0.006986833762566138</v>
+        <v>-0.0005</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -2802,19 +2838,19 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="D84" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E84" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F84" t="n">
-        <v>0.008288280166456229</v>
+        <v>0.0004800000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>0.005736833762566139</v>
+        <v>-0.0015</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -2830,19 +2866,19 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D85" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E85" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="F85" t="n">
-        <v>0.009500000000000001</v>
+        <v>0.0003825</v>
       </c>
       <c r="G85" t="n">
-        <v>0.00625</v>
+        <v>-0.001</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -2858,19 +2894,19 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D86" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E86" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F86" t="n">
-        <v>0.003136130241965427</v>
+        <v>0.0004175</v>
       </c>
       <c r="G86" t="n">
-        <v>0.005498348676669243</v>
+        <v>-0.0015</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
@@ -2886,19 +2922,19 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D87" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F87" t="n">
-        <v>0.002603513550129027</v>
+        <v>0.0053125</v>
       </c>
       <c r="G87" t="n">
-        <v>0.006827843705301541</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -2914,19 +2950,19 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D88" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F88" t="n">
-        <v>0.005147457191205085</v>
+        <v>0.004660000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>0.007131006259066117</v>
+        <v>-0.0005</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -2942,19 +2978,19 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D89" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E89" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F89" t="n">
-        <v>0.003609177024748856</v>
+        <v>0.0053475</v>
       </c>
       <c r="G89" t="n">
-        <v>0.007644172496499979</v>
+        <v>-0.0005</v>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -2970,19 +3006,19 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D90" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E90" t="n">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="F90" t="n">
-        <v>0.002070896858292628</v>
+        <v>0.0039375</v>
       </c>
       <c r="G90" t="n">
-        <v>0.008157338733933841</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -2998,19 +3034,19 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D91" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E91" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F91" t="n">
-        <v>0.01226189900498261</v>
+        <v>0.003285</v>
       </c>
       <c r="G91" t="n">
-        <v>0.002713911078465526</v>
+        <v>-0.0005</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -3026,19 +3062,19 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="D92" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01342459933665507</v>
+        <v>0.0039725</v>
       </c>
       <c r="G92" t="n">
-        <v>0.00355927405231035</v>
+        <v>-0.0005</v>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -3054,19 +3090,19 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D93" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="F93" t="n">
-        <v>0.01351189900498261</v>
+        <v>0.004007500000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>0.004463911078465526</v>
+        <v>-0.001</v>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
@@ -3082,19 +3118,19 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D94" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E94" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F94" t="n">
-        <v>0.01208729966832754</v>
+        <v>0.003355</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0009046370261551752</v>
+        <v>-0.0015</v>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -3110,19 +3146,19 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D95" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E95" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F95" t="n">
-        <v>0.01325</v>
+        <v>0.0040425</v>
       </c>
       <c r="G95" t="n">
-        <v>0.00175</v>
+        <v>-0.0015</v>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -3138,19 +3174,19 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D96" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E96" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F96" t="n">
-        <v>0.01333729966832754</v>
+        <v>0.0025625</v>
       </c>
       <c r="G96" t="n">
-        <v>0.002654637026155175</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
@@ -3166,19 +3202,19 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D97" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E97" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F97" t="n">
-        <v>0.01458729966832754</v>
+        <v>0.00191</v>
       </c>
       <c r="G97" t="n">
-        <v>0.004404637026155176</v>
+        <v>-0.0005</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
@@ -3197,16 +3233,16 @@
         <v>12</v>
       </c>
       <c r="D98" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E98" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F98" t="n">
-        <v>0.01575</v>
+        <v>0.0025975</v>
       </c>
       <c r="G98" t="n">
-        <v>0.00525</v>
+        <v>-0.0005</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
@@ -3222,19 +3258,19 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D99" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E99" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F99" t="n">
-        <v>0.01583729966832754</v>
+        <v>0.0011875</v>
       </c>
       <c r="G99" t="n">
-        <v>0.006154637026155175</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
@@ -3250,19 +3286,19 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D100" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E100" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F100" t="n">
-        <v>0.01133729966832754</v>
+        <v>0.0012225</v>
       </c>
       <c r="G100" t="n">
-        <v>0.002154637026155175</v>
+        <v>-0.0005</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
@@ -3278,19 +3314,19 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D101" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E101" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F101" t="n">
-        <v>0.01125</v>
+        <v>0.0012575</v>
       </c>
       <c r="G101" t="n">
-        <v>0.00125</v>
+        <v>-0.001</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
@@ -3306,19 +3342,19 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D102" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E102" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F102" t="n">
-        <v>0.01151189900498261</v>
+        <v>0.0012925</v>
       </c>
       <c r="G102" t="n">
-        <v>0.003963911078465525</v>
+        <v>-0.0015</v>
       </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
@@ -3334,19 +3370,19 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D103" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E103" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="F103" t="n">
-        <v>0.01142459933665507</v>
+        <v>0.0027025</v>
       </c>
       <c r="G103" t="n">
-        <v>0.00305927405231035</v>
+        <v>-0.002</v>
       </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
@@ -3362,19 +3398,19 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D104" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="E104" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F104" t="n">
-        <v>0.01058729966832754</v>
+        <v>0.00205</v>
       </c>
       <c r="G104" t="n">
-        <v>0.003404637026155176</v>
+        <v>-0.0025</v>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
@@ -3390,19 +3426,19 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D105" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="E105" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F105" t="n">
-        <v>0.009837299668327536</v>
+        <v>0.0027375</v>
       </c>
       <c r="G105" t="n">
-        <v>0.004654637026155175</v>
+        <v>-0.0025</v>
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
@@ -3418,19 +3454,19 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D106" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E106" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F106" t="n">
-        <v>0.009750000000000002</v>
+        <v>0.0013275</v>
       </c>
       <c r="G106" t="n">
-        <v>0.00375</v>
+        <v>-0.002</v>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
@@ -3446,19 +3482,19 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D107" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E107" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="F107" t="n">
-        <v>0.01133729966832754</v>
+        <v>0.0013625</v>
       </c>
       <c r="G107" t="n">
-        <v>0.008404637026155175</v>
+        <v>-0.0025</v>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
@@ -3474,19 +3510,19 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D108" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="E108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>0.01283729966832754</v>
+        <v>0.0013975</v>
       </c>
       <c r="G108" t="n">
-        <v>0.007654637026155176</v>
+        <v>-0.003</v>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
@@ -3502,19 +3538,19 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D109" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="E109" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0125</v>
+        <v>0.0014325</v>
       </c>
       <c r="G109" t="n">
-        <v>0.009250000000000001</v>
+        <v>-0.0035</v>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
@@ -3530,19 +3566,19 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D110" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E110" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F110" t="n">
-        <v>0.01201189900498261</v>
+        <v>0.0026325</v>
       </c>
       <c r="G110" t="n">
-        <v>0.005213911078465526</v>
+        <v>-0.001</v>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
@@ -3558,19 +3594,19 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D111" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E111" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F111" t="n">
-        <v>0.01317459933665507</v>
+        <v>0.00198</v>
       </c>
       <c r="G111" t="n">
-        <v>0.00605927405231035</v>
+        <v>-0.0015</v>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
@@ -3586,19 +3622,19 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D112" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E112" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F112" t="n">
-        <v>0.01433729966832754</v>
+        <v>0.0026675</v>
       </c>
       <c r="G112" t="n">
-        <v>0.006904637026155175</v>
+        <v>-0.0015</v>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
@@ -3614,19 +3650,19 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D113" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E113" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0155</v>
+        <v>0.00665</v>
       </c>
       <c r="G113" t="n">
-        <v>0.00775</v>
+        <v>-0.0005</v>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
@@ -3642,19 +3678,19 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D114" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E114" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F114" t="n">
-        <v>0.01117459933665507</v>
+        <v>0.0074</v>
       </c>
       <c r="G114" t="n">
-        <v>0.00555927405231035</v>
+        <v>-0.0005</v>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
@@ -3670,19 +3706,19 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D115" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E115" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F115" t="n">
-        <v>0.01083729966832754</v>
+        <v>0.006750000000000001</v>
       </c>
       <c r="G115" t="n">
-        <v>0.007154637026155175</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
@@ -3698,19 +3734,19 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D116" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E116" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F116" t="n">
-        <v>0.01033729966832754</v>
+        <v>0.00795</v>
       </c>
       <c r="G116" t="n">
-        <v>0.005904637026155175</v>
+        <v>-0.0015</v>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
@@ -3726,19 +3762,19 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D117" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E117" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F117" t="n">
-        <v>0.006750000000000001</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0015</v>
+        <v>-0.0015</v>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
@@ -3754,19 +3790,19 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D118" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E118" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F118" t="n">
-        <v>0.007750000000000001</v>
+        <v>0.00805</v>
       </c>
       <c r="G118" t="n">
-        <v>0.00225</v>
+        <v>-0.001</v>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
@@ -3782,19 +3818,19 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D119" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E119" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F119" t="n">
-        <v>0.006</v>
+        <v>0.008150000000000001</v>
       </c>
       <c r="G119" t="n">
-        <v>0.00275</v>
+        <v>-0.0005</v>
       </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
@@ -3810,19 +3846,19 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D120" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E120" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F120" t="n">
-        <v>0.01025</v>
+        <v>0.008900000000000002</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0005</v>
+        <v>-0.0005</v>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
@@ -3838,19 +3874,19 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D121" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E121" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F121" t="n">
-        <v>0.009500000000000001</v>
+        <v>0.00825</v>
       </c>
       <c r="G121" t="n">
-        <v>0.00175</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
@@ -3866,19 +3902,19 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D122" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E122" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F122" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.009250000000000001</v>
       </c>
       <c r="G122" t="n">
-        <v>0.003</v>
+        <v>-0.0025</v>
       </c>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
@@ -3894,19 +3930,19 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D123" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E123" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F123" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="G123" t="n">
-        <v>0.00425</v>
+        <v>-0.0025</v>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
@@ -3922,19 +3958,19 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D124" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E124" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F124" t="n">
-        <v>0.004907901741563027</v>
+        <v>0.009350000000000001</v>
       </c>
       <c r="G124" t="n">
-        <v>0.001333221130700677</v>
+        <v>-0.002</v>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
@@ -3950,19 +3986,19 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D125" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E125" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F125" t="n">
-        <v>0.006657901741563027</v>
+        <v>0.01055</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0008332211307006767</v>
+        <v>-0.0035</v>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
@@ -3978,19 +4014,19 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D126" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E126" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F126" t="n">
-        <v>0.00472370522468908</v>
+        <v>0.0113</v>
       </c>
       <c r="G126" t="n">
-        <v>-3.366078979700582e-07</v>
+        <v>-0.0035</v>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
@@ -4006,19 +4042,19 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D127" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E127" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F127" t="n">
-        <v>0.006565803483126053</v>
+        <v>0.01065</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0001664422614013533</v>
+        <v>-0.003</v>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
@@ -4034,19 +4070,19 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D128" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E128" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F128" t="n">
-        <v>0.008407901741563027</v>
+        <v>0.01075</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0003332211307006767</v>
+        <v>-0.0025</v>
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
@@ -4062,19 +4098,19 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D129" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E129" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F129" t="n">
-        <v>0.004282616691836399</v>
+        <v>0.0115</v>
       </c>
       <c r="G129" t="n">
-        <v>0.002670504971367701</v>
+        <v>-0.0025</v>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
@@ -4090,19 +4126,19 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E130" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F130" t="n">
-        <v>0.003032616691836399</v>
+        <v>0.01085</v>
       </c>
       <c r="G130" t="n">
-        <v>0.002170504971367702</v>
+        <v>-0.002</v>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
@@ -4118,19 +4154,19 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D131" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E131" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F131" t="n">
-        <v>0.00375</v>
+        <v>0.009650000000000001</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0015</v>
+        <v>-0.0005</v>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
@@ -4146,19 +4182,19 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D132" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E132" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F132" t="n">
-        <v>0.002847850075509199</v>
+        <v>0.0104</v>
       </c>
       <c r="G132" t="n">
-        <v>0.004011514914103105</v>
+        <v>-0.0005</v>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
@@ -4174,19 +4210,19 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D133" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E133" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F133" t="n">
-        <v>0.002315233383672799</v>
+        <v>0.009750000000000002</v>
       </c>
       <c r="G133" t="n">
-        <v>0.002841009942735403</v>
+        <v>0</v>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
@@ -4202,19 +4238,19 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D134" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E134" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F134" t="n">
-        <v>0.001782616691836399</v>
+        <v>0.01095</v>
       </c>
       <c r="G134" t="n">
-        <v>0.001670504971367702</v>
+        <v>-0.0015</v>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
@@ -4230,19 +4266,19 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D135" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E135" t="n">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="F135" t="n">
-        <v>0.00125</v>
+        <v>0.0117</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
@@ -4258,19 +4294,19 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D136" t="n">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E136" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F136" t="n">
-        <v>0.003565803483126053</v>
+        <v>0.01105</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0001664422614013533</v>
+        <v>-0.001</v>
       </c>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
@@ -4286,19 +4322,19 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D137" t="n">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E137" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F137" t="n">
-        <v>0.003657901741563027</v>
+        <v>0.01115</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0008332211307006767</v>
+        <v>-0.0005</v>
       </c>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
@@ -4314,19 +4350,19 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D138" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E138" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F138" t="n">
-        <v>0.002407901741563027</v>
+        <v>0.0119</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0003332211307006767</v>
+        <v>-0.0005</v>
       </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
@@ -4342,19 +4378,19 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D139" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E139" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="F139" t="n">
-        <v>0.006038280166456229</v>
+        <v>0.01125</v>
       </c>
       <c r="G139" t="n">
-        <v>0.006486833762566139</v>
+        <v>0</v>
       </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
@@ -4370,19 +4406,19 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D140" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="E140" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F140" t="n">
-        <v>0.005070896858292628</v>
+        <v>0.00945</v>
       </c>
       <c r="G140" t="n">
-        <v>0.00615733873393384</v>
+        <v>-0.0015</v>
       </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
@@ -4398,19 +4434,19 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D141" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="E141" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F141" t="n">
-        <v>0.005032616691836399</v>
+        <v>0.0102</v>
       </c>
       <c r="G141" t="n">
-        <v>0.005670504971367701</v>
+        <v>-0.0015</v>
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
@@ -4426,19 +4462,19 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D142" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E142" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F142" t="n">
-        <v>0.006114840499368685</v>
+        <v>0.009549999999999999</v>
       </c>
       <c r="G142" t="n">
-        <v>0.007460501287698416</v>
+        <v>-0.001</v>
       </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
@@ -4454,19 +4490,19 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D143" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E143" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F143" t="n">
-        <v>0.005109177024748857</v>
+        <v>0.006</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006644172496499979</v>
+        <v>-0.0035</v>
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
@@ -4482,19 +4518,19 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D144" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E144" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F144" t="n">
-        <v>0.004103513550129027</v>
+        <v>0.0053475</v>
       </c>
       <c r="G144" t="n">
-        <v>0.005827843705301541</v>
+        <v>-0.0035</v>
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
@@ -4510,19 +4546,19 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D145" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E145" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F145" t="n">
-        <v>0.003097850075509198</v>
+        <v>0.0053475</v>
       </c>
       <c r="G145" t="n">
-        <v>0.005011514914103104</v>
+        <v>-0.004</v>
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
@@ -4538,19 +4574,19 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D146" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E146" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="F146" t="n">
-        <v>0.005249999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="G146" t="n">
-        <v>0.003</v>
+        <v>-0.0025</v>
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
@@ -4566,19 +4602,19 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D147" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E147" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0045326166918364</v>
+        <v>0.0053475</v>
       </c>
       <c r="G147" t="n">
-        <v>0.003670504971367701</v>
+        <v>-0.0025</v>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
@@ -4594,19 +4630,19 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="D148" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E148" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F148" t="n">
-        <v>0.00575</v>
+        <v>0.0053475</v>
       </c>
       <c r="G148" t="n">
-        <v>0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
@@ -4622,19 +4658,19 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D149" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E149" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="F149" t="n">
-        <v>0.004782616691836399</v>
+        <v>0.004695</v>
       </c>
       <c r="G149" t="n">
-        <v>0.004670504971367701</v>
+        <v>-0.0035</v>
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
@@ -4650,19 +4686,19 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D150" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="E150" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F150" t="n">
-        <v>0.003815233383672799</v>
+        <v>0.0040425</v>
       </c>
       <c r="G150" t="n">
-        <v>0.004341009942735403</v>
+        <v>-0.0035</v>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
@@ -4678,19 +4714,19 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E151" t="n">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="F151" t="n">
-        <v>0.006826560332912457</v>
+        <v>0.0040425</v>
       </c>
       <c r="G151" t="n">
-        <v>0.006723667525132277</v>
+        <v>-0.004</v>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
@@ -4706,19 +4742,19 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D152" t="n">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="E152" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F152" t="n">
-        <v>0.006750000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="G152" t="n">
-        <v>0.00575</v>
+        <v>-0.0015</v>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -4734,19 +4770,19 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D153" t="n">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="E153" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F153" t="n">
-        <v>0.006788280166456229</v>
+        <v>0.0053475</v>
       </c>
       <c r="G153" t="n">
-        <v>0.006236833762566138</v>
+        <v>-0.0015</v>
       </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
@@ -4762,19 +4798,19 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D154" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E154" t="n">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="F154" t="n">
-        <v>0.007538280166456229</v>
+        <v>0.0053475</v>
       </c>
       <c r="G154" t="n">
-        <v>0.005986833762566138</v>
+        <v>-0.002</v>
       </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
@@ -4790,19 +4826,19 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D155" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E155" t="n">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="F155" t="n">
-        <v>0.00825</v>
+        <v>0.006</v>
       </c>
       <c r="G155" t="n">
-        <v>0.005249999999999999</v>
+        <v>-0.0005</v>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
@@ -4818,19 +4854,19 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="D156" t="n">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="E156" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F156" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0053475</v>
       </c>
       <c r="G156" t="n">
-        <v>0.00475</v>
+        <v>-0.001</v>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
@@ -4846,19 +4882,19 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D157" t="n">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="E157" t="n">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="F157" t="n">
-        <v>0.00625</v>
+        <v>0.004695</v>
       </c>
       <c r="G157" t="n">
-        <v>0.00375</v>
+        <v>-0.0015</v>
       </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
@@ -4874,19 +4910,19 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D158" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="E158" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F158" t="n">
-        <v>0.007250000000000001</v>
+        <v>0.0040425</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0045</v>
+        <v>-0.002</v>
       </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
@@ -4902,16 +4938,20 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D159" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E159" t="n">
-        <v>115</v>
-      </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
+        <v>127</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="G159" t="n">
+        <v>-0.0035</v>
+      </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="n">
@@ -4926,16 +4966,20 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D160" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E160" t="n">
-        <v>31</v>
-      </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.0027375</v>
+      </c>
+      <c r="G160" t="n">
+        <v>-0.0035</v>
+      </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="n">
@@ -4950,16 +4994,20 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D161" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E161" t="n">
-        <v>113</v>
-      </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
+        <v>122</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.0027375</v>
+      </c>
+      <c r="G161" t="n">
+        <v>-0.004</v>
+      </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="n">
@@ -4974,16 +5022,20 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D162" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="E162" t="n">
-        <v>118</v>
-      </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
+        <v>132</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="G162" t="n">
+        <v>-0.0025</v>
+      </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="n">
@@ -4998,16 +5050,20 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D163" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E163" t="n">
-        <v>117</v>
-      </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.0027375</v>
+      </c>
+      <c r="G163" t="n">
+        <v>-0.003</v>
+      </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="n">
@@ -5022,16 +5078,20 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D164" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E164" t="n">
-        <v>36</v>
-      </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.002085</v>
+      </c>
+      <c r="G164" t="n">
+        <v>-0.0035</v>
+      </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="n">
@@ -5046,16 +5106,20 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D165" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E165" t="n">
-        <v>118</v>
-      </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
+        <v>132</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.0014325</v>
+      </c>
+      <c r="G165" t="n">
+        <v>-0.004</v>
+      </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="n">
@@ -5070,16 +5134,20 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D166" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E166" t="n">
-        <v>120</v>
-      </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
+        <v>135</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.004695</v>
+      </c>
+      <c r="G166" t="n">
+        <v>-0.0025</v>
+      </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="n">
@@ -5094,16 +5162,20 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D167" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E167" t="n">
-        <v>100</v>
-      </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.0040425</v>
+      </c>
+      <c r="G167" t="n">
+        <v>-0.0025</v>
+      </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="n">
@@ -5118,16 +5190,20 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D168" t="n">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="E168" t="n">
-        <v>32</v>
-      </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.0040425</v>
+      </c>
+      <c r="G168" t="n">
+        <v>-0.003</v>
+      </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="n">
@@ -5142,16 +5218,20 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D169" t="n">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="E169" t="n">
-        <v>120</v>
-      </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
+        <v>135</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="G169" t="n">
+        <v>-0.004</v>
+      </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="n">
@@ -5166,16 +5246,20 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D170" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="E170" t="n">
-        <v>122</v>
-      </c>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="G170" t="n">
+        <v>-0.0035</v>
+      </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="n">
@@ -5190,16 +5274,20 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D171" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E171" t="n">
-        <v>105</v>
-      </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
+        <v>137</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="G171" t="n">
+        <v>-0.004</v>
+      </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="n">
@@ -5214,16 +5302,20 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D172" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="E172" t="n">
-        <v>9</v>
-      </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="G172" t="n">
+        <v>-0.0035</v>
+      </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
@@ -5238,16 +5330,20 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D173" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="E173" t="n">
-        <v>122</v>
-      </c>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="G173" t="n">
+        <v>-0.0035</v>
+      </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
@@ -5262,16 +5358,20 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D174" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="E174" t="n">
-        <v>117</v>
-      </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="G174" t="n">
+        <v>-0.003</v>
+      </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="n">
@@ -5286,16 +5386,20 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D175" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E175" t="n">
-        <v>121</v>
-      </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="G175" t="n">
+        <v>-0.0025</v>
+      </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
@@ -5310,16 +5414,20 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D176" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="E176" t="n">
-        <v>36</v>
-      </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.009250000000000001</v>
+      </c>
+      <c r="G176" t="n">
+        <v>-0.004</v>
+      </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="n">
@@ -5334,16 +5442,20 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D177" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="E177" t="n">
-        <v>117</v>
-      </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.009250000000000001</v>
+      </c>
+      <c r="G177" t="n">
+        <v>-0.0035</v>
+      </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="n">
@@ -5358,7 +5470,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D178" t="n">
         <v>123</v>
@@ -5366,8 +5478,12 @@
       <c r="E178" t="n">
         <v>116</v>
       </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
+      <c r="F178" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="G178" t="n">
+        <v>-0.0035</v>
+      </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="n">
@@ -5385,13 +5501,17 @@
         <v>123</v>
       </c>
       <c r="D179" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E179" t="n">
-        <v>124</v>
-      </c>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
+        <v>139</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.01055</v>
+      </c>
+      <c r="G179" t="n">
+        <v>-0.004</v>
+      </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="n">
@@ -5409,13 +5529,17 @@
         <v>116</v>
       </c>
       <c r="D180" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E180" t="n">
-        <v>35</v>
-      </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="G180" t="n">
+        <v>-0.0035</v>
+      </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="n">
@@ -5433,13 +5557,17 @@
         <v>123</v>
       </c>
       <c r="D181" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E181" t="n">
         <v>116</v>
       </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="F181" t="n">
+        <v>0.009250000000000001</v>
+      </c>
+      <c r="G181" t="n">
+        <v>-0.003</v>
+      </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="n">
@@ -5454,16 +5582,20 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D182" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E182" t="n">
-        <v>126</v>
-      </c>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="G182" t="n">
+        <v>-0.0025</v>
+      </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="n">
@@ -5478,16 +5610,20 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D183" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E183" t="n">
-        <v>56</v>
-      </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
+        <v>133</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="G183" t="n">
+        <v>-0.002</v>
+      </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="n">
@@ -5502,16 +5638,20 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D184" t="n">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E184" t="n">
-        <v>17</v>
-      </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="G184" t="n">
+        <v>-0.0015</v>
+      </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="n">
@@ -5526,16 +5666,20 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D185" t="n">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E185" t="n">
-        <v>126</v>
-      </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="G185" t="n">
+        <v>-0.002</v>
+      </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="n">
@@ -5550,16 +5694,20 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D186" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E186" t="n">
         <v>119</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
+      <c r="F186" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="G186" t="n">
+        <v>-0.0015</v>
+      </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="n">
@@ -5574,16 +5722,20 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D187" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E187" t="n">
-        <v>53</v>
-      </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
+        <v>130</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="G187" t="n">
+        <v>-0.001</v>
+      </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="n">
@@ -5601,13 +5753,17 @@
         <v>119</v>
       </c>
       <c r="D188" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="E188" t="n">
-        <v>4</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="G188" t="n">
+        <v>-0.003</v>
+      </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="n">
@@ -5622,16 +5778,20 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D189" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="E189" t="n">
         <v>119</v>
       </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
+      <c r="F189" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="G189" t="n">
+        <v>-0.0025</v>
+      </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="n">
@@ -5646,16 +5806,20 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D190" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E190" t="n">
-        <v>124</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
+        <v>139</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="G190" t="n">
+        <v>-0.0025</v>
+      </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="n">
@@ -5670,13 +5834,13 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D191" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E191" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
@@ -5694,13 +5858,13 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D192" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E192" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
@@ -5718,13 +5882,13 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D193" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E193" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
@@ -5742,13 +5906,13 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D194" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E194" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
@@ -5766,13 +5930,13 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D195" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E195" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
@@ -5790,13 +5954,13 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="D196" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E196" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
@@ -5814,13 +5978,13 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D197" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E197" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
@@ -5838,13 +6002,13 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D198" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E198" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
@@ -5862,13 +6026,13 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D199" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E199" t="n">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
@@ -5886,13 +6050,13 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D200" t="n">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="E200" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
@@ -5910,13 +6074,13 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D201" t="n">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="E201" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
@@ -5934,13 +6098,13 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D202" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E202" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
@@ -5958,13 +6122,13 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D203" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E203" t="n">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
@@ -5982,13 +6146,13 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="D204" t="n">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="E204" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
@@ -6006,13 +6170,13 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D205" t="n">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="E205" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
@@ -6030,13 +6194,13 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D206" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="E206" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
@@ -6054,13 +6218,13 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D207" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E207" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
@@ -6078,13 +6242,13 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D208" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E208" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
@@ -6102,13 +6266,13 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D209" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E209" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
@@ -6126,13 +6290,13 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D210" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="E210" t="n">
-        <v>64</v>
+        <v>153</v>
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
@@ -6150,13 +6314,13 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="D211" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E211" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
@@ -6174,13 +6338,13 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
-        <v>64</v>
+        <v>153</v>
       </c>
       <c r="D212" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="E212" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
@@ -6198,13 +6362,13 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="D213" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="E213" t="n">
-        <v>64</v>
+        <v>153</v>
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
@@ -6222,13 +6386,13 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D214" t="n">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="E214" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
@@ -6246,13 +6410,13 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="n">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="D215" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E215" t="n">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr"/>
@@ -6270,13 +6434,13 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="D216" t="n">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="E216" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
@@ -6294,13 +6458,13 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="D217" t="n">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="E217" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
@@ -6318,13 +6482,13 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D218" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="E218" t="n">
-        <v>67</v>
+        <v>157</v>
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
@@ -6342,13 +6506,13 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D219" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E219" t="n">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr"/>
@@ -6366,13 +6530,13 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
-        <v>67</v>
+        <v>157</v>
       </c>
       <c r="D220" t="n">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
@@ -6390,13 +6554,13 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D221" t="n">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="E221" t="n">
-        <v>67</v>
+        <v>157</v>
       </c>
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr"/>
@@ -6414,13 +6578,13 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D222" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="E222" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
@@ -6438,13 +6602,13 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="D223" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E223" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr"/>
@@ -6462,13 +6626,13 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="D224" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="E224" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
@@ -6486,13 +6650,13 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="D225" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="E225" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr"/>
@@ -6510,13 +6674,13 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D226" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="E226" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr"/>
@@ -6534,13 +6698,13 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D227" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E227" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr"/>
@@ -6558,13 +6722,13 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D228" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E228" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
@@ -6582,13 +6746,13 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D229" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E229" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
@@ -6606,13 +6770,13 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D230" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="E230" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
@@ -6630,13 +6794,13 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="D231" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E231" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr"/>
@@ -6654,13 +6818,13 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="D232" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E232" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr"/>
@@ -6678,13 +6842,13 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="D233" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E233" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
@@ -6702,13 +6866,13 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D234" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="E234" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
@@ -6726,13 +6890,13 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D235" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E235" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
@@ -6750,13 +6914,13 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="D236" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="E236" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
@@ -6774,13 +6938,13 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D237" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="E237" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr"/>
@@ -6798,13 +6962,13 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D238" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="E238" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr"/>
@@ -6822,13 +6986,13 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="D239" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E239" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr"/>
@@ -6846,13 +7010,13 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D240" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="E240" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
@@ -6870,13 +7034,13 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="D241" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="E241" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
@@ -6894,13 +7058,13 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D242" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E242" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
@@ -6918,13 +7082,13 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr"/>
       <c r="C243" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D243" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E243" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
@@ -6942,13 +7106,13 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="D244" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="E244" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
@@ -6966,13 +7130,13 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D245" t="n">
+        <v>165</v>
+      </c>
+      <c r="E245" t="n">
         <v>146</v>
-      </c>
-      <c r="E245" t="n">
-        <v>128</v>
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr"/>
@@ -6990,13 +7154,13 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D246" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E246" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr"/>
@@ -7014,13 +7178,13 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D247" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E247" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr"/>
@@ -7038,13 +7202,13 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D248" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E248" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr"/>
@@ -7062,13 +7226,13 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D249" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E249" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
@@ -7086,13 +7250,13 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D250" t="n">
+        <v>167</v>
+      </c>
+      <c r="E250" t="n">
         <v>149</v>
-      </c>
-      <c r="E250" t="n">
-        <v>131</v>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
@@ -7110,13 +7274,13 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D251" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E251" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
@@ -7134,13 +7298,13 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="D252" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="E252" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
@@ -7158,13 +7322,13 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="n">
+        <v>167</v>
+      </c>
+      <c r="D253" t="n">
+        <v>158</v>
+      </c>
+      <c r="E253" t="n">
         <v>149</v>
-      </c>
-      <c r="D253" t="n">
-        <v>144</v>
-      </c>
-      <c r="E253" t="n">
-        <v>131</v>
       </c>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
@@ -7182,13 +7346,13 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D254" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="E254" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
@@ -7206,13 +7370,13 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D255" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E255" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
@@ -7230,13 +7394,13 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="D256" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E256" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
@@ -7254,13 +7418,13 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D257" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E257" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
@@ -7278,13 +7442,13 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D258" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="E258" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
@@ -7302,13 +7466,13 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="D259" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E259" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr"/>
@@ -7326,13 +7490,13 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="D260" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="E260" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr"/>
@@ -7350,13 +7514,13 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="D261" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="E261" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr"/>
@@ -7374,13 +7538,13 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D262" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="E262" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
@@ -7398,13 +7562,13 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="D263" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E263" t="n">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
@@ -7422,13 +7586,13 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D264" t="n">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="E264" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr"/>
@@ -7446,13 +7610,13 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="D265" t="n">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="E265" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr"/>
@@ -7470,13 +7634,13 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr"/>
       <c r="C266" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D266" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E266" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr"/>
@@ -7494,13 +7658,13 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D267" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E267" t="n">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr"/>
@@ -7518,13 +7682,13 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D268" t="n">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="E268" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr"/>
@@ -7542,13 +7706,13 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D269" t="n">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="E269" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr"/>
@@ -7566,13 +7730,13 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D270" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="E270" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr"/>
@@ -7590,13 +7754,13 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr"/>
       <c r="C271" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D271" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E271" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr"/>
@@ -7614,13 +7778,13 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="D272" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E272" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr"/>
@@ -7638,13 +7802,13 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D273" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E273" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
@@ -7662,13 +7826,13 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D274" t="n">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="E274" t="n">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
@@ -7686,13 +7850,13 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="D275" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E275" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr"/>
@@ -7710,13 +7874,13 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="n">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="D276" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="E276" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr"/>
@@ -7734,13 +7898,13 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="n">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="D277" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="E277" t="n">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr"/>
@@ -7758,13 +7922,13 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D278" t="n">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="E278" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr"/>
@@ -7782,13 +7946,13 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="D279" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E279" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr"/>
@@ -7806,13 +7970,13 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D280" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E280" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr"/>
@@ -7830,13 +7994,13 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="D281" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E281" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr"/>
@@ -7854,13 +8018,13 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D282" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="E282" t="n">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
@@ -7878,13 +8042,13 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="D283" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E283" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr"/>
@@ -7902,13 +8066,13 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="n">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="D284" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E284" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr"/>
@@ -7926,13 +8090,13 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="D285" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E285" t="n">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr"/>
@@ -7950,13 +8114,13 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D286" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="E286" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr"/>
@@ -7974,13 +8138,13 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D287" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E287" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr"/>
@@ -7998,13 +8162,13 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="D288" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="E288" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr"/>
@@ -8022,13 +8186,13 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D289" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="E289" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr"/>
@@ -8045,9 +8209,15 @@
     <row r="290">
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr"/>
-      <c r="C290" t="inlineStr"/>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
+      <c r="C290" t="n">
+        <v>16</v>
+      </c>
+      <c r="D290" t="n">
+        <v>182</v>
+      </c>
+      <c r="E290" t="n">
+        <v>151</v>
+      </c>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr"/>
@@ -8063,9 +8233,15 @@
     <row r="291">
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr"/>
-      <c r="C291" t="inlineStr"/>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
+      <c r="C291" t="n">
+        <v>182</v>
+      </c>
+      <c r="D291" t="n">
+        <v>55</v>
+      </c>
+      <c r="E291" t="n">
+        <v>183</v>
+      </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
@@ -8081,9 +8257,15 @@
     <row r="292">
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr"/>
-      <c r="C292" t="inlineStr"/>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
+      <c r="C292" t="n">
+        <v>151</v>
+      </c>
+      <c r="D292" t="n">
+        <v>183</v>
+      </c>
+      <c r="E292" t="n">
+        <v>47</v>
+      </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr"/>
@@ -8099,9 +8281,15 @@
     <row r="293">
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr"/>
-      <c r="C293" t="inlineStr"/>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr"/>
+      <c r="C293" t="n">
+        <v>182</v>
+      </c>
+      <c r="D293" t="n">
+        <v>183</v>
+      </c>
+      <c r="E293" t="n">
+        <v>151</v>
+      </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr"/>
@@ -8117,9 +8305,15 @@
     <row r="294">
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr"/>
-      <c r="C294" t="inlineStr"/>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr"/>
+      <c r="C294" t="n">
+        <v>55</v>
+      </c>
+      <c r="D294" t="n">
+        <v>184</v>
+      </c>
+      <c r="E294" t="n">
+        <v>185</v>
+      </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr"/>
@@ -8135,9 +8329,15 @@
     <row r="295">
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr"/>
-      <c r="C295" t="inlineStr"/>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
+      <c r="C295" t="n">
+        <v>184</v>
+      </c>
+      <c r="D295" t="n">
+        <v>13</v>
+      </c>
+      <c r="E295" t="n">
+        <v>115</v>
+      </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr"/>
@@ -8153,9 +8353,15 @@
     <row r="296">
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr"/>
-      <c r="C296" t="inlineStr"/>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
+      <c r="C296" t="n">
+        <v>185</v>
+      </c>
+      <c r="D296" t="n">
+        <v>115</v>
+      </c>
+      <c r="E296" t="n">
+        <v>35</v>
+      </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
@@ -8171,9 +8377,15 @@
     <row r="297">
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr"/>
-      <c r="C297" t="inlineStr"/>
-      <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr"/>
+      <c r="C297" t="n">
+        <v>184</v>
+      </c>
+      <c r="D297" t="n">
+        <v>115</v>
+      </c>
+      <c r="E297" t="n">
+        <v>185</v>
+      </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr"/>
@@ -8189,9 +8401,15 @@
     <row r="298">
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr"/>
-      <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
+      <c r="C298" t="n">
+        <v>47</v>
+      </c>
+      <c r="D298" t="n">
+        <v>186</v>
+      </c>
+      <c r="E298" t="n">
+        <v>154</v>
+      </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
@@ -8207,9 +8425,15 @@
     <row r="299">
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr"/>
-      <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr"/>
+      <c r="C299" t="n">
+        <v>186</v>
+      </c>
+      <c r="D299" t="n">
+        <v>35</v>
+      </c>
+      <c r="E299" t="n">
+        <v>112</v>
+      </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr"/>
@@ -8225,9 +8449,15 @@
     <row r="300">
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr"/>
-      <c r="C300" t="inlineStr"/>
-      <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr"/>
+      <c r="C300" t="n">
+        <v>154</v>
+      </c>
+      <c r="D300" t="n">
+        <v>112</v>
+      </c>
+      <c r="E300" t="n">
+        <v>6</v>
+      </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr"/>
@@ -8243,9 +8473,15 @@
     <row r="301">
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr"/>
-      <c r="C301" t="inlineStr"/>
-      <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr"/>
+      <c r="C301" t="n">
+        <v>186</v>
+      </c>
+      <c r="D301" t="n">
+        <v>112</v>
+      </c>
+      <c r="E301" t="n">
+        <v>154</v>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
@@ -8261,9 +8497,15 @@
     <row r="302">
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr"/>
-      <c r="C302" t="inlineStr"/>
-      <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr"/>
+      <c r="C302" t="n">
+        <v>55</v>
+      </c>
+      <c r="D302" t="n">
+        <v>185</v>
+      </c>
+      <c r="E302" t="n">
+        <v>183</v>
+      </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr"/>
@@ -8279,9 +8521,15 @@
     <row r="303">
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr"/>
-      <c r="C303" t="inlineStr"/>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr"/>
+      <c r="C303" t="n">
+        <v>185</v>
+      </c>
+      <c r="D303" t="n">
+        <v>35</v>
+      </c>
+      <c r="E303" t="n">
+        <v>186</v>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
@@ -8297,9 +8545,15 @@
     <row r="304">
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr"/>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
+      <c r="C304" t="n">
+        <v>183</v>
+      </c>
+      <c r="D304" t="n">
+        <v>186</v>
+      </c>
+      <c r="E304" t="n">
+        <v>47</v>
+      </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
@@ -8315,9 +8569,15 @@
     <row r="305">
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr"/>
-      <c r="C305" t="inlineStr"/>
-      <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
+      <c r="C305" t="n">
+        <v>185</v>
+      </c>
+      <c r="D305" t="n">
+        <v>186</v>
+      </c>
+      <c r="E305" t="n">
+        <v>183</v>
+      </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
@@ -8333,9 +8593,15 @@
     <row r="306">
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr"/>
-      <c r="C306" t="inlineStr"/>
-      <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr"/>
+      <c r="C306" t="n">
+        <v>18</v>
+      </c>
+      <c r="D306" t="n">
+        <v>177</v>
+      </c>
+      <c r="E306" t="n">
+        <v>171</v>
+      </c>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
@@ -8351,9 +8617,15 @@
     <row r="307">
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr"/>
-      <c r="C307" t="inlineStr"/>
-      <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr"/>
+      <c r="C307" t="n">
+        <v>177</v>
+      </c>
+      <c r="D307" t="n">
+        <v>54</v>
+      </c>
+      <c r="E307" t="n">
+        <v>187</v>
+      </c>
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr"/>
@@ -8369,9 +8641,15 @@
     <row r="308">
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr"/>
-      <c r="C308" t="inlineStr"/>
-      <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
+      <c r="C308" t="n">
+        <v>171</v>
+      </c>
+      <c r="D308" t="n">
+        <v>187</v>
+      </c>
+      <c r="E308" t="n">
+        <v>52</v>
+      </c>
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr"/>
@@ -8387,9 +8665,15 @@
     <row r="309">
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr"/>
-      <c r="C309" t="inlineStr"/>
-      <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr"/>
+      <c r="C309" t="n">
+        <v>177</v>
+      </c>
+      <c r="D309" t="n">
+        <v>187</v>
+      </c>
+      <c r="E309" t="n">
+        <v>171</v>
+      </c>
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
@@ -8405,9 +8689,15 @@
     <row r="310">
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr"/>
-      <c r="C310" t="inlineStr"/>
-      <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr"/>
+      <c r="C310" t="n">
+        <v>54</v>
+      </c>
+      <c r="D310" t="n">
+        <v>181</v>
+      </c>
+      <c r="E310" t="n">
+        <v>188</v>
+      </c>
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr"/>
@@ -8423,9 +8713,15 @@
     <row r="311">
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr"/>
-      <c r="C311" t="inlineStr"/>
-      <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr"/>
+      <c r="C311" t="n">
+        <v>181</v>
+      </c>
+      <c r="D311" t="n">
+        <v>13</v>
+      </c>
+      <c r="E311" t="n">
+        <v>184</v>
+      </c>
       <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr"/>
@@ -8441,9 +8737,15 @@
     <row r="312">
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr"/>
-      <c r="C312" t="inlineStr"/>
-      <c r="D312" t="inlineStr"/>
-      <c r="E312" t="inlineStr"/>
+      <c r="C312" t="n">
+        <v>188</v>
+      </c>
+      <c r="D312" t="n">
+        <v>184</v>
+      </c>
+      <c r="E312" t="n">
+        <v>55</v>
+      </c>
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
@@ -8459,9 +8761,15 @@
     <row r="313">
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr"/>
-      <c r="C313" t="inlineStr"/>
-      <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr"/>
+      <c r="C313" t="n">
+        <v>181</v>
+      </c>
+      <c r="D313" t="n">
+        <v>184</v>
+      </c>
+      <c r="E313" t="n">
+        <v>188</v>
+      </c>
       <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr"/>
@@ -8477,9 +8785,15 @@
     <row r="314">
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr"/>
-      <c r="C314" t="inlineStr"/>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
+      <c r="C314" t="n">
+        <v>52</v>
+      </c>
+      <c r="D314" t="n">
+        <v>189</v>
+      </c>
+      <c r="E314" t="n">
+        <v>174</v>
+      </c>
       <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr"/>
@@ -8495,9 +8809,15 @@
     <row r="315">
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr"/>
-      <c r="C315" t="inlineStr"/>
-      <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
+      <c r="C315" t="n">
+        <v>189</v>
+      </c>
+      <c r="D315" t="n">
+        <v>55</v>
+      </c>
+      <c r="E315" t="n">
+        <v>182</v>
+      </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr"/>
@@ -8510,6 +8830,1194 @@
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr"/>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr"/>
+      <c r="B316" t="inlineStr"/>
+      <c r="C316" t="n">
+        <v>174</v>
+      </c>
+      <c r="D316" t="n">
+        <v>182</v>
+      </c>
+      <c r="E316" t="n">
+        <v>16</v>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="n">
+        <v>189</v>
+      </c>
+      <c r="D317" t="n">
+        <v>182</v>
+      </c>
+      <c r="E317" t="n">
+        <v>174</v>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr"/>
+      <c r="B318" t="inlineStr"/>
+      <c r="C318" t="n">
+        <v>54</v>
+      </c>
+      <c r="D318" t="n">
+        <v>188</v>
+      </c>
+      <c r="E318" t="n">
+        <v>187</v>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr"/>
+      <c r="B319" t="inlineStr"/>
+      <c r="C319" t="n">
+        <v>188</v>
+      </c>
+      <c r="D319" t="n">
+        <v>55</v>
+      </c>
+      <c r="E319" t="n">
+        <v>189</v>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" t="inlineStr"/>
+      <c r="C320" t="n">
+        <v>187</v>
+      </c>
+      <c r="D320" t="n">
+        <v>189</v>
+      </c>
+      <c r="E320" t="n">
+        <v>52</v>
+      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="inlineStr"/>
+      <c r="C321" t="n">
+        <v>188</v>
+      </c>
+      <c r="D321" t="n">
+        <v>189</v>
+      </c>
+      <c r="E321" t="n">
+        <v>187</v>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+      <c r="J321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" t="inlineStr"/>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+      <c r="J322" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" t="inlineStr"/>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" t="inlineStr"/>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr"/>
+      <c r="B325" t="inlineStr"/>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
+      <c r="J325" t="n">
+        <v>0</v>
+      </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr"/>
+      <c r="B326" t="inlineStr"/>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" t="inlineStr"/>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
+      <c r="J327" t="n">
+        <v>0</v>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr"/>
+      <c r="B328" t="inlineStr"/>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
+      <c r="J328" t="n">
+        <v>0</v>
+      </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr"/>
+      <c r="B329" t="inlineStr"/>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
+      <c r="J329" t="n">
+        <v>0</v>
+      </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" t="inlineStr"/>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
+      <c r="J330" t="n">
+        <v>0</v>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" t="inlineStr"/>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
+      <c r="J331" t="n">
+        <v>0</v>
+      </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr"/>
+      <c r="B332" t="inlineStr"/>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
+      <c r="J332" t="n">
+        <v>0</v>
+      </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" t="inlineStr"/>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
+      <c r="J333" t="n">
+        <v>0</v>
+      </c>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" t="inlineStr"/>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
+      <c r="J334" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr"/>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
+      <c r="J335" t="n">
+        <v>0</v>
+      </c>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="inlineStr"/>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
+      <c r="J336" t="n">
+        <v>0</v>
+      </c>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
+      <c r="J337" t="n">
+        <v>0</v>
+      </c>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr"/>
+      <c r="B338" t="inlineStr"/>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
+      <c r="J338" t="n">
+        <v>0</v>
+      </c>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" t="inlineStr"/>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
+      <c r="J339" t="n">
+        <v>0</v>
+      </c>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr"/>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
+      <c r="J340" t="n">
+        <v>0</v>
+      </c>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr"/>
+      <c r="B341" t="inlineStr"/>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
+      <c r="J341" t="n">
+        <v>0</v>
+      </c>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr"/>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
+      <c r="J342" t="n">
+        <v>0</v>
+      </c>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+      <c r="B343" t="inlineStr"/>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
+      <c r="J343" t="n">
+        <v>0</v>
+      </c>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr"/>
+      <c r="B344" t="inlineStr"/>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="n">
+        <v>0</v>
+      </c>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr"/>
+      <c r="B345" t="inlineStr"/>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr"/>
+      <c r="J345" t="n">
+        <v>0</v>
+      </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+      <c r="B346" t="inlineStr"/>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
+      <c r="J346" t="n">
+        <v>0</v>
+      </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" t="inlineStr"/>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
+      <c r="J347" t="n">
+        <v>0</v>
+      </c>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" t="inlineStr"/>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
+      <c r="J348" t="n">
+        <v>0</v>
+      </c>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="n">
+        <v>0</v>
+      </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="n">
+        <v>0</v>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr"/>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="n">
+        <v>0</v>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr"/>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="n">
+        <v>0</v>
+      </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="n">
+        <v>0</v>
+      </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="n">
+        <v>0</v>
+      </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="n">
+        <v>0</v>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="n">
+        <v>0</v>
+      </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="n">
+        <v>0</v>
+      </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="n">
+        <v>0</v>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="n">
+        <v>0</v>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr"/>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="n">
+        <v>0</v>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="n">
+        <v>0</v>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="n">
+        <v>0</v>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="n">
+        <v>0</v>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="n">
+        <v>0</v>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr"/>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="n">
+        <v>0</v>
+      </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr"/>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="n">
+        <v>0</v>
+      </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr"/>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="n">
+        <v>0</v>
+      </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr"/>
+      <c r="B370" t="inlineStr"/>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="n">
+        <v>0</v>
+      </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr"/>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
+      <c r="J371" t="n">
+        <v>0</v>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr"/>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="n">
+        <v>0</v>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr"/>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
+      <c r="J373" t="n">
+        <v>0</v>
+      </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" t="inlineStr"/>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="n">
+        <v>0</v>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr"/>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
+      <c r="J375" t="n">
+        <v>0</v>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr"/>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr"/>
+      <c r="J376" t="n">
+        <v>0</v>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr"/>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
+      <c r="J377" t="n">
+        <v>0</v>
+      </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr"/>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr"/>
+      <c r="J378" t="n">
+        <v>0</v>
+      </c>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr"/>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="n">
+        <v>0</v>
+      </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
